--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:53</v>

--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -1313,7 +1313,7 @@
         <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B25" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:42</v>
@@ -1503,7 +1503,7 @@
         <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:33</v>

--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L221"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>מתנאל סבח - שריטות ופחדים קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410322&amp;sid=43fe725fde6d02927362e89be5d6c20b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>3:56</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>מתנאל סבח - שריטות ופחדים קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>ליאור כהן - חוזה לך ברח קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410321&amp;sid=43fe725fde6d02927362e89be5d6c20b</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-01</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Miley Cyrus</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>ליאור כהן - חוזה לך ברח קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>להקת נשמחה - לב לבן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410320&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>3:42</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Conan Gray</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>להקת נשמחה - לב לבן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410319&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>2:16</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>אריאל עדן - הוויה קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410318&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:08</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Kylie Morgan</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>אריאל עדן - הוויה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>אליאור נונה - שבע בערב קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410317&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-01</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:38</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>אליאור נונה - שבע בערב קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410316&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-01</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Angelina Mango</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>אברהם דהאן - בשורות טובות קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410315&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-01</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:59</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Julio Iglesias</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>אברהם דהאן - בשורות טובות קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B10" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-01</v>
@@ -758,10 +758,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:59</v>
+        <v>3:56</v>
       </c>
       <c r="H10" t="str">
-        <v>Loreen</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B11" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-01</v>
@@ -796,10 +796,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:58</v>
+        <v>2:50</v>
       </c>
       <c r="H11" t="str">
-        <v>Jessie Ware</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-01</v>
@@ -834,10 +834,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:49</v>
+        <v>3:42</v>
       </c>
       <c r="H12" t="str">
-        <v>Holly Humberstone</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:22</v>
+        <v>2:16</v>
       </c>
       <c r="H13" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:50</v>
+        <v>3:08</v>
       </c>
       <c r="H14" t="str">
-        <v>Ella Langley</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>6:43</v>
+        <v>3:38</v>
       </c>
       <c r="H15" t="str">
-        <v>David Gilmour</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:52</v>
+        <v>3:01</v>
       </c>
       <c r="H16" t="str">
-        <v>Eagles</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-01</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:13</v>
+        <v>3:59</v>
       </c>
       <c r="H17" t="str">
-        <v>Moody Joody</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-01</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:28</v>
+        <v>2:59</v>
       </c>
       <c r="H18" t="str">
-        <v>Jackson Dean</v>
+        <v>Loreen</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-01</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:01</v>
+        <v>2:58</v>
       </c>
       <c r="H19" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:00</v>
+        <v>3:49</v>
       </c>
       <c r="H20" t="str">
-        <v>Madison Cunningham</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:35</v>
+        <v>3:22</v>
       </c>
       <c r="H21" t="str">
-        <v>mary in the junkyard</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-01</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:01</v>
+        <v>3:50</v>
       </c>
       <c r="H22" t="str">
-        <v>Adam Sanders</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B23" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-01</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:40</v>
+        <v>6:43</v>
       </c>
       <c r="H23" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B24" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-01</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:25</v>
+        <v>4:52</v>
       </c>
       <c r="H24" t="str">
-        <v>twocolors</v>
+        <v>Eagles</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-01</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:42</v>
+        <v>3:13</v>
       </c>
       <c r="H25" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-01</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:56</v>
+        <v>3:28</v>
       </c>
       <c r="H26" t="str">
-        <v>Prince</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-01</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:12</v>
+        <v>3:01</v>
       </c>
       <c r="H27" t="str">
-        <v>RAYE</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B28" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-01</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:30</v>
+        <v>4:00</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B29" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-01</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:18</v>
+        <v>5:35</v>
       </c>
       <c r="H29" t="str">
-        <v>Pentatonix</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-01</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:33</v>
+        <v>3:01</v>
       </c>
       <c r="H30" t="str">
-        <v>Tenille Townes</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B31" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-01</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:53</v>
+        <v>3:40</v>
       </c>
       <c r="H31" t="str">
-        <v>Jessie Ware</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-01</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:37</v>
+        <v>2:25</v>
       </c>
       <c r="H32" t="str">
-        <v>Niall Horan</v>
+        <v>twocolors</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B33" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:26</v>
+        <v>3:42</v>
       </c>
       <c r="H33" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B34" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:40</v>
+        <v>3:56</v>
       </c>
       <c r="H34" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Prince</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:30</v>
+        <v>5:12</v>
       </c>
       <c r="H35" t="str">
-        <v>Jackson Dean</v>
+        <v>RAYE</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B36" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-01</v>
@@ -1746,10 +1746,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:02</v>
+        <v>3:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Foo Fighters</v>
+        <v>The Warning</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B37" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-01</v>
@@ -1784,10 +1784,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:40</v>
+        <v>3:18</v>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B38" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-01</v>
@@ -1822,10 +1822,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:22</v>
+        <v>3:33</v>
       </c>
       <c r="H38" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-01</v>
@@ -1860,10 +1860,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:47</v>
+        <v>5:53</v>
       </c>
       <c r="H39" t="str">
-        <v>Ella Langley</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B40" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-01</v>
@@ -1898,10 +1898,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:39</v>
+        <v>2:37</v>
       </c>
       <c r="H40" t="str">
-        <v>Cannons</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B41" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-01</v>
@@ -1936,10 +1936,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:10</v>
+        <v>2:26</v>
       </c>
       <c r="H41" t="str">
-        <v>Luke Combs</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-01</v>
@@ -1974,10 +1974,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:47</v>
+        <v>2:40</v>
       </c>
       <c r="H42" t="str">
-        <v>Nessa Barrett</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B43" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-01</v>
@@ -2012,10 +2012,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:14</v>
+        <v>3:30</v>
       </c>
       <c r="H43" t="str">
-        <v>aron!</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-01</v>
@@ -2050,10 +2050,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:00</v>
+        <v>4:02</v>
       </c>
       <c r="H44" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B45" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-01</v>
@@ -2088,10 +2088,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:56</v>
+        <v>3:40</v>
       </c>
       <c r="H45" t="str">
-        <v>DMA'S</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-01</v>
@@ -2126,10 +2126,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:17</v>
+        <v>2:22</v>
       </c>
       <c r="H46" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:17</v>
+        <v>3:47</v>
       </c>
       <c r="H47" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:31</v>
+        <v>3:39</v>
       </c>
       <c r="H48" t="str">
-        <v>Nick Carter</v>
+        <v>Cannons</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:38</v>
+        <v>4:10</v>
       </c>
       <c r="H49" t="str">
-        <v>Carly Pearce</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>4:47</v>
       </c>
       <c r="H50" t="str">
-        <v>OneRepublic</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:57</v>
+        <v>2:14</v>
       </c>
       <c r="H51" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>aron!</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:47</v>
+        <v>4:00</v>
       </c>
       <c r="H52" t="str">
-        <v>Armin van Buuren</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>7:10</v>
+        <v>3:56</v>
       </c>
       <c r="H53" t="str">
-        <v>David Gilmour</v>
+        <v>DMA'S</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H54" t="str">
-        <v>Grace Enger</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-01</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:05</v>
+        <v>3:17</v>
       </c>
       <c r="H55" t="str">
-        <v>Tucker Wetmore</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-01</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:12</v>
+        <v>3:31</v>
       </c>
       <c r="H56" t="str">
-        <v>Freya Ridings</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-01</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>9:11</v>
+        <v>3:38</v>
       </c>
       <c r="H57" t="str">
-        <v>David Gilmour</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-01</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:49</v>
+        <v>4:11</v>
       </c>
       <c r="H58" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-01</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:28</v>
+        <v>2:57</v>
       </c>
       <c r="H59" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-01</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H60" t="str">
-        <v>Martin Garrix</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-01</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:11</v>
+        <v>7:10</v>
       </c>
       <c r="H61" t="str">
-        <v>Baby Queen</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-01</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:27</v>
+        <v>3:06</v>
       </c>
       <c r="H62" t="str">
-        <v>HAUSER</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-01</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:34</v>
+        <v>3:05</v>
       </c>
       <c r="H63" t="str">
-        <v>Holly Humberstone</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-01</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:50</v>
+        <v>3:12</v>
       </c>
       <c r="H64" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-01</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:51</v>
+        <v>9:11</v>
       </c>
       <c r="H65" t="str">
-        <v>Rick Astley</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-01</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:39</v>
+        <v>3:49</v>
       </c>
       <c r="H66" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-01</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:08</v>
+        <v>3:28</v>
       </c>
       <c r="H67" t="str">
-        <v>Jessie J</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-01</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:46</v>
+        <v>3:31</v>
       </c>
       <c r="H68" t="str">
-        <v>Bishop Briggs</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-01</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:42</v>
+        <v>3:11</v>
       </c>
       <c r="H69" t="str">
-        <v>Dean Lewis</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-01</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:31</v>
+        <v>2:27</v>
       </c>
       <c r="H70" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>HAUSER</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-01</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:14</v>
+        <v>3:34</v>
       </c>
       <c r="H71" t="str">
-        <v>Luke Combs</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-01</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:22</v>
+        <v>2:50</v>
       </c>
       <c r="H72" t="str">
-        <v>Allison Russell</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-01</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:43</v>
+        <v>3:51</v>
       </c>
       <c r="H73" t="str">
-        <v>We Three</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-01</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:54</v>
+        <v>2:39</v>
       </c>
       <c r="H74" t="str">
-        <v>paris jackson</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-01</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:46</v>
+        <v>5:08</v>
       </c>
       <c r="H75" t="str">
-        <v>Kane Brown</v>
+        <v>Jessie J</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-01</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:37</v>
+        <v>3:46</v>
       </c>
       <c r="H76" t="str">
-        <v>Lainey Wilson</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-01</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:57</v>
+        <v>2:42</v>
       </c>
       <c r="H77" t="str">
-        <v>Malcolm Todd</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-01</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:38</v>
+        <v>2:31</v>
       </c>
       <c r="H78" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-01</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:29</v>
+        <v>3:14</v>
       </c>
       <c r="H79" t="str">
-        <v>Kungs</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-01</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:28</v>
+        <v>3:22</v>
       </c>
       <c r="H80" t="str">
-        <v>Sunday (1994)</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-01</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:26</v>
+        <v>3:43</v>
       </c>
       <c r="H81" t="str">
-        <v>aron!</v>
+        <v>We Three</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-01</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:51</v>
+        <v>2:54</v>
       </c>
       <c r="H82" t="str">
-        <v>Colinstoughmusic</v>
+        <v>paris jackson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-01</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Sunday (1994)</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-01</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:16</v>
+        <v>3:37</v>
       </c>
       <c r="H84" t="str">
-        <v>Owen Riegling</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-01</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:16</v>
+        <v>2:57</v>
       </c>
       <c r="H85" t="str">
-        <v>LANY</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-01</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:25</v>
+        <v>3:38</v>
       </c>
       <c r="H86" t="str">
-        <v>Maverick Sabre</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-01</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:50</v>
+        <v>4:29</v>
       </c>
       <c r="H87" t="str">
-        <v>Amanda Jordan</v>
+        <v>Kungs</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>4:28</v>
       </c>
       <c r="H88" t="str">
-        <v>Beabadoobee</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:58</v>
+        <v>3:26</v>
       </c>
       <c r="H89" t="str">
-        <v>Spacey Jane</v>
+        <v>aron!</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:25</v>
+        <v>3:51</v>
       </c>
       <c r="H90" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-01</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:09</v>
+        <v>2:49</v>
       </c>
       <c r="H91" t="str">
-        <v>Mei Semones</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-01</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:08</v>
+        <v>4:16</v>
       </c>
       <c r="H92" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-01</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:57</v>
+        <v>4:16</v>
       </c>
       <c r="H93" t="str">
-        <v>Natalie Jane</v>
+        <v>LANY</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-01</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H94" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-01</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:12</v>
+        <v>2:50</v>
       </c>
       <c r="H95" t="str">
-        <v>David Gilmour</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-01</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>Far Caspian</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-01</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:34</v>
+        <v>3:58</v>
       </c>
       <c r="H97" t="str">
-        <v>Celine Dion</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-01</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:48</v>
+        <v>3:25</v>
       </c>
       <c r="H98" t="str">
-        <v>Harry Styles</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-01</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:58</v>
+        <v>4:09</v>
       </c>
       <c r="H99" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-01</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:33</v>
+        <v>2:08</v>
       </c>
       <c r="H100" t="str">
-        <v>Ellise</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-01</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:01</v>
+        <v>2:57</v>
       </c>
       <c r="H101" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:32</v>
+        <v>3:13</v>
       </c>
       <c r="H102" t="str">
-        <v>In Color</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Home on the Range</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>1:37</v>
+        <v>4:12</v>
       </c>
       <c r="H103" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Days We Left Behind</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:18</v>
+        <v>3:57</v>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:47</v>
+        <v>3:34</v>
       </c>
       <c r="H105" t="str">
-        <v>Miley Cyrus</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>6:17</v>
+        <v>3:48</v>
       </c>
       <c r="H106" t="str">
-        <v>RAYE</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>MARATHON</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>MARATHON - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:49</v>
+        <v>4:58</v>
       </c>
       <c r="H107" t="str">
-        <v>Becky G</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ALL THE TIME</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>2:33</v>
       </c>
       <c r="H108" t="str">
-        <v>John Summit</v>
+        <v>Ellise</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Sucker For Love</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sexistential</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:34</v>
+        <v>4:56</v>
       </c>
       <c r="H109" t="str">
-        <v>Robyn</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>FATHER</v>
+        <v>CHICA 305</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>BULLY</v>
+        <v>CHICA 305 - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>2:49</v>
+        <v>3:08</v>
       </c>
       <c r="H110" t="str">
-        <v>Kanye West</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
       </c>
       <c r="L110" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>CHICA 305 - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Lose Control</v>
+        <v>Jet Lag Mouth</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ADL</v>
+        <v>Jet Lag Mouth - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>2:32</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>In Color</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
       </c>
       <c r="L111" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>Jet Lag Mouth - In Color</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Zavier</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>3:18</v>
       </c>
       <c r="H112" t="str">
-        <v>Fetty Wap</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WAGWAN</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:07</v>
+        <v>2:47</v>
       </c>
       <c r="H113" t="str">
-        <v>Central Cee</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L113" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sideways</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>KONNAKOL</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G114" t="str">
-        <v>3:12</v>
+        <v>6:17</v>
       </c>
       <c r="H114" t="str">
-        <v>ZAYN</v>
+        <v>RAYE</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L114" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Automatic</v>
+        <v>MARATHON</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Superbloom</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:57</v>
+        <v>2:49</v>
       </c>
       <c r="H115" t="str">
-        <v>Jessie Ware</v>
+        <v>Becky G</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L115" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tractor Beam</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ricochet</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H116" t="str">
-        <v>Snail Mail</v>
+        <v>John Summit</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L116" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Back Home</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Sexistential</v>
       </c>
       <c r="G117" t="str">
-        <v>1:36</v>
+        <v>3:34</v>
       </c>
       <c r="H117" t="str">
-        <v>MIKE</v>
+        <v>Robyn</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L117" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>prom queen</v>
+        <v>FATHER</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>prom queen - Single</v>
+        <v>BULLY</v>
       </c>
       <c r="G118" t="str">
-        <v>2:43</v>
+        <v>2:49</v>
       </c>
       <c r="H118" t="str">
-        <v>Amelia Moore</v>
+        <v>Kanye West</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L118" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Pal Agua</v>
+        <v>Lose Control</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Pal Agua - Single</v>
+        <v>ADL</v>
       </c>
       <c r="G119" t="str">
-        <v>3:26</v>
+        <v>2:39</v>
       </c>
       <c r="H119" t="str">
-        <v>J Balvin</v>
+        <v>Yeat</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L119" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Phoenix</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Phoenix - Single</v>
+        <v>Zavier</v>
       </c>
       <c r="G120" t="str">
-        <v>2:24</v>
+        <v>3:44</v>
       </c>
       <c r="H120" t="str">
-        <v>Marshmello</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L120" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G121" t="str">
-        <v>2:56</v>
+        <v>2:07</v>
       </c>
       <c r="H121" t="str">
-        <v>Ne-Yo</v>
+        <v>Central Cee</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L121" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Feel Your Rain</v>
+        <v>Sideways</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G122" t="str">
-        <v>3:36</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>Eli</v>
+        <v>ZAYN</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L122" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Lonely</v>
+        <v>Automatic</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Ö</v>
+        <v>Superbloom</v>
       </c>
       <c r="G123" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H123" t="str">
-        <v>Fcukers</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L123" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Back in Love</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Back in Love - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G124" t="str">
-        <v>3:14</v>
+        <v>3:34</v>
       </c>
       <c r="H124" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L124" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Sideways</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Whatever's Clever!</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G125" t="str">
-        <v>3:55</v>
+        <v>1:37</v>
       </c>
       <c r="H125" t="str">
-        <v>Charlie Puth</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L125" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>prom queen</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Honora</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:22</v>
+        <v>2:43</v>
       </c>
       <c r="H126" t="str">
-        <v>Flea</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L126" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Back Home</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>1:36</v>
       </c>
       <c r="H127" t="str">
-        <v>Chelsea Cutler</v>
+        <v>MIKE</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L127" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:02</v>
+        <v>3:26</v>
       </c>
       <c r="H128" t="str">
-        <v>Honey Bxby</v>
+        <v>J Balvin</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L128" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>One Thing At A Time</v>
+        <v>Phoenix</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Creature of Habit</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:42</v>
+        <v>2:24</v>
       </c>
       <c r="H129" t="str">
-        <v>Courtney Barnett</v>
+        <v>Marshmello</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L129" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>wasteland</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>wasteland - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:05</v>
+        <v>2:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Yuna</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L130" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>getting up to no good</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:31</v>
+        <v>3:36</v>
       </c>
       <c r="H131" t="str">
-        <v>Artemas</v>
+        <v>Eli</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L131" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Por LA</v>
+        <v>Lonely</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>TODO Ø NADA</v>
+        <v>Ö</v>
       </c>
       <c r="G132" t="str">
-        <v>2:19</v>
+        <v>2:58</v>
       </c>
       <c r="H132" t="str">
-        <v>Linea Personal</v>
+        <v>Fcukers</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L132" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>You Lead Me</v>
+        <v>Back in Love</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:14</v>
+        <v>3:14</v>
       </c>
       <c r="H133" t="str">
-        <v>Lauren Daigle</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L133" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Just A Kid</v>
+        <v>Sideways</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Broken View</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G134" t="str">
-        <v>4:18</v>
+        <v>3:55</v>
       </c>
       <c r="H134" t="str">
-        <v>Sam Barber</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L134" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Country And She Knows It</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G135" t="str">
-        <v>2:54</v>
+        <v>4:22</v>
       </c>
       <c r="H135" t="str">
-        <v>Luke Bryan</v>
+        <v>Flea</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L135" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Georgia On My Mind</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:35</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>Thomas Rhett</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L136" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Deep Blue</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Deep Blue</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:17</v>
+        <v>3:02</v>
       </c>
       <c r="H137" t="str">
-        <v>ERNEST</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L137" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Special</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>sounds for someone</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G138" t="str">
-        <v>2:49</v>
+        <v>4:42</v>
       </c>
       <c r="H138" t="str">
-        <v>Elmiene</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L138" t="str">
-        <v>Special - Elmiene</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Heart Attack</v>
+        <v>wasteland</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>CANDY</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:52</v>
+        <v>3:05</v>
       </c>
       <c r="H139" t="str">
-        <v>Justine Skye</v>
+        <v>Yuna</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L139" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>STAY</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>STAY - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G140" t="str">
-        <v>3:06</v>
+        <v>2:31</v>
       </c>
       <c r="H140" t="str">
-        <v>Stray Kids</v>
+        <v>Artemas</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L140" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Unglued</v>
+        <v>Por LA</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Work of Heart</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G141" t="str">
-        <v>3:54</v>
+        <v>2:19</v>
       </c>
       <c r="H141" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L141" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Ritual</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Ritual - Single</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G142" t="str">
-        <v>3:01</v>
+        <v>4:14</v>
       </c>
       <c r="H142" t="str">
-        <v>Icona Pop</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L142" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>The Best</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Broken View</v>
       </c>
       <c r="G143" t="str">
-        <v>3:48</v>
+        <v>4:18</v>
       </c>
       <c r="H143" t="str">
-        <v>Conan Gray</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L143" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Smile</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Smile - Single</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:50</v>
+        <v>2:54</v>
       </c>
       <c r="H144" t="str">
-        <v>Two Shell</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L144" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Duro</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Duro - Single</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:05</v>
+        <v>2:35</v>
       </c>
       <c r="H145" t="str">
-        <v>Skrillex</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L145" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G146" t="str">
-        <v>2:58</v>
+        <v>3:17</v>
       </c>
       <c r="H146" t="str">
-        <v>Sublime</v>
+        <v>ERNEST</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L146" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Carousel</v>
+        <v>Special</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Everything Glows</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G147" t="str">
-        <v>3:36</v>
+        <v>2:49</v>
       </c>
       <c r="H147" t="str">
-        <v>Cannons</v>
+        <v>Elmiene</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L147" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Mercy</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Mercy - Single</v>
+        <v>CANDY</v>
       </c>
       <c r="G148" t="str">
-        <v>3:49</v>
+        <v>2:52</v>
       </c>
       <c r="H148" t="str">
-        <v>PRESIDENT</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L148" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Palms</v>
+        <v>STAY</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Palms - Single</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:18</v>
+        <v>3:06</v>
       </c>
       <c r="H149" t="str">
-        <v>The Maine</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L149" t="str">
-        <v>Palms - The Maine</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Ozzy's Song</v>
+        <v>Unglued</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G150" t="str">
-        <v>5:28</v>
+        <v>3:54</v>
       </c>
       <c r="H150" t="str">
-        <v>Black Label Society</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L150" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Danger</v>
+        <v>Ritual</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Danger - Single</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:19</v>
+        <v>3:01</v>
       </c>
       <c r="H151" t="str">
-        <v>Nia Archives</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L151" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Icarus</v>
+        <v>The Best</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Icarus - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G152" t="str">
-        <v>4:25</v>
+        <v>3:48</v>
       </c>
       <c r="H152" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L152" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>idk idk</v>
+        <v>Smile</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>idk idk - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:26</v>
+        <v>3:50</v>
       </c>
       <c r="H153" t="str">
-        <v>Jim Legxacy</v>
+        <v>Two Shell</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L153" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tonight</v>
+        <v>Duro</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Tonight - Single</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:25</v>
+        <v>3:05</v>
       </c>
       <c r="H154" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Skrillex</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L154" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Switcheroo</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G155" t="str">
-        <v>3:44</v>
+        <v>2:58</v>
       </c>
       <c r="H155" t="str">
-        <v>Gelli Haha</v>
+        <v>Sublime</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L155" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>Carousel</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G156" t="str">
-        <v>2:45</v>
+        <v>3:36</v>
       </c>
       <c r="H156" t="str">
-        <v>BIA</v>
+        <v>Cannons</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L156" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>this girl wants everything</v>
+        <v>Mercy</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:33</v>
+        <v>3:49</v>
       </c>
       <c r="H157" t="str">
-        <v>Isaia Huron</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L157" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>Palms</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:44</v>
+        <v>3:18</v>
       </c>
       <c r="H158" t="str">
-        <v>Slayyyter</v>
+        <v>The Maine</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L158" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Deep Water - EP</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G159" t="str">
-        <v>2:41</v>
+        <v>5:28</v>
       </c>
       <c r="H159" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L159" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>R3verse</v>
+        <v>Danger</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>takeaways</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:31</v>
+        <v>2:19</v>
       </c>
       <c r="H160" t="str">
-        <v>Medium Build</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L160" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>Icarus</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:32</v>
+        <v>4:25</v>
       </c>
       <c r="H161" t="str">
-        <v>MIKE</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L161" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>heart of gold</v>
+        <v>idk idk</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>heart of gold - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:51</v>
+        <v>2:26</v>
       </c>
       <c r="H162" t="str">
-        <v>kai devega</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L162" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Breaking Down</v>
+        <v>Tonight</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Skeletor</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:21</v>
+        <v>2:25</v>
       </c>
       <c r="H163" t="str">
-        <v>Chief Keef</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L163" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Dream House</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Dream House - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G164" t="str">
-        <v>2:54</v>
+        <v>3:44</v>
       </c>
       <c r="H164" t="str">
-        <v>Empress Of</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L164" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Baby Blue</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>2:51</v>
+        <v>2:45</v>
       </c>
       <c r="H165" t="str">
-        <v>Cody Simpson</v>
+        <v>BIA</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L165" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G166" t="str">
-        <v>2:37</v>
+        <v>3:33</v>
       </c>
       <c r="H166" t="str">
-        <v>MEDUZA</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L166" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Forever Now</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G167" t="str">
-        <v>4:05</v>
+        <v>3:44</v>
       </c>
       <c r="H167" t="str">
-        <v>Switchfoot</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L167" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>3:46</v>
+        <v>2:41</v>
       </c>
       <c r="H168" t="str">
-        <v>Benny G</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L168" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Cry In Front Of You</v>
+        <v>R3verse</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>takeaways</v>
       </c>
       <c r="G169" t="str">
-        <v>3:03</v>
+        <v>3:31</v>
       </c>
       <c r="H169" t="str">
-        <v>Eric Bellinger</v>
+        <v>Medium Build</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L169" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G170" t="str">
-        <v>4:19</v>
+        <v>2:32</v>
       </c>
       <c r="H170" t="str">
-        <v>Anish Kumar</v>
+        <v>MIKE</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L170" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>GASLIGHT</v>
+        <v>heart of gold</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:10</v>
+        <v>2:51</v>
       </c>
       <c r="H171" t="str">
-        <v>WesGhost</v>
+        <v>kai devega</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L171" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Truth To Be Told</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G172" t="str">
-        <v>3:17</v>
+        <v>4:21</v>
       </c>
       <c r="H172" t="str">
-        <v>GERD</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L172" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Free Your Mind</v>
+        <v>Dream House</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:21</v>
+        <v>2:54</v>
       </c>
       <c r="H173" t="str">
-        <v>Prospa</v>
+        <v>Empress Of</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L173" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Down To The Bone</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G174" t="str">
         <v>2:51</v>
       </c>
       <c r="H174" t="str">
-        <v>Josh Baker</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L174" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Breathe</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Breathe - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:48</v>
+        <v>2:37</v>
       </c>
       <c r="H175" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L175" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>xs</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>xs - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G176" t="str">
-        <v>3:19</v>
+        <v>4:05</v>
       </c>
       <c r="H176" t="str">
-        <v>Ashley Cooke</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L176" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Sail</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G177" t="str">
-        <v>4:54</v>
+        <v>3:46</v>
       </c>
       <c r="H177" t="str">
-        <v>Future Islands</v>
+        <v>Benny G</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L177" t="str">
-        <v>Sail - Future Islands</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Dreaming</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Dear Nashville</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:33</v>
+        <v>3:03</v>
       </c>
       <c r="H178" t="str">
-        <v>Ashley Monroe</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L178" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>NEW TINGZ</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G179" t="str">
-        <v>2:39</v>
+        <v>4:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Armanii</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L179" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>La Opinión</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Mis Compas El Final</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:23</v>
+        <v>2:10</v>
       </c>
       <c r="H180" t="str">
-        <v>Joss Favela</v>
+        <v>WesGhost</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L180" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>qué ves en mí?</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:24</v>
+        <v>3:17</v>
       </c>
       <c r="H181" t="str">
-        <v>Paloma Morphy</v>
+        <v>GERD</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L181" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:43</v>
+        <v>3:21</v>
       </c>
       <c r="H182" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Prospa</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L182" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>TUTUTU</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:16</v>
+        <v>2:51</v>
       </c>
       <c r="H183" t="str">
-        <v>ELENA ROSE</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L183" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>Breathe</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:56</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>2'Live Bre</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L184" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Me Neither</v>
+        <v>xs</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Heavy On The Soul</v>
+        <v>xs - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:32</v>
+        <v>3:19</v>
       </c>
       <c r="H185" t="str">
-        <v>Ty Myers</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L185" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Cole Palmer</v>
+        <v>Sail</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Solid Ground</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G186" t="str">
-        <v>2:48</v>
+        <v>4:54</v>
       </c>
       <c r="H186" t="str">
-        <v>Limoblaze</v>
+        <v>Future Islands</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L186" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Wonder</v>
+        <v>Dreaming</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Wonder - Single</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G187" t="str">
-        <v>3:48</v>
+        <v>3:33</v>
       </c>
       <c r="H187" t="str">
-        <v>Meeks Carter</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L187" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>ICU</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>ICU - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G188" t="str">
-        <v>2:53</v>
+        <v>2:39</v>
       </c>
       <c r="H188" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Armanii</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L188" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>La Opinión</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G189" t="str">
-        <v>2:45</v>
+        <v>3:23</v>
       </c>
       <c r="H189" t="str">
-        <v>Jozzy</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L189" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Waiting Room (feat. Jordan Ward)</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Single</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:21</v>
+        <v>3:24</v>
       </c>
       <c r="H190" t="str">
-        <v>Jenevieve</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L190" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Rise</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:02</v>
+        <v>2:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L191" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Roll On Thru</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:51</v>
+        <v>2:16</v>
       </c>
       <c r="H192" t="str">
-        <v>Hayden Everett</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L192" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Delicately</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Delicately - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:20</v>
+        <v>2:56</v>
       </c>
       <c r="H193" t="str">
-        <v>Andrea Bejar</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L193" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>One Of Those Things</v>
+        <v>Me Neither</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G194" t="str">
-        <v>3:27</v>
+        <v>3:32</v>
       </c>
       <c r="H194" t="str">
-        <v>Lucy Clearwater</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L194" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>For Every Dusk</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G195" t="str">
-        <v>6:04</v>
+        <v>2:48</v>
       </c>
       <c r="H195" t="str">
-        <v>José González</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L195" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>I'll Wait</v>
+        <v>Wonder</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:33</v>
+        <v>3:48</v>
       </c>
       <c r="H196" t="str">
-        <v>Buzzy Lee</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L196" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Daisy</v>
+        <v>ICU</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Daisy - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:02</v>
+        <v>2:53</v>
       </c>
       <c r="H197" t="str">
-        <v>Lola Blue</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L197" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Friend Remixes</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G198" t="str">
-        <v>3:57</v>
+        <v>2:45</v>
       </c>
       <c r="H198" t="str">
-        <v>james K</v>
+        <v>Jozzy</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L198" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Waiting Room (feat. Jordan Ward)</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Perdidos - Single</v>
+        <v>Waiting Room (feat. Jordan Ward) - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:45</v>
+        <v>3:21</v>
       </c>
       <c r="H199" t="str">
-        <v>MAVICA</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
       </c>
       <c r="L199" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Fort</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Fort - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G200" t="str">
-        <v>2:27</v>
+        <v>4:02</v>
       </c>
       <c r="H200" t="str">
-        <v>Lamb</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L200" t="str">
-        <v>Fort - Lamb</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>SAME LA</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>SAME LA - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:44</v>
+        <v>3:51</v>
       </c>
       <c r="H201" t="str">
-        <v>Tiffany Day</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L201" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Working On It</v>
+        <v>Delicately</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-01</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Working On It - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>3:20</v>
       </c>
       <c r="H202" t="str">
-        <v>Arthur Hill</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L202" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>spring cleaning</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-01</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>spring cleaning - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>4:03</v>
+        <v>3:27</v>
       </c>
       <c r="H203" t="str">
-        <v>Ethan Regan</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L203" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Just Drivin'</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-01</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G204" t="str">
-        <v>3:26</v>
+        <v>6:04</v>
       </c>
       <c r="H204" t="str">
-        <v>Presley Haile</v>
+        <v>José González</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L204" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Simple Things</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D205" t="str">
         <v>2026-04-01</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Simple Things - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G205" t="str">
-        <v>3:46</v>
+        <v>3:33</v>
       </c>
       <c r="H205" t="str">
-        <v>Evening Elephants</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L205" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Want It Back</v>
+        <v>Daisy</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D206" t="str">
         <v>2026-04-01</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Want It Back - Single</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H206" t="str">
-        <v>Giant Rooks</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L206" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Bite Down</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D207" t="str">
         <v>2026-04-01</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Bite Down - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G207" t="str">
-        <v>3:36</v>
+        <v>3:57</v>
       </c>
       <c r="H207" t="str">
-        <v>Anna Sofia</v>
+        <v>james K</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L207" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D208" t="str">
         <v>2026-04-01</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>5:42</v>
+        <v>2:45</v>
       </c>
       <c r="H208" t="str">
-        <v>Dimmu Borgir</v>
+        <v>MAVICA</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L208" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Demons</v>
+        <v>Fort</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D209" t="str">
         <v>2026-04-01</v>
@@ -8317,36 +8317,36 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G209" t="str">
-        <v>2:42</v>
+        <v>2:27</v>
       </c>
       <c r="H209" t="str">
-        <v>Anella</v>
+        <v>Lamb</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L209" t="str">
-        <v>Demons - Anella</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Es brennt...</v>
+        <v>SAME LA</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D210" t="str">
         <v>2026-04-01</v>
@@ -8355,36 +8355,36 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Es brennt... - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G210" t="str">
-        <v>3:35</v>
+        <v>3:44</v>
       </c>
       <c r="H210" t="str">
-        <v>Till Lindemann</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L210" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Fire Marengo</v>
+        <v>Working On It</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D211" t="str">
         <v>2026-04-01</v>
@@ -8393,68 +8393,410 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G211" t="str">
-        <v>3:49</v>
+        <v>3:06</v>
       </c>
       <c r="H211" t="str">
-        <v>Enslaved</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L211" t="str">
-        <v>Fire Marengo - Enslaved</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
+        <v>spring cleaning</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>spring cleaning - Single</v>
+      </c>
+      <c r="G212" t="str">
+        <v>4:03</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Ethan Regan</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+      </c>
+      <c r="L212" t="str">
+        <v>spring cleaning - Ethan Regan</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Just Drivin'</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>Just Drivin' - Single</v>
+      </c>
+      <c r="G213" t="str">
+        <v>3:26</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Presley Haile</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Just Drivin' - Presley Haile</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Simple Things</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>Simple Things - Single</v>
+      </c>
+      <c r="G214" t="str">
+        <v>3:46</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Evening Elephants</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Simple Things - Evening Elephants</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Want It Back</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>Want It Back - Single</v>
+      </c>
+      <c r="G215" t="str">
+        <v>3:27</v>
+      </c>
+      <c r="H215" t="str">
+        <v>Giant Rooks</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Want It Back - Giant Rooks</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>Bite Down</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v>Bite Down - Single</v>
+      </c>
+      <c r="G216" t="str">
+        <v>3:36</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Anna Sofia</v>
+      </c>
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+      </c>
+      <c r="K216" t="str">
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Bite Down - Anna Sofia</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Ulvgjeld &amp; Blodsodel</v>
+      </c>
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+      </c>
+      <c r="D217" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v>Grand Serpent Rising</v>
+      </c>
+      <c r="G217" t="str">
+        <v>5:42</v>
+      </c>
+      <c r="H217" t="str">
+        <v>Dimmu Borgir</v>
+      </c>
+      <c r="I217" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J217" t="str">
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+      </c>
+      <c r="K217" t="str">
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+      </c>
+      <c r="L217" t="str">
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Demons</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" t="str">
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
+      </c>
+      <c r="D218" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v>Ask Me How I’ve Been</v>
+      </c>
+      <c r="G218" t="str">
+        <v>2:42</v>
+      </c>
+      <c r="H218" t="str">
+        <v>Anella</v>
+      </c>
+      <c r="I218" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+      </c>
+      <c r="K218" t="str">
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Demons - Anella</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Es brennt...</v>
+      </c>
+      <c r="B219" t="str">
+        <v/>
+      </c>
+      <c r="C219" t="str">
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+      </c>
+      <c r="D219" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v>Es brennt... - Single</v>
+      </c>
+      <c r="G219" t="str">
+        <v>3:35</v>
+      </c>
+      <c r="H219" t="str">
+        <v>Till Lindemann</v>
+      </c>
+      <c r="I219" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J219" t="str">
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+      </c>
+      <c r="K219" t="str">
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+      </c>
+      <c r="L219" t="str">
+        <v>Es brennt... - Till Lindemann</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Fire Marengo</v>
+      </c>
+      <c r="B220" t="str">
+        <v/>
+      </c>
+      <c r="C220" t="str">
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+      </c>
+      <c r="D220" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+      </c>
+      <c r="G220" t="str">
+        <v>3:49</v>
+      </c>
+      <c r="H220" t="str">
+        <v>Enslaved</v>
+      </c>
+      <c r="I220" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J220" t="str">
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+      </c>
+      <c r="K220" t="str">
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+      </c>
+      <c r="L220" t="str">
+        <v>Fire Marengo - Enslaved</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
         <v>Close to the Bone</v>
       </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
+      <c r="B221" t="str">
+        <v/>
+      </c>
+      <c r="C221" t="str">
         <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
-      <c r="D212" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
+      <c r="D221" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G212" t="str">
+      <c r="G221" t="str">
         <v>4:09</v>
       </c>
-      <c r="H212" t="str">
+      <c r="H221" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
+      <c r="I221" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J221" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K212" t="str">
+      <c r="K221" t="str">
         <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
-      <c r="L212" t="str">
+      <c r="L221" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L212"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L221"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L221"/>
+  <dimension ref="A1:L213"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתנאל סבח - שריטות ופחדים קאבר</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-01</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410322&amp;sid=43fe725fde6d02927362e89be5d6c20b</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:56</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתנאל סבח - שריטות ופחדים קאבר</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאור כהן - חוזה לך ברח קאבר</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-01</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410321&amp;sid=43fe725fde6d02927362e89be5d6c20b</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-01</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2:50</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאור כהן - חוזה לך ברח קאבר</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>להקת נשמחה - לב לבן קאבר</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-01</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410320&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>3:42</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Conan Gray</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>להקת נשמחה - לב לבן קאבר</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-01</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410319&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>2:16</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אריאל עדן - הוויה קאבר</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-01</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410318&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>3:08</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אריאל עדן - הוויה קאבר</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אליאור נונה - שבע בערב קאבר</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-01</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410317&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-01</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>3:38</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אליאור נונה - שבע בערב קאבר</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-01</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410316&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-01</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>3:01</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Angelina Mango</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אברהם דהאן - בשורות טובות קאבר</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-01</v>
+        <v>5 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410315&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-01</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אברהם דהאן - בשורות טובות קאבר</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-01</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:56</v>
+        <v>2:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Charlie Puth</v>
+        <v>Loreen</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-01</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:50</v>
+        <v>2:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Miley Cyrus</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="H12" t="str">
-        <v>Conan Gray</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:16</v>
+        <v>3:22</v>
       </c>
       <c r="H13" t="str">
-        <v>Charlie Puth</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:08</v>
+        <v>3:50</v>
       </c>
       <c r="H14" t="str">
-        <v>Kylie Morgan</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:38</v>
+        <v>6:43</v>
       </c>
       <c r="H15" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:01</v>
+        <v>4:52</v>
       </c>
       <c r="H16" t="str">
-        <v>Angelina Mango</v>
+        <v>Eagles</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-01</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:59</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>Julio Iglesias</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-01</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:59</v>
+        <v>3:28</v>
       </c>
       <c r="H18" t="str">
-        <v>Loreen</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-01</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:58</v>
+        <v>3:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:49</v>
+        <v>4:00</v>
       </c>
       <c r="H20" t="str">
-        <v>Holly Humberstone</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:22</v>
+        <v>5:35</v>
       </c>
       <c r="H21" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-01</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:50</v>
+        <v>3:01</v>
       </c>
       <c r="H22" t="str">
-        <v>Ella Langley</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-01</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>6:43</v>
+        <v>3:40</v>
       </c>
       <c r="H23" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-01</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:52</v>
+        <v>2:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Eagles</v>
+        <v>twocolors</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-01</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:13</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>Moody Joody</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-01</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Jackson Dean</v>
+        <v>Prince</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-01</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:01</v>
+        <v>5:12</v>
       </c>
       <c r="H27" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>RAYE</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-01</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:00</v>
+        <v>3:30</v>
       </c>
       <c r="H28" t="str">
-        <v>Madison Cunningham</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-01</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:35</v>
+        <v>3:18</v>
       </c>
       <c r="H29" t="str">
-        <v>mary in the junkyard</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-01</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:01</v>
+        <v>3:33</v>
       </c>
       <c r="H30" t="str">
-        <v>Adam Sanders</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-01</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:40</v>
+        <v>5:53</v>
       </c>
       <c r="H31" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B32" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-01</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:25</v>
+        <v>2:37</v>
       </c>
       <c r="H32" t="str">
-        <v>twocolors</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B33" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-01</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:42</v>
+        <v>2:26</v>
       </c>
       <c r="H33" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-01</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:56</v>
+        <v>2:40</v>
       </c>
       <c r="H34" t="str">
-        <v>Prince</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-01</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:12</v>
+        <v>3:30</v>
       </c>
       <c r="H35" t="str">
-        <v>RAYE</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-01</v>
@@ -1746,10 +1746,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:30</v>
+        <v>4:02</v>
       </c>
       <c r="H36" t="str">
-        <v>The Warning</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-01</v>
@@ -1784,10 +1784,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:18</v>
+        <v>3:40</v>
       </c>
       <c r="H37" t="str">
-        <v>Pentatonix</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-01</v>
@@ -1822,10 +1822,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H38" t="str">
-        <v>Tenille Townes</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-01</v>
@@ -1860,10 +1860,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>5:53</v>
+        <v>3:47</v>
       </c>
       <c r="H39" t="str">
-        <v>Jessie Ware</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-01</v>
@@ -1898,10 +1898,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:37</v>
+        <v>3:39</v>
       </c>
       <c r="H40" t="str">
-        <v>Niall Horan</v>
+        <v>Cannons</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B41" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-01</v>
@@ -1936,10 +1936,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:26</v>
+        <v>4:10</v>
       </c>
       <c r="H41" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B42" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-01</v>
@@ -1974,10 +1974,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:40</v>
+        <v>4:47</v>
       </c>
       <c r="H42" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B43" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-01</v>
@@ -2012,10 +2012,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:30</v>
+        <v>2:14</v>
       </c>
       <c r="H43" t="str">
-        <v>Jackson Dean</v>
+        <v>aron!</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B44" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-01</v>
@@ -2050,10 +2050,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:02</v>
+        <v>4:00</v>
       </c>
       <c r="H44" t="str">
-        <v>Foo Fighters</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B45" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-01</v>
@@ -2088,10 +2088,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:40</v>
+        <v>3:56</v>
       </c>
       <c r="H45" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DMA'S</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:22</v>
+        <v>3:17</v>
       </c>
       <c r="H46" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:47</v>
+        <v>3:17</v>
       </c>
       <c r="H47" t="str">
-        <v>Ella Langley</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:39</v>
+        <v>3:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Cannons</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:10</v>
+        <v>3:38</v>
       </c>
       <c r="H49" t="str">
-        <v>Luke Combs</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:47</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>Nessa Barrett</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:14</v>
+        <v>2:57</v>
       </c>
       <c r="H51" t="str">
-        <v>aron!</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:00</v>
+        <v>3:47</v>
       </c>
       <c r="H52" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:56</v>
+        <v>7:10</v>
       </c>
       <c r="H53" t="str">
-        <v>DMA'S</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H54" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-01</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:17</v>
+        <v>3:05</v>
       </c>
       <c r="H55" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-01</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:31</v>
+        <v>3:12</v>
       </c>
       <c r="H56" t="str">
-        <v>Nick Carter</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-01</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:38</v>
+        <v>9:11</v>
       </c>
       <c r="H57" t="str">
-        <v>Carly Pearce</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-01</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:11</v>
+        <v>3:49</v>
       </c>
       <c r="H58" t="str">
-        <v>OneRepublic</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-01</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:57</v>
+        <v>3:28</v>
       </c>
       <c r="H59" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-01</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:47</v>
+        <v>3:31</v>
       </c>
       <c r="H60" t="str">
-        <v>Armin van Buuren</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-01</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>7:10</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>David Gilmour</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-01</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:06</v>
+        <v>2:27</v>
       </c>
       <c r="H62" t="str">
-        <v>Grace Enger</v>
+        <v>HAUSER</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-01</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:05</v>
+        <v>3:34</v>
       </c>
       <c r="H63" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-01</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:12</v>
+        <v>2:50</v>
       </c>
       <c r="H64" t="str">
-        <v>Freya Ridings</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-01</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>9:11</v>
+        <v>3:51</v>
       </c>
       <c r="H65" t="str">
-        <v>David Gilmour</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-01</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:49</v>
+        <v>2:39</v>
       </c>
       <c r="H66" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-01</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:28</v>
+        <v>5:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Jessie J</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-01</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:31</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Martin Garrix</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-01</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:11</v>
+        <v>2:42</v>
       </c>
       <c r="H69" t="str">
-        <v>Baby Queen</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-01</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:27</v>
+        <v>2:31</v>
       </c>
       <c r="H70" t="str">
-        <v>HAUSER</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-01</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:34</v>
+        <v>3:14</v>
       </c>
       <c r="H71" t="str">
-        <v>Holly Humberstone</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-01</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:50</v>
+        <v>3:22</v>
       </c>
       <c r="H72" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-01</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:51</v>
+        <v>3:43</v>
       </c>
       <c r="H73" t="str">
-        <v>Rick Astley</v>
+        <v>We Three</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-01</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:39</v>
+        <v>2:54</v>
       </c>
       <c r="H74" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>paris jackson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-01</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>5:08</v>
+        <v>2:46</v>
       </c>
       <c r="H75" t="str">
-        <v>Jessie J</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-01</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:46</v>
+        <v>3:37</v>
       </c>
       <c r="H76" t="str">
-        <v>Bishop Briggs</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-01</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:42</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Dean Lewis</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-01</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:31</v>
+        <v>3:38</v>
       </c>
       <c r="H78" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-01</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:14</v>
+        <v>4:29</v>
       </c>
       <c r="H79" t="str">
-        <v>Luke Combs</v>
+        <v>Kungs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-01</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:22</v>
+        <v>4:28</v>
       </c>
       <c r="H80" t="str">
-        <v>Allison Russell</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-01</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:43</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>We Three</v>
+        <v>aron!</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-01</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:54</v>
+        <v>3:51</v>
       </c>
       <c r="H82" t="str">
-        <v>paris jackson</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-01</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>2:49</v>
       </c>
       <c r="H83" t="str">
-        <v>Kane Brown</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-01</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:37</v>
+        <v>4:16</v>
       </c>
       <c r="H84" t="str">
-        <v>Lainey Wilson</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-01</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:57</v>
+        <v>4:16</v>
       </c>
       <c r="H85" t="str">
-        <v>Malcolm Todd</v>
+        <v>LANY</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-01</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:38</v>
+        <v>3:25</v>
       </c>
       <c r="H86" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-01</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:29</v>
+        <v>2:50</v>
       </c>
       <c r="H87" t="str">
-        <v>Kungs</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-01</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:28</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Sunday (1994)</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-01</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:26</v>
+        <v>3:58</v>
       </c>
       <c r="H89" t="str">
-        <v>aron!</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-01</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:51</v>
+        <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-01</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:49</v>
+        <v>4:09</v>
       </c>
       <c r="H91" t="str">
-        <v>Sunday (1994)</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-01</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:16</v>
+        <v>2:08</v>
       </c>
       <c r="H92" t="str">
-        <v>Owen Riegling</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-01</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:16</v>
+        <v>2:57</v>
       </c>
       <c r="H93" t="str">
-        <v>LANY</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-01</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:25</v>
+        <v>3:13</v>
       </c>
       <c r="H94" t="str">
-        <v>Maverick Sabre</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-01</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:50</v>
+        <v>4:12</v>
       </c>
       <c r="H95" t="str">
-        <v>Amanda Jordan</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-01</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>Beabadoobee</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-01</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:58</v>
+        <v>3:34</v>
       </c>
       <c r="H97" t="str">
-        <v>Spacey Jane</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-01</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:25</v>
+        <v>3:48</v>
       </c>
       <c r="H98" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-01</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:09</v>
+        <v>4:58</v>
       </c>
       <c r="H99" t="str">
-        <v>Mei Semones</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-01</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:08</v>
+        <v>2:33</v>
       </c>
       <c r="H100" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Ellise</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-01</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:57</v>
+        <v>4:56</v>
       </c>
       <c r="H101" t="str">
-        <v>Natalie Jane</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>CHICA 305</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>CHICA 305 - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H102" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>John Summit</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
       </c>
       <c r="L102" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>CHICA 305 - John Summit</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Jet Lag Mouth</v>
       </c>
       <c r="B103" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>3 weeks ago</v>
+        <v>Jet Lag Mouth - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>4:12</v>
+        <v>2:32</v>
       </c>
       <c r="H103" t="str">
-        <v>David Gilmour</v>
+        <v>In Color</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
       </c>
       <c r="L103" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Jet Lag Mouth - In Color</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B104" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>3 weeks ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>3:57</v>
+        <v>3:18</v>
       </c>
       <c r="H104" t="str">
-        <v>Far Caspian</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B105" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>3 weeks ago</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:34</v>
+        <v>2:47</v>
       </c>
       <c r="H105" t="str">
-        <v>Celine Dion</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L105" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B106" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>3 weeks ago</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G106" t="str">
-        <v>3:48</v>
+        <v>6:17</v>
       </c>
       <c r="H106" t="str">
-        <v>Harry Styles</v>
+        <v>RAYE</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L106" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>MARATHON</v>
       </c>
       <c r="B107" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>3 weeks ago</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>4:58</v>
+        <v>2:49</v>
       </c>
       <c r="H107" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Becky G</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L107" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B108" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>3 weeks ago</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:33</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Ellise</v>
+        <v>John Summit</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L108" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B109" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>3 weeks ago</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>4:56</v>
+        <v>3:34</v>
       </c>
       <c r="H109" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>CHICA 305</v>
+        <v>FATHER</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>CHICA 305 - Single</v>
+        <v>BULLY</v>
       </c>
       <c r="G110" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>Kanye West</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L110" t="str">
-        <v>CHICA 305 - John Summit</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>Lose Control</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>ADL</v>
       </c>
       <c r="G111" t="str">
-        <v>2:32</v>
+        <v>2:39</v>
       </c>
       <c r="H111" t="str">
-        <v>In Color</v>
+        <v>Yeat</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L111" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Days We Left Behind</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Zavier</v>
       </c>
       <c r="G112" t="str">
-        <v>3:18</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>Paul McCartney</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L112" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G113" t="str">
-        <v>2:47</v>
+        <v>2:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Miley Cyrus</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L113" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>Sideways</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G114" t="str">
-        <v>6:17</v>
+        <v>3:12</v>
       </c>
       <c r="H114" t="str">
-        <v>RAYE</v>
+        <v>ZAYN</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L114" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>MARATHON</v>
+        <v>Automatic</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>MARATHON - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G115" t="str">
-        <v>2:49</v>
+        <v>2:57</v>
       </c>
       <c r="H115" t="str">
-        <v>Becky G</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L115" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ALL THE TIME</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G116" t="str">
-        <v>3:00</v>
+        <v>3:34</v>
       </c>
       <c r="H116" t="str">
-        <v>John Summit</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L116" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Sucker For Love</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Sexistential</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G117" t="str">
-        <v>3:34</v>
+        <v>1:37</v>
       </c>
       <c r="H117" t="str">
-        <v>Robyn</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L117" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>FATHER</v>
+        <v>prom queen</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>BULLY</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:49</v>
+        <v>2:43</v>
       </c>
       <c r="H118" t="str">
-        <v>Kanye West</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L118" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Lose Control</v>
+        <v>Back Home</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ADL</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G119" t="str">
-        <v>2:39</v>
+        <v>1:36</v>
       </c>
       <c r="H119" t="str">
-        <v>Yeat</v>
+        <v>MIKE</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L119" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Zavier</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:44</v>
+        <v>3:26</v>
       </c>
       <c r="H120" t="str">
-        <v>Fetty Wap</v>
+        <v>J Balvin</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L120" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>WAGWAN</v>
+        <v>Phoenix</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:07</v>
+        <v>2:24</v>
       </c>
       <c r="H121" t="str">
-        <v>Central Cee</v>
+        <v>Marshmello</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L121" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Sideways</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>KONNAKOL</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:12</v>
+        <v>2:56</v>
       </c>
       <c r="H122" t="str">
-        <v>ZAYN</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L122" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Automatic</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Superbloom</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:57</v>
+        <v>3:36</v>
       </c>
       <c r="H123" t="str">
-        <v>Jessie Ware</v>
+        <v>Eli</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L123" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tractor Beam</v>
+        <v>Lonely</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ricochet</v>
+        <v>Ö</v>
       </c>
       <c r="G124" t="str">
-        <v>3:34</v>
+        <v>2:58</v>
       </c>
       <c r="H124" t="str">
-        <v>Snail Mail</v>
+        <v>Fcukers</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L124" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Home on the Range</v>
+        <v>Back in Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>1:37</v>
+        <v>3:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L125" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>prom queen</v>
+        <v>Sideways</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>prom queen - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G126" t="str">
-        <v>2:43</v>
+        <v>3:55</v>
       </c>
       <c r="H126" t="str">
-        <v>Amelia Moore</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L126" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Back Home</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Honora</v>
       </c>
       <c r="G127" t="str">
-        <v>1:36</v>
+        <v>4:22</v>
       </c>
       <c r="H127" t="str">
-        <v>MIKE</v>
+        <v>Flea</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L127" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Pal Agua</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Pal Agua - Single</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>J Balvin</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L128" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Phoenix</v>
+        <v>Shame (feat. BunnaB)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Phoenix - Single</v>
+        <v>Shame (feat. BunnaB) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:24</v>
+        <v>3:02</v>
       </c>
       <c r="H129" t="str">
-        <v>Marshmello</v>
+        <v>Honey Bxby</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
       </c>
       <c r="L129" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Shame (feat. BunnaB) - Honey Bxby</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G130" t="str">
-        <v>2:56</v>
+        <v>4:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Ne-Yo</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L130" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Feel Your Rain</v>
+        <v>wasteland</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:36</v>
+        <v>3:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Eli</v>
+        <v>Yuna</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L131" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Lonely</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Ö</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G132" t="str">
-        <v>2:58</v>
+        <v>2:31</v>
       </c>
       <c r="H132" t="str">
-        <v>Fcukers</v>
+        <v>Artemas</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L132" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Back in Love</v>
+        <v>Por LA</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Back in Love - Single</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G133" t="str">
-        <v>3:14</v>
+        <v>2:19</v>
       </c>
       <c r="H133" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L133" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Sideways</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Whatever's Clever!</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G134" t="str">
-        <v>3:55</v>
+        <v>4:14</v>
       </c>
       <c r="H134" t="str">
-        <v>Charlie Puth</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L134" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Honora</v>
+        <v>Broken View</v>
       </c>
       <c r="G135" t="str">
-        <v>4:22</v>
+        <v>4:18</v>
       </c>
       <c r="H135" t="str">
-        <v>Flea</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L135" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>2:54</v>
       </c>
       <c r="H136" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L136" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:02</v>
+        <v>2:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Honey Bxby</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L137" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>One Thing At A Time</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Creature of Habit</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G138" t="str">
-        <v>4:42</v>
+        <v>3:17</v>
       </c>
       <c r="H138" t="str">
-        <v>Courtney Barnett</v>
+        <v>ERNEST</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L138" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>wasteland</v>
+        <v>Special</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>wasteland - Single</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G139" t="str">
-        <v>3:05</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>Yuna</v>
+        <v>Elmiene</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L139" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>getting up to no good</v>
+        <v>CANDY</v>
       </c>
       <c r="G140" t="str">
-        <v>2:31</v>
+        <v>2:52</v>
       </c>
       <c r="H140" t="str">
-        <v>Artemas</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L140" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Por LA</v>
+        <v>STAY</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>TODO Ø NADA</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:19</v>
+        <v>3:06</v>
       </c>
       <c r="H141" t="str">
-        <v>Linea Personal</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L141" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>You Lead Me</v>
+        <v>Unglued</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G142" t="str">
-        <v>4:14</v>
+        <v>3:54</v>
       </c>
       <c r="H142" t="str">
-        <v>Lauren Daigle</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L142" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Just A Kid</v>
+        <v>Ritual</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Broken View</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:18</v>
+        <v>3:01</v>
       </c>
       <c r="H143" t="str">
-        <v>Sam Barber</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L143" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Country And She Knows It</v>
+        <v>The Best</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G144" t="str">
-        <v>2:54</v>
+        <v>3:48</v>
       </c>
       <c r="H144" t="str">
-        <v>Luke Bryan</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L144" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Smile</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:35</v>
+        <v>3:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Thomas Rhett</v>
+        <v>Two Shell</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L145" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Deep Blue</v>
+        <v>Duro</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Deep Blue</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:17</v>
+        <v>3:05</v>
       </c>
       <c r="H146" t="str">
-        <v>ERNEST</v>
+        <v>Skrillex</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L146" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Special</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>sounds for someone</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G147" t="str">
-        <v>2:49</v>
+        <v>2:58</v>
       </c>
       <c r="H147" t="str">
-        <v>Elmiene</v>
+        <v>Sublime</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L147" t="str">
-        <v>Special - Elmiene</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Heart Attack</v>
+        <v>Carousel</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>CANDY</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G148" t="str">
-        <v>2:52</v>
+        <v>3:36</v>
       </c>
       <c r="H148" t="str">
-        <v>Justine Skye</v>
+        <v>Cannons</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L148" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>STAY</v>
+        <v>Mercy</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>STAY - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:06</v>
+        <v>3:49</v>
       </c>
       <c r="H149" t="str">
-        <v>Stray Kids</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L149" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Unglued</v>
+        <v>Palms</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Work of Heart</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:54</v>
+        <v>3:18</v>
       </c>
       <c r="H150" t="str">
-        <v>Flatland Cavalry</v>
+        <v>The Maine</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L150" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ritual</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ritual - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G151" t="str">
-        <v>3:01</v>
+        <v>5:28</v>
       </c>
       <c r="H151" t="str">
-        <v>Icona Pop</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L151" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>The Best</v>
+        <v>Danger</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:48</v>
+        <v>2:19</v>
       </c>
       <c r="H152" t="str">
-        <v>Conan Gray</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L152" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Smile</v>
+        <v>Icarus</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Smile - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:50</v>
+        <v>4:25</v>
       </c>
       <c r="H153" t="str">
-        <v>Two Shell</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L153" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Duro</v>
+        <v>idk idk</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Duro - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:05</v>
+        <v>2:26</v>
       </c>
       <c r="H154" t="str">
-        <v>Skrillex</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L154" t="str">
-        <v>Duro - Skrillex</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Tonight</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:58</v>
+        <v>2:25</v>
       </c>
       <c r="H155" t="str">
-        <v>Sublime</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L155" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Carousel</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Everything Glows</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G156" t="str">
-        <v>3:36</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>Cannons</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L156" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Mercy</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Mercy - Single</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>3:49</v>
+        <v>2:45</v>
       </c>
       <c r="H157" t="str">
-        <v>PRESIDENT</v>
+        <v>BIA</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L157" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Palms</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Palms - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G158" t="str">
-        <v>3:18</v>
+        <v>3:33</v>
       </c>
       <c r="H158" t="str">
-        <v>The Maine</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L158" t="str">
-        <v>Palms - The Maine</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Ozzy's Song</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G159" t="str">
-        <v>5:28</v>
+        <v>3:44</v>
       </c>
       <c r="H159" t="str">
-        <v>Black Label Society</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L159" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Danger</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Danger - Single</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>2:19</v>
+        <v>2:41</v>
       </c>
       <c r="H160" t="str">
-        <v>Nia Archives</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L160" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Icarus</v>
+        <v>R3verse</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Icarus - Single</v>
+        <v>takeaways</v>
       </c>
       <c r="G161" t="str">
-        <v>4:25</v>
+        <v>3:31</v>
       </c>
       <c r="H161" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Medium Build</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L161" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>idk idk</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>idk idk - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G162" t="str">
-        <v>2:26</v>
+        <v>2:32</v>
       </c>
       <c r="H162" t="str">
-        <v>Jim Legxacy</v>
+        <v>MIKE</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L162" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Tonight</v>
+        <v>heart of gold</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Tonight - Single</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:25</v>
+        <v>2:51</v>
       </c>
       <c r="H163" t="str">
-        <v>girlsweetvoiced</v>
+        <v>kai devega</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L163" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Switcheroo</v>
+        <v>Skeletor</v>
       </c>
       <c r="G164" t="str">
-        <v>3:44</v>
+        <v>4:21</v>
       </c>
       <c r="H164" t="str">
-        <v>Gelli Haha</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L164" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>Dream House</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:45</v>
+        <v>2:54</v>
       </c>
       <c r="H165" t="str">
-        <v>BIA</v>
+        <v>Empress Of</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L165" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>this girl wants everything</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:33</v>
+        <v>2:51</v>
       </c>
       <c r="H166" t="str">
-        <v>Isaia Huron</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L166" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:44</v>
+        <v>2:37</v>
       </c>
       <c r="H167" t="str">
-        <v>Slayyyter</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L167" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Deep Water - EP</v>
+        <v>Forever Now</v>
       </c>
       <c r="G168" t="str">
-        <v>2:41</v>
+        <v>4:05</v>
       </c>
       <c r="H168" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L168" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>R3verse</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>takeaways</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>3:31</v>
+        <v>3:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Medium Build</v>
+        <v>Benny G</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L169" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:32</v>
+        <v>3:03</v>
       </c>
       <c r="H170" t="str">
-        <v>MIKE</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L170" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>heart of gold</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>heart of gold - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>2:51</v>
+        <v>4:19</v>
       </c>
       <c r="H171" t="str">
-        <v>kai devega</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L171" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Breaking Down</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Skeletor</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:21</v>
+        <v>2:10</v>
       </c>
       <c r="H172" t="str">
-        <v>Chief Keef</v>
+        <v>WesGhost</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L172" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Dream House</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Dream House - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:54</v>
+        <v>3:17</v>
       </c>
       <c r="H173" t="str">
-        <v>Empress Of</v>
+        <v>GERD</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L173" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Baby Blue</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:51</v>
+        <v>3:21</v>
       </c>
       <c r="H174" t="str">
-        <v>Cody Simpson</v>
+        <v>Prospa</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L174" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:37</v>
+        <v>2:51</v>
       </c>
       <c r="H175" t="str">
-        <v>MEDUZA</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L175" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>Breathe</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Forever Now</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:05</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>Switchfoot</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L176" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>xs</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>xs - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:46</v>
+        <v>3:19</v>
       </c>
       <c r="H177" t="str">
-        <v>Benny G</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L177" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Sail</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G178" t="str">
-        <v>3:03</v>
+        <v>4:54</v>
       </c>
       <c r="H178" t="str">
-        <v>Eric Bellinger</v>
+        <v>Future Islands</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L178" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Dreaming</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G179" t="str">
-        <v>4:19</v>
+        <v>3:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Anish Kumar</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L179" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>GASLIGHT</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G180" t="str">
-        <v>2:10</v>
+        <v>2:39</v>
       </c>
       <c r="H180" t="str">
-        <v>WesGhost</v>
+        <v>Armanii</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L180" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Truth To Be Told</v>
+        <v>La Opinión</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G181" t="str">
-        <v>3:17</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>GERD</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L181" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Free Your Mind</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:21</v>
+        <v>3:24</v>
       </c>
       <c r="H182" t="str">
-        <v>Prospa</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L182" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Down To The Bone</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:51</v>
+        <v>2:43</v>
       </c>
       <c r="H183" t="str">
-        <v>Josh Baker</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L183" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Breathe</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Breathe - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>2:16</v>
       </c>
       <c r="H184" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L184" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>xs</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>xs - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:19</v>
+        <v>2:56</v>
       </c>
       <c r="H185" t="str">
-        <v>Ashley Cooke</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L185" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Sail</v>
+        <v>Me Neither</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G186" t="str">
-        <v>4:54</v>
+        <v>3:32</v>
       </c>
       <c r="H186" t="str">
-        <v>Future Islands</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L186" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Dreaming</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Dear Nashville</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G187" t="str">
-        <v>3:33</v>
+        <v>2:48</v>
       </c>
       <c r="H187" t="str">
-        <v>Ashley Monroe</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L187" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>NEW TINGZ</v>
+        <v>Wonder</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:39</v>
+        <v>3:48</v>
       </c>
       <c r="H188" t="str">
-        <v>Armanii</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L188" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>La Opinión</v>
+        <v>ICU</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Mis Compas El Final</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:23</v>
+        <v>2:53</v>
       </c>
       <c r="H189" t="str">
-        <v>Joss Favela</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L189" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>qué ves en mí?</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G190" t="str">
-        <v>3:24</v>
+        <v>2:45</v>
       </c>
       <c r="H190" t="str">
-        <v>Paloma Morphy</v>
+        <v>Jozzy</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L190" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>Waiting Room (feat. Jordan Ward)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Waiting Room (feat. Jordan Ward) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:43</v>
+        <v>3:21</v>
       </c>
       <c r="H191" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
       </c>
       <c r="L191" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>TUTUTU</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G192" t="str">
-        <v>2:16</v>
+        <v>4:02</v>
       </c>
       <c r="H192" t="str">
-        <v>ELENA ROSE</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L192" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:56</v>
+        <v>3:51</v>
       </c>
       <c r="H193" t="str">
-        <v>2'Live Bre</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L193" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Me Neither</v>
+        <v>Delicately</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:32</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>Ty Myers</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L194" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Cole Palmer</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Solid Ground</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:48</v>
+        <v>3:27</v>
       </c>
       <c r="H195" t="str">
-        <v>Limoblaze</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L195" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Wonder</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Wonder - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G196" t="str">
-        <v>3:48</v>
+        <v>6:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Meeks Carter</v>
+        <v>José González</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L196" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>ICU</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>ICU - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G197" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H197" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L197" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Daisy</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:45</v>
+        <v>3:02</v>
       </c>
       <c r="H198" t="str">
-        <v>Jozzy</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L198" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Waiting Room (feat. Jordan Ward)</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G199" t="str">
-        <v>3:21</v>
+        <v>3:57</v>
       </c>
       <c r="H199" t="str">
-        <v>Jenevieve</v>
+        <v>james K</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L199" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Rise</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:02</v>
+        <v>2:45</v>
       </c>
       <c r="H200" t="str">
-        <v>Melissa Etheridge</v>
+        <v>MAVICA</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L200" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Roll On Thru</v>
+        <v>Fort</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:51</v>
+        <v>2:27</v>
       </c>
       <c r="H201" t="str">
-        <v>Hayden Everett</v>
+        <v>Lamb</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L201" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Delicately</v>
+        <v>SAME LA</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-01</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Delicately - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:20</v>
+        <v>3:44</v>
       </c>
       <c r="H202" t="str">
-        <v>Andrea Bejar</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L202" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>One Of Those Things</v>
+        <v>Working On It</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-01</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:27</v>
+        <v>3:06</v>
       </c>
       <c r="H203" t="str">
-        <v>Lucy Clearwater</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L203" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>For Every Dusk</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-01</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>6:04</v>
+        <v>4:03</v>
       </c>
       <c r="H204" t="str">
-        <v>José González</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L204" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>I'll Wait</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D205" t="str">
         <v>2026-04-01</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:33</v>
+        <v>3:26</v>
       </c>
       <c r="H205" t="str">
-        <v>Buzzy Lee</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L205" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Daisy</v>
+        <v>Simple Things</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D206" t="str">
         <v>2026-04-01</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Daisy - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:02</v>
+        <v>3:46</v>
       </c>
       <c r="H206" t="str">
-        <v>Lola Blue</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L206" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Want It Back</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D207" t="str">
         <v>2026-04-01</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Friend Remixes</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:57</v>
+        <v>3:27</v>
       </c>
       <c r="H207" t="str">
-        <v>james K</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L207" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Bite Down</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D208" t="str">
         <v>2026-04-01</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Perdidos - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>2:45</v>
+        <v>3:36</v>
       </c>
       <c r="H208" t="str">
-        <v>MAVICA</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L208" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Fort</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D209" t="str">
         <v>2026-04-01</v>
@@ -8317,36 +8317,36 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Fort - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G209" t="str">
-        <v>2:27</v>
+        <v>5:42</v>
       </c>
       <c r="H209" t="str">
-        <v>Lamb</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L209" t="str">
-        <v>Fort - Lamb</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>SAME LA</v>
+        <v>Demons</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D210" t="str">
         <v>2026-04-01</v>
@@ -8355,36 +8355,36 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>SAME LA - Single</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G210" t="str">
-        <v>3:44</v>
+        <v>2:42</v>
       </c>
       <c r="H210" t="str">
-        <v>Tiffany Day</v>
+        <v>Anella</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L210" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Working On It</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D211" t="str">
         <v>2026-04-01</v>
@@ -8393,36 +8393,36 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Working On It - Single</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G211" t="str">
-        <v>3:06</v>
+        <v>3:35</v>
       </c>
       <c r="H211" t="str">
-        <v>Arthur Hill</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L211" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>spring cleaning</v>
+        <v>Fire Marengo</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D212" t="str">
         <v>2026-04-01</v>
@@ -8431,36 +8431,36 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
       </c>
       <c r="G212" t="str">
-        <v>4:03</v>
+        <v>3:49</v>
       </c>
       <c r="H212" t="str">
-        <v>Ethan Regan</v>
+        <v>Enslaved</v>
       </c>
       <c r="I212" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
       </c>
       <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
       </c>
       <c r="L212" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Fire Marengo - Enslaved</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Just Drivin'</v>
+        <v>Close to the Bone</v>
       </c>
       <c r="B213" t="str">
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D213" t="str">
         <v>2026-04-01</v>
@@ -8469,334 +8469,30 @@
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G213" t="str">
-        <v>3:26</v>
+        <v>4:09</v>
       </c>
       <c r="H213" t="str">
-        <v>Presley Haile</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I213" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
       <c r="L213" t="str">
-        <v>Just Drivin' - Presley Haile</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Simple Things</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>Simple Things - Single</v>
-      </c>
-      <c r="G214" t="str">
-        <v>3:46</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Evening Elephants</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
-      </c>
-      <c r="L214" t="str">
-        <v>Simple Things - Evening Elephants</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Want It Back</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Want It Back - Single</v>
-      </c>
-      <c r="G215" t="str">
-        <v>3:27</v>
-      </c>
-      <c r="H215" t="str">
-        <v>Giant Rooks</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
-      </c>
-      <c r="L215" t="str">
-        <v>Want It Back - Giant Rooks</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Bite Down</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>Bite Down - Single</v>
-      </c>
-      <c r="G216" t="str">
-        <v>3:36</v>
-      </c>
-      <c r="H216" t="str">
-        <v>Anna Sofia</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
-      </c>
-      <c r="L216" t="str">
-        <v>Bite Down - Anna Sofia</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
-      </c>
-      <c r="B217" t="str">
-        <v/>
-      </c>
-      <c r="C217" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
-      </c>
-      <c r="D217" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v>Grand Serpent Rising</v>
-      </c>
-      <c r="G217" t="str">
-        <v>5:42</v>
-      </c>
-      <c r="H217" t="str">
-        <v>Dimmu Borgir</v>
-      </c>
-      <c r="I217" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J217" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
-      </c>
-      <c r="K217" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
-      </c>
-      <c r="L217" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>Demons</v>
-      </c>
-      <c r="B218" t="str">
-        <v/>
-      </c>
-      <c r="C218" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
-      </c>
-      <c r="D218" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E218" t="str">
-        <v/>
-      </c>
-      <c r="F218" t="str">
-        <v>Ask Me How I’ve Been</v>
-      </c>
-      <c r="G218" t="str">
-        <v>2:42</v>
-      </c>
-      <c r="H218" t="str">
-        <v>Anella</v>
-      </c>
-      <c r="I218" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J218" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
-      </c>
-      <c r="K218" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
-      </c>
-      <c r="L218" t="str">
-        <v>Demons - Anella</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>Es brennt...</v>
-      </c>
-      <c r="B219" t="str">
-        <v/>
-      </c>
-      <c r="C219" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
-      </c>
-      <c r="D219" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E219" t="str">
-        <v/>
-      </c>
-      <c r="F219" t="str">
-        <v>Es brennt... - Single</v>
-      </c>
-      <c r="G219" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H219" t="str">
-        <v>Till Lindemann</v>
-      </c>
-      <c r="I219" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J219" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
-      </c>
-      <c r="K219" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
-      </c>
-      <c r="L219" t="str">
-        <v>Es brennt... - Till Lindemann</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>Fire Marengo</v>
-      </c>
-      <c r="B220" t="str">
-        <v/>
-      </c>
-      <c r="C220" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
-      </c>
-      <c r="D220" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E220" t="str">
-        <v/>
-      </c>
-      <c r="F220" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
-      </c>
-      <c r="G220" t="str">
-        <v>3:49</v>
-      </c>
-      <c r="H220" t="str">
-        <v>Enslaved</v>
-      </c>
-      <c r="I220" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J220" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
-      </c>
-      <c r="K220" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
-      </c>
-      <c r="L220" t="str">
-        <v>Fire Marengo - Enslaved</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>Close to the Bone</v>
-      </c>
-      <c r="B221" t="str">
-        <v/>
-      </c>
-      <c r="C221" t="str">
-        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
-      </c>
-      <c r="D221" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E221" t="str">
-        <v/>
-      </c>
-      <c r="F221" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G221" t="str">
-        <v>4:09</v>
-      </c>
-      <c r="H221" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I221" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J221" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K221" t="str">
-        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
-      </c>
-      <c r="L221" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L221"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -1351,7 +1351,7 @@
         <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B26" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:56</v>

--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L213"/>
+  <dimension ref="A1:L214"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>תמר אופיר – בדמייך חיי</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>2026-04-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%91%d7%93%d7%9e%d7%99%d7%99%d7%9a-%d7%97%d7%99%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>השיר בדמייך חיי בביצועה של תמר אופיר, המבוסס על הפסוקים “ואעבור עלייך…” מתוך ספר יחזקאל (שנכנסו גם לנוסח ההגדה), הוא דוגמה יפה לשילוב בין טקסט מקראי טעון לבין פרשנות מוזיקלית עכשווית, רגשית ואינטימית. המילים מהוות ביטוי עוצמתי לקידוש החיים מתוך</v>
       </c>
       <c r="G2" t="str">
-        <v>3:56</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>תמר אופיר – בדמייך חיי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:50</v>
+        <v>3:56</v>
       </c>
       <c r="H3" t="str">
-        <v>Miley Cyrus</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:42</v>
+        <v>2:50</v>
       </c>
       <c r="H4" t="str">
-        <v>Conan Gray</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:16</v>
+        <v>3:42</v>
       </c>
       <c r="H5" t="str">
-        <v>Charlie Puth</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:08</v>
+        <v>2:16</v>
       </c>
       <c r="H6" t="str">
-        <v>Kylie Morgan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:38</v>
+        <v>3:08</v>
       </c>
       <c r="H7" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:01</v>
+        <v>3:38</v>
       </c>
       <c r="H8" t="str">
-        <v>Angelina Mango</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:59</v>
+        <v>3:01</v>
       </c>
       <c r="H9" t="str">
-        <v>Julio Iglesias</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B10" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -758,10 +758,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:59</v>
+        <v>3:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Loreen</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -796,10 +796,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:58</v>
+        <v>2:59</v>
       </c>
       <c r="H11" t="str">
-        <v>Jessie Ware</v>
+        <v>Loreen</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B12" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -834,10 +834,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:49</v>
+        <v>2:58</v>
       </c>
       <c r="H12" t="str">
-        <v>Holly Humberstone</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:22</v>
+        <v>3:49</v>
       </c>
       <c r="H13" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B14" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -910,10 +910,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:50</v>
+        <v>3:22</v>
       </c>
       <c r="H14" t="str">
-        <v>Ella Langley</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B15" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -948,10 +948,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>6:43</v>
+        <v>3:50</v>
       </c>
       <c r="H15" t="str">
-        <v>David Gilmour</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B16" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -986,10 +986,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:52</v>
+        <v>6:43</v>
       </c>
       <c r="H16" t="str">
-        <v>Eagles</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B17" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1024,10 +1024,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:13</v>
+        <v>4:52</v>
       </c>
       <c r="H17" t="str">
-        <v>Moody Joody</v>
+        <v>Eagles</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B18" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:28</v>
+        <v>3:13</v>
       </c>
       <c r="H18" t="str">
-        <v>Jackson Dean</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H19" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:00</v>
+        <v>3:01</v>
       </c>
       <c r="H20" t="str">
-        <v>Madison Cunningham</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B21" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:35</v>
+        <v>4:00</v>
       </c>
       <c r="H21" t="str">
-        <v>mary in the junkyard</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B22" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:01</v>
+        <v>5:35</v>
       </c>
       <c r="H22" t="str">
-        <v>Adam Sanders</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:40</v>
+        <v>3:01</v>
       </c>
       <c r="H23" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B24" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:25</v>
+        <v>3:40</v>
       </c>
       <c r="H24" t="str">
-        <v>twocolors</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:42</v>
+        <v>2:25</v>
       </c>
       <c r="H25" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>twocolors</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B26" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:56</v>
+        <v>3:42</v>
       </c>
       <c r="H26" t="str">
-        <v>Prince</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B27" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:12</v>
+        <v>3:56</v>
       </c>
       <c r="H27" t="str">
-        <v>RAYE</v>
+        <v>Prince</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:30</v>
+        <v>5:12</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>RAYE</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B29" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H29" t="str">
-        <v>Pentatonix</v>
+        <v>The Warning</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:33</v>
+        <v>3:18</v>
       </c>
       <c r="H30" t="str">
-        <v>Tenille Townes</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1556,10 +1556,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:53</v>
+        <v>3:33</v>
       </c>
       <c r="H31" t="str">
-        <v>Jessie Ware</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:37</v>
+        <v>5:53</v>
       </c>
       <c r="H32" t="str">
-        <v>Niall Horan</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B33" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:26</v>
+        <v>2:37</v>
       </c>
       <c r="H33" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B34" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:40</v>
+        <v>2:26</v>
       </c>
       <c r="H34" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:30</v>
+        <v>2:40</v>
       </c>
       <c r="H35" t="str">
-        <v>Jackson Dean</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B36" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:02</v>
+        <v>3:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Foo Fighters</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:40</v>
+        <v>4:02</v>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:22</v>
+        <v>3:40</v>
       </c>
       <c r="H38" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:47</v>
+        <v>2:22</v>
       </c>
       <c r="H39" t="str">
-        <v>Ella Langley</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:39</v>
+        <v>3:47</v>
       </c>
       <c r="H40" t="str">
-        <v>Cannons</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B41" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:10</v>
+        <v>3:39</v>
       </c>
       <c r="H41" t="str">
-        <v>Luke Combs</v>
+        <v>Cannons</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:47</v>
+        <v>4:10</v>
       </c>
       <c r="H42" t="str">
-        <v>Nessa Barrett</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B43" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:14</v>
+        <v>4:47</v>
       </c>
       <c r="H43" t="str">
-        <v>aron!</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B44" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:00</v>
+        <v>2:14</v>
       </c>
       <c r="H44" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>aron!</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B45" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:56</v>
+        <v>4:00</v>
       </c>
       <c r="H45" t="str">
-        <v>DMA'S</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2126,10 +2126,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:17</v>
+        <v>3:56</v>
       </c>
       <c r="H46" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>DMA'S</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:17</v>
       </c>
       <c r="H47" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,21 +2179,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2202,10 +2202,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H48" t="str">
-        <v>Nick Carter</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B49" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,10 +2240,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H49" t="str">
-        <v>Carly Pearce</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,21 +2255,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>3:38</v>
       </c>
       <c r="H50" t="str">
-        <v>OneRepublic</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,21 +2293,21 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2316,10 +2316,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:57</v>
+        <v>4:11</v>
       </c>
       <c r="H51" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,21 +2331,21 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2354,10 +2354,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:47</v>
+        <v>2:57</v>
       </c>
       <c r="H52" t="str">
-        <v>Armin van Buuren</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,21 +2369,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2392,10 +2392,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>7:10</v>
+        <v>3:47</v>
       </c>
       <c r="H53" t="str">
-        <v>David Gilmour</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:06</v>
+        <v>7:10</v>
       </c>
       <c r="H54" t="str">
-        <v>Grace Enger</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:05</v>
+        <v>3:06</v>
       </c>
       <c r="H55" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:12</v>
+        <v>3:05</v>
       </c>
       <c r="H56" t="str">
-        <v>Freya Ridings</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>9:11</v>
+        <v>3:12</v>
       </c>
       <c r="H57" t="str">
-        <v>David Gilmour</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:49</v>
+        <v>9:11</v>
       </c>
       <c r="H58" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:28</v>
+        <v>3:49</v>
       </c>
       <c r="H59" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:31</v>
+        <v>3:28</v>
       </c>
       <c r="H60" t="str">
-        <v>Martin Garrix</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:11</v>
+        <v>3:31</v>
       </c>
       <c r="H61" t="str">
-        <v>Baby Queen</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,21 +2711,21 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:27</v>
+        <v>3:11</v>
       </c>
       <c r="H62" t="str">
-        <v>HAUSER</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H63" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,21 +2787,21 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:50</v>
+        <v>3:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:51</v>
+        <v>2:50</v>
       </c>
       <c r="H65" t="str">
-        <v>Rick Astley</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:39</v>
+        <v>3:51</v>
       </c>
       <c r="H66" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:08</v>
+        <v>2:39</v>
       </c>
       <c r="H67" t="str">
-        <v>Jessie J</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,21 +2939,21 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:46</v>
+        <v>5:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Bishop Briggs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:42</v>
+        <v>3:46</v>
       </c>
       <c r="H69" t="str">
-        <v>Dean Lewis</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:31</v>
+        <v>2:42</v>
       </c>
       <c r="H70" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:14</v>
+        <v>2:31</v>
       </c>
       <c r="H71" t="str">
-        <v>Luke Combs</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,21 +3091,21 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H72" t="str">
-        <v>Allison Russell</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:43</v>
+        <v>3:22</v>
       </c>
       <c r="H73" t="str">
-        <v>We Three</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:54</v>
+        <v>3:43</v>
       </c>
       <c r="H74" t="str">
-        <v>paris jackson</v>
+        <v>We Three</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H75" t="str">
-        <v>Kane Brown</v>
+        <v>paris jackson</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:37</v>
+        <v>2:46</v>
       </c>
       <c r="H76" t="str">
-        <v>Lainey Wilson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:57</v>
+        <v>3:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Malcolm Todd</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:38</v>
+        <v>2:57</v>
       </c>
       <c r="H78" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:29</v>
+        <v>3:38</v>
       </c>
       <c r="H79" t="str">
-        <v>Kungs</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,21 +3395,21 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:28</v>
+        <v>4:29</v>
       </c>
       <c r="H80" t="str">
-        <v>Sunday (1994)</v>
+        <v>Kungs</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:26</v>
+        <v>4:28</v>
       </c>
       <c r="H81" t="str">
-        <v>aron!</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:51</v>
+        <v>3:26</v>
       </c>
       <c r="H82" t="str">
-        <v>Colinstoughmusic</v>
+        <v>aron!</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:49</v>
+        <v>3:51</v>
       </c>
       <c r="H83" t="str">
-        <v>Sunday (1994)</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:16</v>
+        <v>2:49</v>
       </c>
       <c r="H84" t="str">
-        <v>Owen Riegling</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3611,7 +3611,7 @@
         <v>4:16</v>
       </c>
       <c r="H85" t="str">
-        <v>LANY</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H86" t="str">
-        <v>Maverick Sabre</v>
+        <v>LANY</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:50</v>
+        <v>3:25</v>
       </c>
       <c r="H87" t="str">
-        <v>Amanda Jordan</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>2:50</v>
       </c>
       <c r="H88" t="str">
-        <v>Beabadoobee</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:58</v>
+        <v>3:57</v>
       </c>
       <c r="H89" t="str">
-        <v>Spacey Jane</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:25</v>
+        <v>3:58</v>
       </c>
       <c r="H90" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:09</v>
+        <v>3:25</v>
       </c>
       <c r="H91" t="str">
-        <v>Mei Semones</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:08</v>
+        <v>4:09</v>
       </c>
       <c r="H92" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:57</v>
+        <v>2:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Natalie Jane</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:13</v>
+        <v>2:57</v>
       </c>
       <c r="H94" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H95" t="str">
-        <v>David Gilmour</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,21 +4003,21 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:57</v>
+        <v>4:12</v>
       </c>
       <c r="H96" t="str">
-        <v>Far Caspian</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,21 +4041,21 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:34</v>
+        <v>3:57</v>
       </c>
       <c r="H97" t="str">
-        <v>Celine Dion</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,21 +4079,21 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:48</v>
+        <v>3:34</v>
       </c>
       <c r="H98" t="str">
-        <v>Harry Styles</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:58</v>
+        <v>3:48</v>
       </c>
       <c r="H99" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:33</v>
+        <v>4:58</v>
       </c>
       <c r="H100" t="str">
-        <v>Ellise</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:56</v>
+        <v>2:33</v>
       </c>
       <c r="H101" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Ellise</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,4268 +4231,4306 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>CHICA 305</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>CHICA 305 - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:08</v>
+        <v>4:56</v>
       </c>
       <c r="H102" t="str">
-        <v>John Summit</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>CHICA 305 - John Summit</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>CHICA 305</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>CHICA 305 - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>2:32</v>
+        <v>3:08</v>
       </c>
       <c r="H103" t="str">
-        <v>In Color</v>
+        <v>John Summit</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
       </c>
       <c r="L103" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>CHICA 305 - John Summit</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Days We Left Behind</v>
+        <v>Jet Lag Mouth</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Jet Lag Mouth - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:18</v>
+        <v>2:32</v>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>In Color</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
       </c>
       <c r="L104" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Jet Lag Mouth - In Color</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G105" t="str">
-        <v>2:47</v>
+        <v>3:18</v>
       </c>
       <c r="H105" t="str">
-        <v>Miley Cyrus</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>6:17</v>
+        <v>2:47</v>
       </c>
       <c r="H106" t="str">
-        <v>RAYE</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L106" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>MARATHON</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>MARATHON - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G107" t="str">
-        <v>2:49</v>
+        <v>6:17</v>
       </c>
       <c r="H107" t="str">
-        <v>Becky G</v>
+        <v>RAYE</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L107" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ALL THE TIME</v>
+        <v>MARATHON</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>2:49</v>
       </c>
       <c r="H108" t="str">
-        <v>John Summit</v>
+        <v>Becky G</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L108" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Sucker For Love</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sexistential</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H109" t="str">
-        <v>Robyn</v>
+        <v>John Summit</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L109" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>FATHER</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>BULLY</v>
+        <v>Sexistential</v>
       </c>
       <c r="G110" t="str">
-        <v>2:49</v>
+        <v>3:34</v>
       </c>
       <c r="H110" t="str">
-        <v>Kanye West</v>
+        <v>Robyn</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L110" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Lose Control</v>
+        <v>FATHER</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ADL</v>
+        <v>BULLY</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>2:49</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>Kanye West</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L111" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>Lose Control</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Zavier</v>
+        <v>ADL</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>2:39</v>
       </c>
       <c r="H112" t="str">
-        <v>Fetty Wap</v>
+        <v>Yeat</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WAGWAN</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>Zavier</v>
       </c>
       <c r="G113" t="str">
-        <v>2:07</v>
+        <v>3:44</v>
       </c>
       <c r="H113" t="str">
-        <v>Central Cee</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L113" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sideways</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>KONNAKOL</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G114" t="str">
-        <v>3:12</v>
+        <v>2:07</v>
       </c>
       <c r="H114" t="str">
-        <v>ZAYN</v>
+        <v>Central Cee</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L114" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Automatic</v>
+        <v>Sideways</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Superbloom</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G115" t="str">
-        <v>2:57</v>
+        <v>3:12</v>
       </c>
       <c r="H115" t="str">
-        <v>Jessie Ware</v>
+        <v>ZAYN</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L115" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tractor Beam</v>
+        <v>Automatic</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ricochet</v>
+        <v>Superbloom</v>
       </c>
       <c r="G116" t="str">
-        <v>3:34</v>
+        <v>2:57</v>
       </c>
       <c r="H116" t="str">
-        <v>Snail Mail</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L116" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Home on the Range</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Ricochet</v>
       </c>
       <c r="G117" t="str">
-        <v>1:37</v>
+        <v>3:34</v>
       </c>
       <c r="H117" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L117" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>prom queen</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>prom queen - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G118" t="str">
-        <v>2:43</v>
+        <v>1:37</v>
       </c>
       <c r="H118" t="str">
-        <v>Amelia Moore</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L118" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Back Home</v>
+        <v>prom queen</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>1:36</v>
+        <v>2:43</v>
       </c>
       <c r="H119" t="str">
-        <v>MIKE</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L119" t="str">
-        <v>Back Home - MIKE</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Pal Agua</v>
+        <v>Back Home</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Pal Agua - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G120" t="str">
-        <v>3:26</v>
+        <v>1:36</v>
       </c>
       <c r="H120" t="str">
-        <v>J Balvin</v>
+        <v>MIKE</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L120" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Phoenix</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Phoenix - Single</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:24</v>
+        <v>3:26</v>
       </c>
       <c r="H121" t="str">
-        <v>Marshmello</v>
+        <v>J Balvin</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L121" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Phoenix</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:56</v>
+        <v>2:24</v>
       </c>
       <c r="H122" t="str">
-        <v>Ne-Yo</v>
+        <v>Marshmello</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L122" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Feel Your Rain</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:36</v>
+        <v>2:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Eli</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L123" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Lonely</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ö</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H124" t="str">
-        <v>Fcukers</v>
+        <v>Eli</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L124" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Back in Love</v>
+        <v>Lonely</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Back in Love - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G125" t="str">
-        <v>3:14</v>
+        <v>2:58</v>
       </c>
       <c r="H125" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Fcukers</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L125" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Sideways</v>
+        <v>Back in Love</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:55</v>
+        <v>3:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Charlie Puth</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L126" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>Sideways</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Honora</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G127" t="str">
-        <v>4:22</v>
+        <v>3:55</v>
       </c>
       <c r="H127" t="str">
-        <v>Flea</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L127" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>4:22</v>
       </c>
       <c r="H128" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Flea</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Shame (feat. BunnaB)</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/shame-feat-bunnab/1887698916</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Shame (feat. BunnaB) - Single</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:02</v>
+        <v>2:58</v>
       </c>
       <c r="H129" t="str">
-        <v>Honey Bxby</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/honey-bxby/1482497204</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/shame-feat-bunnab/1887698914</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L129" t="str">
-        <v>Shame (feat. BunnaB) - Honey Bxby</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>One Thing At A Time</v>
+        <v>Shame</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/shame/1887698916</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Creature of Habit</v>
+        <v>Shame - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:42</v>
+        <v>3:02</v>
       </c>
       <c r="H130" t="str">
-        <v>Courtney Barnett</v>
+        <v>BunnaB</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/bunnab/1695734940</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/shame/1887698914</v>
       </c>
       <c r="L130" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>Shame - BunnaB</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>wasteland</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>wasteland - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G131" t="str">
-        <v>3:05</v>
+        <v>4:42</v>
       </c>
       <c r="H131" t="str">
-        <v>Yuna</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L131" t="str">
-        <v>wasteland - Yuna</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>wasteland</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>getting up to no good</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:31</v>
+        <v>3:05</v>
       </c>
       <c r="H132" t="str">
-        <v>Artemas</v>
+        <v>Yuna</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L132" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Por LA</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>TODO Ø NADA</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G133" t="str">
-        <v>2:19</v>
+        <v>2:31</v>
       </c>
       <c r="H133" t="str">
-        <v>Linea Personal</v>
+        <v>Artemas</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L133" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>You Lead Me</v>
+        <v>Por LA</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G134" t="str">
-        <v>4:14</v>
+        <v>2:19</v>
       </c>
       <c r="H134" t="str">
-        <v>Lauren Daigle</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L134" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Just A Kid</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Broken View</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G135" t="str">
-        <v>4:18</v>
+        <v>4:14</v>
       </c>
       <c r="H135" t="str">
-        <v>Sam Barber</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L135" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Country And She Knows It</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G136" t="str">
-        <v>2:54</v>
+        <v>4:18</v>
       </c>
       <c r="H136" t="str">
-        <v>Luke Bryan</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L136" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:35</v>
+        <v>2:54</v>
       </c>
       <c r="H137" t="str">
-        <v>Thomas Rhett</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L137" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Deep Blue</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Deep Blue</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:17</v>
+        <v>2:35</v>
       </c>
       <c r="H138" t="str">
-        <v>ERNEST</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L138" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Special</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>sounds for someone</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G139" t="str">
-        <v>2:49</v>
+        <v>3:17</v>
       </c>
       <c r="H139" t="str">
-        <v>Elmiene</v>
+        <v>ERNEST</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L139" t="str">
-        <v>Special - Elmiene</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Heart Attack</v>
+        <v>Special</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>CANDY</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G140" t="str">
-        <v>2:52</v>
+        <v>2:49</v>
       </c>
       <c r="H140" t="str">
-        <v>Justine Skye</v>
+        <v>Elmiene</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L140" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>STAY</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>STAY - Single</v>
+        <v>CANDY</v>
       </c>
       <c r="G141" t="str">
-        <v>3:06</v>
+        <v>2:52</v>
       </c>
       <c r="H141" t="str">
-        <v>Stray Kids</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L141" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Unglued</v>
+        <v>STAY</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Work of Heart</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:54</v>
+        <v>3:06</v>
       </c>
       <c r="H142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L142" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Ritual</v>
+        <v>Unglued</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Ritual - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G143" t="str">
-        <v>3:01</v>
+        <v>3:54</v>
       </c>
       <c r="H143" t="str">
-        <v>Icona Pop</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L143" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>The Best</v>
+        <v>Ritual</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:48</v>
+        <v>3:01</v>
       </c>
       <c r="H144" t="str">
-        <v>Conan Gray</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L144" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Smile</v>
+        <v>The Best</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Smile - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G145" t="str">
-        <v>3:50</v>
+        <v>3:48</v>
       </c>
       <c r="H145" t="str">
-        <v>Two Shell</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L145" t="str">
-        <v>Smile - Two Shell</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Duro</v>
+        <v>Smile</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Duro - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:05</v>
+        <v>3:50</v>
       </c>
       <c r="H146" t="str">
-        <v>Skrillex</v>
+        <v>Two Shell</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L146" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Duro</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H147" t="str">
-        <v>Sublime</v>
+        <v>Skrillex</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L147" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Carousel</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Everything Glows</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G148" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H148" t="str">
-        <v>Cannons</v>
+        <v>Sublime</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L148" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Mercy</v>
+        <v>Carousel</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Mercy - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G149" t="str">
-        <v>3:49</v>
+        <v>3:36</v>
       </c>
       <c r="H149" t="str">
-        <v>PRESIDENT</v>
+        <v>Cannons</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L149" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Palms</v>
+        <v>Mercy</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Palms - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:18</v>
+        <v>3:49</v>
       </c>
       <c r="H150" t="str">
-        <v>The Maine</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L150" t="str">
-        <v>Palms - The Maine</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ozzy's Song</v>
+        <v>Palms</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:28</v>
+        <v>3:18</v>
       </c>
       <c r="H151" t="str">
-        <v>Black Label Society</v>
+        <v>The Maine</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L151" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Danger</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Danger - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G152" t="str">
-        <v>2:19</v>
+        <v>5:28</v>
       </c>
       <c r="H152" t="str">
-        <v>Nia Archives</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L152" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Icarus</v>
+        <v>Danger</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Icarus - Single</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>4:25</v>
+        <v>2:19</v>
       </c>
       <c r="H153" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L153" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>idk idk</v>
+        <v>Icarus</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>idk idk - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:26</v>
+        <v>4:25</v>
       </c>
       <c r="H154" t="str">
-        <v>Jim Legxacy</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L154" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tonight</v>
+        <v>idk idk</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Tonight - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:25</v>
+        <v>2:26</v>
       </c>
       <c r="H155" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L155" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Tonight</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Switcheroo</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>2:25</v>
       </c>
       <c r="H156" t="str">
-        <v>Gelli Haha</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L156" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G157" t="str">
-        <v>2:45</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>BIA</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L157" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>this girl wants everything</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>3:33</v>
+        <v>2:45</v>
       </c>
       <c r="H158" t="str">
-        <v>Isaia Huron</v>
+        <v>BIA</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L158" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G159" t="str">
-        <v>3:44</v>
+        <v>3:33</v>
       </c>
       <c r="H159" t="str">
-        <v>Slayyyter</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L159" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Kingdom of Fear</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Deep Water - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G160" t="str">
-        <v>2:41</v>
+        <v>3:44</v>
       </c>
       <c r="H160" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L160" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>R3verse</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>takeaways</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G161" t="str">
-        <v>3:31</v>
+        <v>2:41</v>
       </c>
       <c r="H161" t="str">
-        <v>Medium Build</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L161" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>R3verse</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>takeaways</v>
       </c>
       <c r="G162" t="str">
-        <v>2:32</v>
+        <v>3:31</v>
       </c>
       <c r="H162" t="str">
-        <v>MIKE</v>
+        <v>Medium Build</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L162" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>heart of gold</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>heart of gold - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G163" t="str">
-        <v>2:51</v>
+        <v>2:32</v>
       </c>
       <c r="H163" t="str">
-        <v>kai devega</v>
+        <v>MIKE</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L163" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Breaking Down</v>
+        <v>heart of gold</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Skeletor</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:21</v>
+        <v>2:51</v>
       </c>
       <c r="H164" t="str">
-        <v>Chief Keef</v>
+        <v>kai devega</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L164" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Dream House</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream House - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G165" t="str">
-        <v>2:54</v>
+        <v>4:21</v>
       </c>
       <c r="H165" t="str">
-        <v>Empress Of</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L165" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Baby Blue</v>
+        <v>Dream House</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H166" t="str">
-        <v>Cody Simpson</v>
+        <v>Empress Of</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L166" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:37</v>
+        <v>2:51</v>
       </c>
       <c r="H167" t="str">
-        <v>MEDUZA</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Forever Now</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:05</v>
+        <v>2:37</v>
       </c>
       <c r="H168" t="str">
-        <v>Switchfoot</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L168" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Forever Now</v>
       </c>
       <c r="G169" t="str">
-        <v>3:46</v>
+        <v>4:05</v>
       </c>
       <c r="H169" t="str">
-        <v>Benny G</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L169" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Cry In Front Of You</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>3:03</v>
+        <v>3:46</v>
       </c>
       <c r="H170" t="str">
-        <v>Eric Bellinger</v>
+        <v>Benny G</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L170" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>4:19</v>
+        <v>3:03</v>
       </c>
       <c r="H171" t="str">
-        <v>Anish Kumar</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L171" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>GASLIGHT</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>2:10</v>
+        <v>4:19</v>
       </c>
       <c r="H172" t="str">
-        <v>WesGhost</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L172" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Truth To Be Told</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:17</v>
+        <v>2:10</v>
       </c>
       <c r="H173" t="str">
-        <v>GERD</v>
+        <v>WesGhost</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L173" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Free Your Mind</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H174" t="str">
-        <v>Prospa</v>
+        <v>GERD</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L174" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Down To The Bone</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:51</v>
+        <v>3:21</v>
       </c>
       <c r="H175" t="str">
-        <v>Josh Baker</v>
+        <v>Prospa</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L175" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Breathe</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Breathe - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:48</v>
+        <v>2:51</v>
       </c>
       <c r="H176" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L176" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>xs</v>
+        <v>Breathe</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>xs - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:19</v>
+        <v>2:48</v>
       </c>
       <c r="H177" t="str">
-        <v>Ashley Cooke</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L177" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Sail</v>
+        <v>xs</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>xs - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:54</v>
+        <v>3:19</v>
       </c>
       <c r="H178" t="str">
-        <v>Future Islands</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L178" t="str">
-        <v>Sail - Future Islands</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Dreaming</v>
+        <v>Sail</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Dear Nashville</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G179" t="str">
-        <v>3:33</v>
+        <v>4:54</v>
       </c>
       <c r="H179" t="str">
-        <v>Ashley Monroe</v>
+        <v>Future Islands</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L179" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>NEW TINGZ</v>
+        <v>Dreaming</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G180" t="str">
-        <v>2:39</v>
+        <v>3:33</v>
       </c>
       <c r="H180" t="str">
-        <v>Armanii</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L180" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>La Opinión</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Mis Compas El Final</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>2:39</v>
       </c>
       <c r="H181" t="str">
-        <v>Joss Favela</v>
+        <v>Armanii</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L181" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>qué ves en mí?</v>
+        <v>La Opinión</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G182" t="str">
-        <v>3:24</v>
+        <v>3:23</v>
       </c>
       <c r="H182" t="str">
-        <v>Paloma Morphy</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L182" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:43</v>
+        <v>3:24</v>
       </c>
       <c r="H183" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L183" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>TUTUTU</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:16</v>
+        <v>2:43</v>
       </c>
       <c r="H184" t="str">
-        <v>ELENA ROSE</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L184" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:56</v>
+        <v>2:16</v>
       </c>
       <c r="H185" t="str">
-        <v>2'Live Bre</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Me Neither</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Heavy On The Soul</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:32</v>
+        <v>2:56</v>
       </c>
       <c r="H186" t="str">
-        <v>Ty Myers</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L186" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Cole Palmer</v>
+        <v>Me Neither</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Solid Ground</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G187" t="str">
-        <v>2:48</v>
+        <v>3:32</v>
       </c>
       <c r="H187" t="str">
-        <v>Limoblaze</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L187" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Wonder</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Wonder - Single</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G188" t="str">
-        <v>3:48</v>
+        <v>2:48</v>
       </c>
       <c r="H188" t="str">
-        <v>Meeks Carter</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L188" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ICU</v>
+        <v>Wonder</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>ICU - Single</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:53</v>
+        <v>3:48</v>
       </c>
       <c r="H189" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L189" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>ICU</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:45</v>
+        <v>2:53</v>
       </c>
       <c r="H190" t="str">
-        <v>Jozzy</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L190" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Waiting Room (feat. Jordan Ward)</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G191" t="str">
-        <v>3:21</v>
+        <v>2:45</v>
       </c>
       <c r="H191" t="str">
-        <v>Jenevieve</v>
+        <v>Jozzy</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L191" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Waiting Room (feat. Jordan Ward)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Rise</v>
+        <v>Waiting Room (feat. Jordan Ward) - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:02</v>
+        <v>3:21</v>
       </c>
       <c r="H192" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
       </c>
       <c r="L192" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Roll On Thru</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G193" t="str">
-        <v>3:51</v>
+        <v>4:02</v>
       </c>
       <c r="H193" t="str">
-        <v>Hayden Everett</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L193" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Delicately</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Delicately - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>3:51</v>
       </c>
       <c r="H194" t="str">
-        <v>Andrea Bejar</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L194" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>One Of Those Things</v>
+        <v>Delicately</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:27</v>
+        <v>3:20</v>
       </c>
       <c r="H195" t="str">
-        <v>Lucy Clearwater</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L195" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>For Every Dusk</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>6:04</v>
+        <v>3:27</v>
       </c>
       <c r="H196" t="str">
-        <v>José González</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L196" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I'll Wait</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G197" t="str">
-        <v>3:33</v>
+        <v>6:04</v>
       </c>
       <c r="H197" t="str">
-        <v>Buzzy Lee</v>
+        <v>José González</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L197" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Daisy</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Daisy - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G198" t="str">
-        <v>3:02</v>
+        <v>3:33</v>
       </c>
       <c r="H198" t="str">
-        <v>Lola Blue</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L198" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Daisy</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Friend Remixes</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H199" t="str">
-        <v>james K</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L199" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Perdidos - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G200" t="str">
-        <v>2:45</v>
+        <v>3:57</v>
       </c>
       <c r="H200" t="str">
-        <v>MAVICA</v>
+        <v>james K</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L200" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Fort</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Fort - Single</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:27</v>
+        <v>2:45</v>
       </c>
       <c r="H201" t="str">
-        <v>Lamb</v>
+        <v>MAVICA</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L201" t="str">
-        <v>Fort - Lamb</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SAME LA</v>
+        <v>Fort</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>SAME LA - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:44</v>
+        <v>2:27</v>
       </c>
       <c r="H202" t="str">
-        <v>Tiffany Day</v>
+        <v>Lamb</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L202" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Working On It</v>
+        <v>SAME LA</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Working On It - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>3:44</v>
       </c>
       <c r="H203" t="str">
-        <v>Arthur Hill</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L203" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>spring cleaning</v>
+        <v>Working On It</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E204" t="str">
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>4:03</v>
+        <v>3:06</v>
       </c>
       <c r="H204" t="str">
-        <v>Ethan Regan</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L204" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Just Drivin'</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E205" t="str">
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:26</v>
+        <v>4:03</v>
       </c>
       <c r="H205" t="str">
-        <v>Presley Haile</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L205" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Simple Things</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E206" t="str">
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Simple Things - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:46</v>
+        <v>3:26</v>
       </c>
       <c r="H206" t="str">
-        <v>Evening Elephants</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L206" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Want It Back</v>
+        <v>Simple Things</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E207" t="str">
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Want It Back - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:27</v>
+        <v>3:46</v>
       </c>
       <c r="H207" t="str">
-        <v>Giant Rooks</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L207" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Bite Down</v>
+        <v>Want It Back</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D208" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E208" t="str">
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Bite Down - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>3:36</v>
+        <v>3:27</v>
       </c>
       <c r="H208" t="str">
-        <v>Anna Sofia</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L208" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Bite Down</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D209" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E209" t="str">
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G209" t="str">
-        <v>5:42</v>
+        <v>3:36</v>
       </c>
       <c r="H209" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L209" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Demons</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D210" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E210" t="str">
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G210" t="str">
-        <v>2:42</v>
+        <v>5:42</v>
       </c>
       <c r="H210" t="str">
-        <v>Anella</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L210" t="str">
-        <v>Demons - Anella</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Es brennt...</v>
+        <v>Demons</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D211" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E211" t="str">
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G211" t="str">
-        <v>3:35</v>
+        <v>2:42</v>
       </c>
       <c r="H211" t="str">
-        <v>Till Lindemann</v>
+        <v>Anella</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L211" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Fire Marengo</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D212" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E212" t="str">
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G212" t="str">
-        <v>3:49</v>
+        <v>3:35</v>
       </c>
       <c r="H212" t="str">
-        <v>Enslaved</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I212" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L212" t="str">
-        <v>Fire Marengo - Enslaved</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
+        <v>Fire Marengo</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+      </c>
+      <c r="G213" t="str">
+        <v>3:49</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Enslaved</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Fire Marengo - Enslaved</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
         <v>Close to the Bone</v>
       </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
         <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
-      <c r="D213" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
+      <c r="D214" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G213" t="str">
+      <c r="G214" t="str">
         <v>4:09</v>
       </c>
-      <c r="H213" t="str">
+      <c r="H214" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K213" t="str">
+      <c r="K214" t="str">
         <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
-      <c r="L213" t="str">
+      <c r="L214" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L214"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L214"/>
+  <dimension ref="A1:L213"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר אופיר – בדמייך חיי</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-02</v>
+        <v>3d ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%91%d7%93%d7%9e%d7%99%d7%99%d7%9a-%d7%97%d7%99%d7%99/</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-02</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר בדמייך חיי בביצועה של תמר אופיר, המבוסס על הפסוקים “ואעבור עלייך…” מתוך ספר יחזקאל (שנכנסו גם לנוסח ההגדה), הוא דוגמה יפה לשילוב בין טקסט מקראי טעון לבין פרשנות מוזיקלית עכשווית, רגשית ואינטימית. המילים מהוות ביטוי עוצמתי לקידוש החיים מתוך</v>
+        <v>3d ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:55</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר אופיר – בדמייך חיי</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-02</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:56</v>
+        <v>2:45</v>
       </c>
       <c r="H3" t="str">
-        <v>Charlie Puth</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-02</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:50</v>
+        <v>6:29</v>
       </c>
       <c r="H4" t="str">
-        <v>Miley Cyrus</v>
+        <v>RAYE</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-02</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:42</v>
+        <v>3:17</v>
       </c>
       <c r="H5" t="str">
-        <v>Conan Gray</v>
+        <v>Take That</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-02</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:16</v>
+        <v>4:22</v>
       </c>
       <c r="H6" t="str">
-        <v>Charlie Puth</v>
+        <v>Armik</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-02</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:08</v>
+        <v>4:10</v>
       </c>
       <c r="H7" t="str">
-        <v>Kylie Morgan</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-02</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H8" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-02</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:01</v>
+        <v>3:03</v>
       </c>
       <c r="H9" t="str">
-        <v>Angelina Mango</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-02</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:59</v>
+        <v>3:56</v>
       </c>
       <c r="H10" t="str">
-        <v>Julio Iglesias</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-02</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:59</v>
+        <v>3:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Loreen</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-02</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:58</v>
+        <v>3:56</v>
       </c>
       <c r="H12" t="str">
-        <v>Jessie Ware</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-02</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:49</v>
+        <v>2:50</v>
       </c>
       <c r="H13" t="str">
-        <v>Holly Humberstone</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-02</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:22</v>
+        <v>3:42</v>
       </c>
       <c r="H14" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-02</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:50</v>
+        <v>2:16</v>
       </c>
       <c r="H15" t="str">
-        <v>Ella Langley</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-02</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G16" t="str">
-        <v>6:43</v>
+        <v>3:08</v>
       </c>
       <c r="H16" t="str">
-        <v>David Gilmour</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-02</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:52</v>
+        <v>3:38</v>
       </c>
       <c r="H17" t="str">
-        <v>Eagles</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-02</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:13</v>
+        <v>3:01</v>
       </c>
       <c r="H18" t="str">
-        <v>Moody Joody</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-02</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:28</v>
+        <v>3:59</v>
       </c>
       <c r="H19" t="str">
-        <v>Jackson Dean</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-02</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:01</v>
+        <v>2:59</v>
       </c>
       <c r="H20" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Loreen</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-02</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:00</v>
+        <v>2:58</v>
       </c>
       <c r="H21" t="str">
-        <v>Madison Cunningham</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-02</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:35</v>
+        <v>3:49</v>
       </c>
       <c r="H22" t="str">
-        <v>mary in the junkyard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B23" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-02</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:01</v>
+        <v>3:22</v>
       </c>
       <c r="H23" t="str">
-        <v>Adam Sanders</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B24" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-02</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:40</v>
+        <v>3:50</v>
       </c>
       <c r="H24" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B25" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-02</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:25</v>
+        <v>6:43</v>
       </c>
       <c r="H25" t="str">
-        <v>twocolors</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>11 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-02</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>11 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:42</v>
+        <v>4:52</v>
       </c>
       <c r="H26" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Eagles</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-02</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:56</v>
+        <v>3:13</v>
       </c>
       <c r="H27" t="str">
-        <v>Prince</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-02</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:12</v>
+        <v>3:28</v>
       </c>
       <c r="H28" t="str">
-        <v>RAYE</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-02</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H29" t="str">
-        <v>The Warning</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B30" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-02</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:18</v>
+        <v>4:00</v>
       </c>
       <c r="H30" t="str">
-        <v>Pentatonix</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B31" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-02</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>12 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:33</v>
+        <v>5:35</v>
       </c>
       <c r="H31" t="str">
-        <v>Tenille Townes</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-02</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G32" t="str">
-        <v>5:53</v>
+        <v>3:01</v>
       </c>
       <c r="H32" t="str">
-        <v>Jessie Ware</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B33" t="str">
-        <v>13 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-02</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>13 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:37</v>
+        <v>3:40</v>
       </c>
       <c r="H33" t="str">
-        <v>Niall Horan</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>13 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-02</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>13 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:26</v>
+        <v>2:25</v>
       </c>
       <c r="H34" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>twocolors</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B35" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-02</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:40</v>
+        <v>3:42</v>
       </c>
       <c r="H35" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B36" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-02</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:30</v>
+        <v>3:56</v>
       </c>
       <c r="H36" t="str">
-        <v>Jackson Dean</v>
+        <v>Prince</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-02</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:02</v>
+        <v>5:12</v>
       </c>
       <c r="H37" t="str">
-        <v>Foo Fighters</v>
+        <v>RAYE</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-02</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:40</v>
+        <v>3:30</v>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Warning</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-02</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:22</v>
+        <v>3:18</v>
       </c>
       <c r="H39" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-02</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:47</v>
+        <v>3:33</v>
       </c>
       <c r="H40" t="str">
-        <v>Ella Langley</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-02</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:39</v>
+        <v>5:53</v>
       </c>
       <c r="H41" t="str">
-        <v>Cannons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B42" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-02</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:10</v>
+        <v>2:37</v>
       </c>
       <c r="H42" t="str">
-        <v>Luke Combs</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-02</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:47</v>
+        <v>2:26</v>
       </c>
       <c r="H43" t="str">
-        <v>Nessa Barrett</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-02</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:14</v>
+        <v>2:40</v>
       </c>
       <c r="H44" t="str">
-        <v>aron!</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B45" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-02</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:00</v>
+        <v>3:30</v>
       </c>
       <c r="H45" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-02</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:56</v>
+        <v>4:02</v>
       </c>
       <c r="H46" t="str">
-        <v>DMA'S</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-02</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:17</v>
+        <v>3:40</v>
       </c>
       <c r="H47" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-02</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:17</v>
+        <v>2:22</v>
       </c>
       <c r="H48" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-02</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H49" t="str">
-        <v>Nick Carter</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-02</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:38</v>
+        <v>3:39</v>
       </c>
       <c r="H50" t="str">
-        <v>Carly Pearce</v>
+        <v>Cannons</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-02</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:11</v>
+        <v>4:10</v>
       </c>
       <c r="H51" t="str">
-        <v>OneRepublic</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-02</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:57</v>
+        <v>4:47</v>
       </c>
       <c r="H52" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-02</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:47</v>
+        <v>2:14</v>
       </c>
       <c r="H53" t="str">
-        <v>Armin van Buuren</v>
+        <v>aron!</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-02</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G54" t="str">
-        <v>7:10</v>
+        <v>4:00</v>
       </c>
       <c r="H54" t="str">
-        <v>David Gilmour</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-02</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:06</v>
+        <v>3:56</v>
       </c>
       <c r="H55" t="str">
-        <v>Grace Enger</v>
+        <v>DMA'S</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-02</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:05</v>
+        <v>3:17</v>
       </c>
       <c r="H56" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-02</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:12</v>
+        <v>3:17</v>
       </c>
       <c r="H57" t="str">
-        <v>Freya Ridings</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-02</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
-        <v>9:11</v>
+        <v>3:31</v>
       </c>
       <c r="H58" t="str">
-        <v>David Gilmour</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-02</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:49</v>
+        <v>3:38</v>
       </c>
       <c r="H59" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-02</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:28</v>
+        <v>4:11</v>
       </c>
       <c r="H60" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-02</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:31</v>
+        <v>2:57</v>
       </c>
       <c r="H61" t="str">
-        <v>Martin Garrix</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-02</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:11</v>
+        <v>3:47</v>
       </c>
       <c r="H62" t="str">
-        <v>Baby Queen</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-02</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>7:10</v>
       </c>
       <c r="H63" t="str">
-        <v>HAUSER</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-02</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:34</v>
+        <v>3:06</v>
       </c>
       <c r="H64" t="str">
-        <v>Holly Humberstone</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-02</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:50</v>
+        <v>3:05</v>
       </c>
       <c r="H65" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-02</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:51</v>
+        <v>3:12</v>
       </c>
       <c r="H66" t="str">
-        <v>Rick Astley</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-02</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:39</v>
+        <v>9:11</v>
       </c>
       <c r="H67" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-02</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:08</v>
+        <v>3:49</v>
       </c>
       <c r="H68" t="str">
-        <v>Jessie J</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-02</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:46</v>
+        <v>3:28</v>
       </c>
       <c r="H69" t="str">
-        <v>Bishop Briggs</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-02</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:42</v>
+        <v>3:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Dean Lewis</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-02</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:31</v>
+        <v>3:11</v>
       </c>
       <c r="H71" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-02</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:14</v>
+        <v>2:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Luke Combs</v>
+        <v>HAUSER</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-02</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H73" t="str">
-        <v>Allison Russell</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-02</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:43</v>
+        <v>2:50</v>
       </c>
       <c r="H74" t="str">
-        <v>We Three</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-02</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:54</v>
+        <v>3:51</v>
       </c>
       <c r="H75" t="str">
-        <v>paris jackson</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-02</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:46</v>
+        <v>2:39</v>
       </c>
       <c r="H76" t="str">
-        <v>Kane Brown</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-02</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:37</v>
+        <v>5:08</v>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson</v>
+        <v>Jessie J</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-02</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:57</v>
+        <v>3:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Malcolm Todd</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-02</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:38</v>
+        <v>2:42</v>
       </c>
       <c r="H79" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-02</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:29</v>
+        <v>2:31</v>
       </c>
       <c r="H80" t="str">
-        <v>Kungs</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-02</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:28</v>
+        <v>3:14</v>
       </c>
       <c r="H81" t="str">
-        <v>Sunday (1994)</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-02</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:26</v>
+        <v>3:22</v>
       </c>
       <c r="H82" t="str">
-        <v>aron!</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-02</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:51</v>
+        <v>3:43</v>
       </c>
       <c r="H83" t="str">
-        <v>Colinstoughmusic</v>
+        <v>We Three</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-02</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:49</v>
+        <v>2:54</v>
       </c>
       <c r="H84" t="str">
-        <v>Sunday (1994)</v>
+        <v>paris jackson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-02</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:16</v>
+        <v>2:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Owen Riegling</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-02</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:16</v>
+        <v>3:37</v>
       </c>
       <c r="H86" t="str">
-        <v>LANY</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-02</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:25</v>
+        <v>2:57</v>
       </c>
       <c r="H87" t="str">
-        <v>Maverick Sabre</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-02</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:50</v>
+        <v>3:38</v>
       </c>
       <c r="H88" t="str">
-        <v>Amanda Jordan</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-02</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:57</v>
+        <v>4:29</v>
       </c>
       <c r="H89" t="str">
-        <v>Beabadoobee</v>
+        <v>Kungs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-02</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:58</v>
+        <v>4:28</v>
       </c>
       <c r="H90" t="str">
-        <v>Spacey Jane</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-02</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>aron!</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-02</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:09</v>
+        <v>3:51</v>
       </c>
       <c r="H92" t="str">
-        <v>Mei Semones</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-02</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:08</v>
+        <v>2:49</v>
       </c>
       <c r="H93" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-02</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:57</v>
+        <v>4:16</v>
       </c>
       <c r="H94" t="str">
-        <v>Natalie Jane</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-02</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:13</v>
+        <v>4:16</v>
       </c>
       <c r="H95" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>LANY</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-02</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:12</v>
+        <v>3:25</v>
       </c>
       <c r="H96" t="str">
-        <v>David Gilmour</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-02</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>2:50</v>
       </c>
       <c r="H97" t="str">
-        <v>Far Caspian</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-02</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:34</v>
+        <v>3:57</v>
       </c>
       <c r="H98" t="str">
-        <v>Celine Dion</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-02</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:48</v>
+        <v>3:58</v>
       </c>
       <c r="H99" t="str">
-        <v>Harry Styles</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-02</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:58</v>
+        <v>3:25</v>
       </c>
       <c r="H100" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-02</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:33</v>
+        <v>4:09</v>
       </c>
       <c r="H101" t="str">
-        <v>Ellise</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>CHICA 305</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-02</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>CHICA 305 - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>4:56</v>
+        <v>3:08</v>
       </c>
       <c r="H102" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>John Summit</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
       </c>
       <c r="L102" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>CHICA 305 - John Summit</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>CHICA 305</v>
+        <v>Jet Lag Mouth</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
+        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-02</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>CHICA 305 - Single</v>
+        <v>Jet Lag Mouth - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:08</v>
+        <v>2:32</v>
       </c>
       <c r="H103" t="str">
-        <v>John Summit</v>
+        <v>In Color</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
+        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
       </c>
       <c r="L103" t="str">
-        <v>CHICA 305 - John Summit</v>
+        <v>Jet Lag Mouth - In Color</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>2:32</v>
+        <v>3:18</v>
       </c>
       <c r="H104" t="str">
-        <v>In Color</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Days We Left Behind</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:18</v>
+        <v>2:47</v>
       </c>
       <c r="H105" t="str">
-        <v>Paul McCartney</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L105" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G106" t="str">
-        <v>2:47</v>
+        <v>6:17</v>
       </c>
       <c r="H106" t="str">
-        <v>Miley Cyrus</v>
+        <v>RAYE</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L106" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>MARATHON</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>6:17</v>
+        <v>2:49</v>
       </c>
       <c r="H107" t="str">
-        <v>RAYE</v>
+        <v>Becky G</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L107" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>MARATHON</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>MARATHON - Single</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Becky G</v>
+        <v>John Summit</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L108" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ALL THE TIME</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>3:00</v>
+        <v>3:34</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Sucker For Love</v>
+        <v>FATHER</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Sexistential</v>
+        <v>BULLY</v>
       </c>
       <c r="G110" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H110" t="str">
-        <v>Robyn</v>
+        <v>Kanye West</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L110" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>FATHER</v>
+        <v>Lose Control</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>BULLY</v>
+        <v>ADL</v>
       </c>
       <c r="G111" t="str">
-        <v>2:49</v>
+        <v>2:39</v>
       </c>
       <c r="H111" t="str">
-        <v>Kanye West</v>
+        <v>Yeat</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L111" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Lose Control</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ADL</v>
+        <v>Zavier</v>
       </c>
       <c r="G112" t="str">
-        <v>2:39</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>Yeat</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L112" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Zavier</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G113" t="str">
-        <v>3:44</v>
+        <v>2:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Fetty Wap</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L113" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WAGWAN</v>
+        <v>Sideways</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G114" t="str">
-        <v>2:07</v>
+        <v>3:12</v>
       </c>
       <c r="H114" t="str">
-        <v>Central Cee</v>
+        <v>ZAYN</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L114" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Sideways</v>
+        <v>Automatic</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>KONNAKOL</v>
+        <v>Superbloom</v>
       </c>
       <c r="G115" t="str">
-        <v>3:12</v>
+        <v>2:57</v>
       </c>
       <c r="H115" t="str">
-        <v>ZAYN</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L115" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Automatic</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Superbloom</v>
+        <v>Ricochet</v>
       </c>
       <c r="G116" t="str">
-        <v>2:57</v>
+        <v>3:34</v>
       </c>
       <c r="H116" t="str">
-        <v>Jessie Ware</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L116" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Tractor Beam</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ricochet</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G117" t="str">
-        <v>3:34</v>
+        <v>1:37</v>
       </c>
       <c r="H117" t="str">
-        <v>Snail Mail</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L117" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Home on the Range</v>
+        <v>prom queen</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>1:37</v>
+        <v>2:43</v>
       </c>
       <c r="H118" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L118" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>prom queen</v>
+        <v>Back Home</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>prom queen - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G119" t="str">
-        <v>2:43</v>
+        <v>1:36</v>
       </c>
       <c r="H119" t="str">
-        <v>Amelia Moore</v>
+        <v>MIKE</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L119" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Back Home</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>1:36</v>
+        <v>3:26</v>
       </c>
       <c r="H120" t="str">
-        <v>MIKE</v>
+        <v>J Balvin</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L120" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Pal Agua</v>
+        <v>Phoenix</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:26</v>
+        <v>2:24</v>
       </c>
       <c r="H121" t="str">
-        <v>J Balvin</v>
+        <v>Marshmello</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L121" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Phoenix</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Phoenix - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:24</v>
+        <v>2:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Marshmello</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L122" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:56</v>
+        <v>3:36</v>
       </c>
       <c r="H123" t="str">
-        <v>Ne-Yo</v>
+        <v>Eli</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L123" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Feel Your Rain</v>
+        <v>Lonely</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G124" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H124" t="str">
-        <v>Eli</v>
+        <v>Fcukers</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L124" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Lonely</v>
+        <v>Back in Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ö</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:58</v>
+        <v>3:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Fcukers</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L125" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Back in Love</v>
+        <v>Sideways</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Back in Love - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G126" t="str">
-        <v>3:14</v>
+        <v>3:55</v>
       </c>
       <c r="H126" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L126" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Sideways</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Honora</v>
       </c>
       <c r="G127" t="str">
-        <v>3:55</v>
+        <v>4:22</v>
       </c>
       <c r="H127" t="str">
-        <v>Charlie Puth</v>
+        <v>Flea</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L127" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Honora</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:22</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Flea</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L128" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Shame</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/shame/1887698916</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Shame - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:58</v>
+        <v>3:02</v>
       </c>
       <c r="H129" t="str">
-        <v>Chelsea Cutler</v>
+        <v>BunnaB</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/bunnab/1695734940</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/shame/1887698914</v>
       </c>
       <c r="L129" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Shame - BunnaB</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Shame</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/shame/1887698916</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Shame - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G130" t="str">
-        <v>3:02</v>
+        <v>4:42</v>
       </c>
       <c r="H130" t="str">
-        <v>BunnaB</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/bunnab/1695734940</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/shame/1887698914</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L130" t="str">
-        <v>Shame - BunnaB</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>One Thing At A Time</v>
+        <v>wasteland</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Creature of Habit</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:42</v>
+        <v>3:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Courtney Barnett</v>
+        <v>Yuna</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L131" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>wasteland</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>wasteland - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G132" t="str">
-        <v>3:05</v>
+        <v>2:31</v>
       </c>
       <c r="H132" t="str">
-        <v>Yuna</v>
+        <v>Artemas</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L132" t="str">
-        <v>wasteland - Yuna</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Por LA</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>getting up to no good</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G133" t="str">
-        <v>2:31</v>
+        <v>2:19</v>
       </c>
       <c r="H133" t="str">
-        <v>Artemas</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L133" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Por LA</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>TODO Ø NADA</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G134" t="str">
-        <v>2:19</v>
+        <v>4:14</v>
       </c>
       <c r="H134" t="str">
-        <v>Linea Personal</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L134" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>You Lead Me</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Broken View</v>
       </c>
       <c r="G135" t="str">
-        <v>4:14</v>
+        <v>4:18</v>
       </c>
       <c r="H135" t="str">
-        <v>Lauren Daigle</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L135" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Just A Kid</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Broken View</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>4:18</v>
+        <v>2:54</v>
       </c>
       <c r="H136" t="str">
-        <v>Sam Barber</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L136" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Country And She Knows It</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:54</v>
+        <v>2:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Luke Bryan</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L137" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G138" t="str">
-        <v>2:35</v>
+        <v>3:17</v>
       </c>
       <c r="H138" t="str">
-        <v>Thomas Rhett</v>
+        <v>ERNEST</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L138" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Deep Blue</v>
+        <v>Special</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Deep Blue</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G139" t="str">
-        <v>3:17</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>ERNEST</v>
+        <v>Elmiene</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L139" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Special</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>sounds for someone</v>
+        <v>CANDY</v>
       </c>
       <c r="G140" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H140" t="str">
-        <v>Elmiene</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L140" t="str">
-        <v>Special - Elmiene</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Heart Attack</v>
+        <v>STAY</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>CANDY</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:52</v>
+        <v>3:06</v>
       </c>
       <c r="H141" t="str">
-        <v>Justine Skye</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L141" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>STAY</v>
+        <v>Unglued</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>STAY - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G142" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H142" t="str">
-        <v>Stray Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L142" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Unglued</v>
+        <v>Ritual</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Work of Heart</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:54</v>
+        <v>3:01</v>
       </c>
       <c r="H143" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L143" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Ritual</v>
+        <v>The Best</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Ritual - Single</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G144" t="str">
-        <v>3:01</v>
+        <v>3:48</v>
       </c>
       <c r="H144" t="str">
-        <v>Icona Pop</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L144" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>The Best</v>
+        <v>Smile</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:48</v>
+        <v>3:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Conan Gray</v>
+        <v>Two Shell</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L145" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Smile</v>
+        <v>Duro</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Smile - Single</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H146" t="str">
-        <v>Two Shell</v>
+        <v>Skrillex</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L146" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Duro</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Duro - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G147" t="str">
-        <v>3:05</v>
+        <v>2:58</v>
       </c>
       <c r="H147" t="str">
-        <v>Skrillex</v>
+        <v>Sublime</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L147" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Carousel</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G148" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H148" t="str">
-        <v>Sublime</v>
+        <v>Cannons</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L148" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Carousel</v>
+        <v>Mercy</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Everything Glows</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:36</v>
+        <v>3:49</v>
       </c>
       <c r="H149" t="str">
-        <v>Cannons</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L149" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Mercy</v>
+        <v>Palms</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Mercy - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:49</v>
+        <v>3:18</v>
       </c>
       <c r="H150" t="str">
-        <v>PRESIDENT</v>
+        <v>The Maine</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L150" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Palms</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Palms - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G151" t="str">
-        <v>3:18</v>
+        <v>5:28</v>
       </c>
       <c r="H151" t="str">
-        <v>The Maine</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L151" t="str">
-        <v>Palms - The Maine</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ozzy's Song</v>
+        <v>Danger</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>5:28</v>
+        <v>2:19</v>
       </c>
       <c r="H152" t="str">
-        <v>Black Label Society</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L152" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Danger</v>
+        <v>Icarus</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Danger - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:19</v>
+        <v>4:25</v>
       </c>
       <c r="H153" t="str">
-        <v>Nia Archives</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L153" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Icarus</v>
+        <v>idk idk</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Icarus - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:25</v>
+        <v>2:26</v>
       </c>
       <c r="H154" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L154" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>idk idk</v>
+        <v>Tonight</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>idk idk - Single</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:26</v>
+        <v>2:25</v>
       </c>
       <c r="H155" t="str">
-        <v>Jim Legxacy</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L155" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Tonight</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Tonight - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G156" t="str">
-        <v>2:25</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L156" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Switcheroo</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>3:44</v>
+        <v>2:45</v>
       </c>
       <c r="H157" t="str">
-        <v>Gelli Haha</v>
+        <v>BIA</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L157" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G158" t="str">
-        <v>2:45</v>
+        <v>3:33</v>
       </c>
       <c r="H158" t="str">
-        <v>BIA</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L158" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>this girl wants everything</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G159" t="str">
-        <v>3:33</v>
+        <v>3:44</v>
       </c>
       <c r="H159" t="str">
-        <v>Isaia Huron</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L159" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>3:44</v>
+        <v>2:41</v>
       </c>
       <c r="H160" t="str">
-        <v>Slayyyter</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L160" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Kingdom of Fear</v>
+        <v>R3verse</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Deep Water - EP</v>
+        <v>takeaways</v>
       </c>
       <c r="G161" t="str">
-        <v>2:41</v>
+        <v>3:31</v>
       </c>
       <c r="H161" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Medium Build</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L161" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>R3verse</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>takeaways</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G162" t="str">
-        <v>3:31</v>
+        <v>2:32</v>
       </c>
       <c r="H162" t="str">
-        <v>Medium Build</v>
+        <v>MIKE</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L162" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>heart of gold</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:32</v>
+        <v>2:51</v>
       </c>
       <c r="H163" t="str">
-        <v>MIKE</v>
+        <v>kai devega</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L163" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>heart of gold</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>heart of gold - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G164" t="str">
-        <v>2:51</v>
+        <v>4:21</v>
       </c>
       <c r="H164" t="str">
-        <v>kai devega</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L164" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Breaking Down</v>
+        <v>Dream House</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Skeletor</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:21</v>
+        <v>2:54</v>
       </c>
       <c r="H165" t="str">
-        <v>Chief Keef</v>
+        <v>Empress Of</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L165" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Dream House</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Dream House - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:54</v>
+        <v>2:51</v>
       </c>
       <c r="H166" t="str">
-        <v>Empress Of</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L166" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Baby Blue</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H167" t="str">
-        <v>Cody Simpson</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L167" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G168" t="str">
-        <v>2:37</v>
+        <v>4:05</v>
       </c>
       <c r="H168" t="str">
-        <v>MEDUZA</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L168" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Forever Now</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>4:05</v>
+        <v>3:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Switchfoot</v>
+        <v>Benny G</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L169" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:46</v>
+        <v>3:03</v>
       </c>
       <c r="H170" t="str">
-        <v>Benny G</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L170" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>3:03</v>
+        <v>4:19</v>
       </c>
       <c r="H171" t="str">
-        <v>Eric Bellinger</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L171" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:19</v>
+        <v>2:10</v>
       </c>
       <c r="H172" t="str">
-        <v>Anish Kumar</v>
+        <v>WesGhost</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L172" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>GASLIGHT</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:10</v>
+        <v>3:17</v>
       </c>
       <c r="H173" t="str">
-        <v>WesGhost</v>
+        <v>GERD</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L173" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Truth To Be Told</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H174" t="str">
-        <v>GERD</v>
+        <v>Prospa</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L174" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Free Your Mind</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H175" t="str">
-        <v>Prospa</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L175" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Down To The Bone</v>
+        <v>Breathe</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:51</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>Josh Baker</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L176" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Breathe</v>
+        <v>xs</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Breathe - Single</v>
+        <v>xs - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H177" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L177" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>xs</v>
+        <v>Sail</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>xs - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G178" t="str">
-        <v>3:19</v>
+        <v>4:54</v>
       </c>
       <c r="H178" t="str">
-        <v>Ashley Cooke</v>
+        <v>Future Islands</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L178" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Sail</v>
+        <v>Dreaming</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G179" t="str">
-        <v>4:54</v>
+        <v>3:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Future Islands</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L179" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Dreaming</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Dear Nashville</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G180" t="str">
-        <v>3:33</v>
+        <v>2:39</v>
       </c>
       <c r="H180" t="str">
-        <v>Ashley Monroe</v>
+        <v>Armanii</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L180" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>NEW TINGZ</v>
+        <v>La Opinión</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G181" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Armanii</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L181" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>La Opinión</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Mis Compas El Final</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:23</v>
+        <v>3:24</v>
       </c>
       <c r="H182" t="str">
-        <v>Joss Favela</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L182" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>qué ves en mí?</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:24</v>
+        <v>2:43</v>
       </c>
       <c r="H183" t="str">
-        <v>Paloma Morphy</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L183" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:43</v>
+        <v>2:16</v>
       </c>
       <c r="H184" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L184" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>TUTUTU</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>TUTUTU - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:16</v>
+        <v>2:56</v>
       </c>
       <c r="H185" t="str">
-        <v>ELENA ROSE</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L185" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>Me Neither</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G186" t="str">
-        <v>2:56</v>
+        <v>3:32</v>
       </c>
       <c r="H186" t="str">
-        <v>2'Live Bre</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L186" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Me Neither</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G187" t="str">
-        <v>3:32</v>
+        <v>2:48</v>
       </c>
       <c r="H187" t="str">
-        <v>Ty Myers</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L187" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Cole Palmer</v>
+        <v>Wonder</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Solid Ground</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:48</v>
+        <v>3:48</v>
       </c>
       <c r="H188" t="str">
-        <v>Limoblaze</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L188" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Wonder</v>
+        <v>ICU</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Wonder - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:48</v>
+        <v>2:53</v>
       </c>
       <c r="H189" t="str">
-        <v>Meeks Carter</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L189" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>ICU</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>ICU - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G190" t="str">
-        <v>2:53</v>
+        <v>2:45</v>
       </c>
       <c r="H190" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Jozzy</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L190" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Waiting Room (feat. Jordan Ward)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Waiting Room (feat. Jordan Ward) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:45</v>
+        <v>3:21</v>
       </c>
       <c r="H191" t="str">
-        <v>Jozzy</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
       </c>
       <c r="L191" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Waiting Room (feat. Jordan Ward)</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G192" t="str">
-        <v>3:21</v>
+        <v>4:02</v>
       </c>
       <c r="H192" t="str">
-        <v>Jenevieve</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L192" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Rise</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:02</v>
+        <v>3:51</v>
       </c>
       <c r="H193" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L193" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Roll On Thru</v>
+        <v>Delicately</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:51</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>Hayden Everett</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L194" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Delicately</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Delicately - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H195" t="str">
-        <v>Andrea Bejar</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L195" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>One Of Those Things</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G196" t="str">
-        <v>3:27</v>
+        <v>6:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Lucy Clearwater</v>
+        <v>José González</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L196" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>For Every Dusk</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G197" t="str">
-        <v>6:04</v>
+        <v>3:33</v>
       </c>
       <c r="H197" t="str">
-        <v>José González</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L197" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>I'll Wait</v>
+        <v>Daisy</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-02</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:33</v>
+        <v>3:02</v>
       </c>
       <c r="H198" t="str">
-        <v>Buzzy Lee</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L198" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Daisy</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-02</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Daisy - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G199" t="str">
-        <v>3:02</v>
+        <v>3:57</v>
       </c>
       <c r="H199" t="str">
-        <v>Lola Blue</v>
+        <v>james K</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L199" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-02</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Friend Remixes</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:57</v>
+        <v>2:45</v>
       </c>
       <c r="H200" t="str">
-        <v>james K</v>
+        <v>MAVICA</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L200" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>Fort</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-02</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Perdidos - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:45</v>
+        <v>2:27</v>
       </c>
       <c r="H201" t="str">
-        <v>MAVICA</v>
+        <v>Lamb</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L201" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Fort</v>
+        <v>SAME LA</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-02</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Fort - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:27</v>
+        <v>3:44</v>
       </c>
       <c r="H202" t="str">
-        <v>Lamb</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L202" t="str">
-        <v>Fort - Lamb</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>SAME LA</v>
+        <v>Working On It</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-02</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>SAME LA - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:44</v>
+        <v>3:06</v>
       </c>
       <c r="H203" t="str">
-        <v>Tiffany Day</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L203" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Working On It</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-02</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Working On It - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:06</v>
+        <v>4:03</v>
       </c>
       <c r="H204" t="str">
-        <v>Arthur Hill</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L204" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>spring cleaning</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D205" t="str">
         <v>2026-04-02</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H205" t="str">
-        <v>Ethan Regan</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L205" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Just Drivin'</v>
+        <v>Simple Things</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D206" t="str">
         <v>2026-04-02</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H206" t="str">
-        <v>Presley Haile</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L206" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Simple Things</v>
+        <v>Want It Back</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D207" t="str">
         <v>2026-04-02</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Simple Things - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:46</v>
+        <v>3:27</v>
       </c>
       <c r="H207" t="str">
-        <v>Evening Elephants</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L207" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Want It Back</v>
+        <v>Bite Down</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D208" t="str">
         <v>2026-04-02</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Want It Back - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>3:27</v>
+        <v>3:36</v>
       </c>
       <c r="H208" t="str">
-        <v>Giant Rooks</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L208" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Bite Down</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D209" t="str">
         <v>2026-04-02</v>
@@ -8317,36 +8317,36 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Bite Down - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G209" t="str">
-        <v>3:36</v>
+        <v>5:42</v>
       </c>
       <c r="H209" t="str">
-        <v>Anna Sofia</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L209" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Demons</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D210" t="str">
         <v>2026-04-02</v>
@@ -8355,36 +8355,36 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G210" t="str">
-        <v>5:42</v>
+        <v>2:42</v>
       </c>
       <c r="H210" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Anella</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L210" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Demons</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D211" t="str">
         <v>2026-04-02</v>
@@ -8393,36 +8393,36 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G211" t="str">
-        <v>2:42</v>
+        <v>3:35</v>
       </c>
       <c r="H211" t="str">
-        <v>Anella</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L211" t="str">
-        <v>Demons - Anella</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Es brennt...</v>
+        <v>Fire Marengo</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D212" t="str">
         <v>2026-04-02</v>
@@ -8431,36 +8431,36 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
       </c>
       <c r="G212" t="str">
-        <v>3:35</v>
+        <v>3:49</v>
       </c>
       <c r="H212" t="str">
-        <v>Till Lindemann</v>
+        <v>Enslaved</v>
       </c>
       <c r="I212" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
       </c>
       <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
       </c>
       <c r="L212" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Fire Marengo - Enslaved</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Fire Marengo</v>
+        <v>Close to the Bone</v>
       </c>
       <c r="B213" t="str">
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D213" t="str">
         <v>2026-04-02</v>
@@ -8469,68 +8469,30 @@
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G213" t="str">
-        <v>3:49</v>
+        <v>4:09</v>
       </c>
       <c r="H213" t="str">
-        <v>Enslaved</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I213" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
       <c r="L213" t="str">
-        <v>Fire Marengo - Enslaved</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Close to the Bone</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G214" t="str">
-        <v>4:09</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
-      </c>
-      <c r="L214" t="str">
         <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L214"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L213"/>
+  <dimension ref="A1:L218"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>3d ago</v>
+        <v>2026-04-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410326&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-02</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3d ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>3:55</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Nothing But Thieves</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>נתנאל ששון - היא יודעת קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>3d ago</v>
+        <v>2026-04-02</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410325&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-02</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3d ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>2:45</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Ocean Alley</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>נתנאל ששון - היא יודעת קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>נהוראי אברהם - מישל קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>3d ago</v>
+        <v>2026-04-02</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410324&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-02</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3d ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>6:29</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>RAYE</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>נהוראי אברהם - מישל קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>5d ago</v>
+        <v>2026-04-02</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410323&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-02</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5d ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Take That</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>5d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-02</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:22</v>
+        <v>3:55</v>
       </c>
       <c r="H6" t="str">
-        <v>Armik</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B7" t="str">
-        <v>5d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-02</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:10</v>
+        <v>2:45</v>
       </c>
       <c r="H7" t="str">
-        <v>Switchfoot</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B8" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-02</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:19</v>
+        <v>6:29</v>
       </c>
       <c r="H8" t="str">
-        <v>Peter Gabriel</v>
+        <v>RAYE</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-02</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H9" t="str">
-        <v>Sarah Julia</v>
+        <v>Take That</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B10" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-02</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:56</v>
+        <v>4:22</v>
       </c>
       <c r="H10" t="str">
-        <v>Chris Norman</v>
+        <v>Armik</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-02</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:58</v>
+        <v>4:10</v>
       </c>
       <c r="H11" t="str">
-        <v>Alan Walker</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B12" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-02</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:56</v>
+        <v>3:19</v>
       </c>
       <c r="H12" t="str">
-        <v>Charlie Puth</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-02</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:50</v>
+        <v>3:03</v>
       </c>
       <c r="H13" t="str">
-        <v>Miley Cyrus</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-02</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:42</v>
+        <v>3:56</v>
       </c>
       <c r="H14" t="str">
-        <v>Conan Gray</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-02</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:16</v>
+        <v>3:58</v>
       </c>
       <c r="H15" t="str">
-        <v>Charlie Puth</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B16" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-02</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:08</v>
+        <v>3:56</v>
       </c>
       <c r="H16" t="str">
-        <v>Kylie Morgan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B17" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-02</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:38</v>
+        <v>2:50</v>
       </c>
       <c r="H17" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-02</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:01</v>
+        <v>3:42</v>
       </c>
       <c r="H18" t="str">
-        <v>Angelina Mango</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B19" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-02</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:59</v>
+        <v>2:16</v>
       </c>
       <c r="H19" t="str">
-        <v>Julio Iglesias</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-02</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:59</v>
+        <v>3:08</v>
       </c>
       <c r="H20" t="str">
-        <v>Loreen</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-02</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:58</v>
+        <v>3:38</v>
       </c>
       <c r="H21" t="str">
-        <v>Jessie Ware</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B22" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-02</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:49</v>
+        <v>3:01</v>
       </c>
       <c r="H22" t="str">
-        <v>Holly Humberstone</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B23" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-02</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:22</v>
+        <v>3:59</v>
       </c>
       <c r="H23" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-02</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:50</v>
+        <v>2:59</v>
       </c>
       <c r="H24" t="str">
-        <v>Ella Langley</v>
+        <v>Loreen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-02</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>6:43</v>
+        <v>2:58</v>
       </c>
       <c r="H25" t="str">
-        <v>David Gilmour</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B26" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-02</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:52</v>
+        <v>3:49</v>
       </c>
       <c r="H26" t="str">
-        <v>Eagles</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-02</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:13</v>
+        <v>3:22</v>
       </c>
       <c r="H27" t="str">
-        <v>Moody Joody</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-02</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:28</v>
+        <v>3:50</v>
       </c>
       <c r="H28" t="str">
-        <v>Jackson Dean</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-02</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:01</v>
+        <v>6:43</v>
       </c>
       <c r="H29" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-02</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:00</v>
+        <v>4:52</v>
       </c>
       <c r="H30" t="str">
-        <v>Madison Cunningham</v>
+        <v>Eagles</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-02</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:35</v>
+        <v>3:13</v>
       </c>
       <c r="H31" t="str">
-        <v>mary in the junkyard</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-02</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H32" t="str">
-        <v>Adam Sanders</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>11d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-02</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>11d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:40</v>
+        <v>3:01</v>
       </c>
       <c r="H33" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B34" t="str">
-        <v>11d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-02</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>11d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:25</v>
+        <v>4:00</v>
       </c>
       <c r="H34" t="str">
-        <v>twocolors</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B35" t="str">
-        <v>12d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-02</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:42</v>
+        <v>5:35</v>
       </c>
       <c r="H35" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>12d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-02</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:56</v>
+        <v>3:01</v>
       </c>
       <c r="H36" t="str">
-        <v>Prince</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B37" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-02</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>5:12</v>
+        <v>3:40</v>
       </c>
       <c r="H37" t="str">
-        <v>RAYE</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-02</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:30</v>
+        <v>2:25</v>
       </c>
       <c r="H38" t="str">
-        <v>The Warning</v>
+        <v>twocolors</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B39" t="str">
-        <v>13d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-02</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:18</v>
+        <v>3:42</v>
       </c>
       <c r="H39" t="str">
-        <v>Pentatonix</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B40" t="str">
-        <v>13d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-02</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>13d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:33</v>
+        <v>3:56</v>
       </c>
       <c r="H40" t="str">
-        <v>Tenille Townes</v>
+        <v>Prince</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-02</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:53</v>
+        <v>5:12</v>
       </c>
       <c r="H41" t="str">
-        <v>Jessie Ware</v>
+        <v>RAYE</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-02</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:37</v>
+        <v>3:30</v>
       </c>
       <c r="H42" t="str">
-        <v>Niall Horan</v>
+        <v>The Warning</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-02</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H43" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-02</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:40</v>
+        <v>3:33</v>
       </c>
       <c r="H44" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-02</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:30</v>
+        <v>5:53</v>
       </c>
       <c r="H45" t="str">
-        <v>Jackson Dean</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B46" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-02</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:02</v>
+        <v>2:37</v>
       </c>
       <c r="H46" t="str">
-        <v>Foo Fighters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B47" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-02</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:40</v>
+        <v>2:26</v>
       </c>
       <c r="H47" t="str">
-        <v>Dermot Kennedy</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-02</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:22</v>
+        <v>2:40</v>
       </c>
       <c r="H48" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B49" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-02</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:47</v>
+        <v>3:30</v>
       </c>
       <c r="H49" t="str">
-        <v>Ella Langley</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-02</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:39</v>
+        <v>4:02</v>
       </c>
       <c r="H50" t="str">
-        <v>Cannons</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B51" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-02</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:10</v>
+        <v>3:40</v>
       </c>
       <c r="H51" t="str">
-        <v>Luke Combs</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-02</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:47</v>
+        <v>2:22</v>
       </c>
       <c r="H52" t="str">
-        <v>Nessa Barrett</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-02</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:14</v>
+        <v>3:47</v>
       </c>
       <c r="H53" t="str">
-        <v>aron!</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-02</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:00</v>
+        <v>3:39</v>
       </c>
       <c r="H54" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Cannons</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-02</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:56</v>
+        <v>4:10</v>
       </c>
       <c r="H55" t="str">
-        <v>DMA'S</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B56" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-02</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:17</v>
+        <v>4:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-02</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:17</v>
+        <v>2:14</v>
       </c>
       <c r="H57" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>aron!</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-02</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:31</v>
+        <v>4:00</v>
       </c>
       <c r="H58" t="str">
-        <v>Nick Carter</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-02</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:38</v>
+        <v>3:56</v>
       </c>
       <c r="H59" t="str">
-        <v>Carly Pearce</v>
+        <v>DMA'S</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-02</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:11</v>
+        <v>3:17</v>
       </c>
       <c r="H60" t="str">
-        <v>OneRepublic</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-02</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:57</v>
+        <v>3:17</v>
       </c>
       <c r="H61" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-02</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:47</v>
+        <v>3:31</v>
       </c>
       <c r="H62" t="str">
-        <v>Armin van Buuren</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-02</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>7:10</v>
+        <v>3:38</v>
       </c>
       <c r="H63" t="str">
-        <v>David Gilmour</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-02</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:06</v>
+        <v>4:11</v>
       </c>
       <c r="H64" t="str">
-        <v>Grace Enger</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-02</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:05</v>
+        <v>2:57</v>
       </c>
       <c r="H65" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-02</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:12</v>
+        <v>3:47</v>
       </c>
       <c r="H66" t="str">
-        <v>Freya Ridings</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-02</v>
@@ -2921,10 +2921,10 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>9:11</v>
+        <v>7:10</v>
       </c>
       <c r="H67" t="str">
         <v>David Gilmour</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-02</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:49</v>
+        <v>3:06</v>
       </c>
       <c r="H68" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-02</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:28</v>
+        <v>3:05</v>
       </c>
       <c r="H69" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-02</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:31</v>
+        <v>3:12</v>
       </c>
       <c r="H70" t="str">
-        <v>Martin Garrix</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-02</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:11</v>
+        <v>9:11</v>
       </c>
       <c r="H71" t="str">
-        <v>Baby Queen</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-02</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:27</v>
+        <v>3:49</v>
       </c>
       <c r="H72" t="str">
-        <v>HAUSER</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-02</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:34</v>
+        <v>3:28</v>
       </c>
       <c r="H73" t="str">
-        <v>Holly Humberstone</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-02</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:50</v>
+        <v>3:31</v>
       </c>
       <c r="H74" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-02</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H75" t="str">
-        <v>Rick Astley</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-02</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:39</v>
+        <v>2:27</v>
       </c>
       <c r="H76" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>HAUSER</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-02</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>5:08</v>
+        <v>3:34</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie J</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-02</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:46</v>
+        <v>2:50</v>
       </c>
       <c r="H78" t="str">
-        <v>Bishop Briggs</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-02</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:42</v>
+        <v>3:51</v>
       </c>
       <c r="H79" t="str">
-        <v>Dean Lewis</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-02</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:31</v>
+        <v>2:39</v>
       </c>
       <c r="H80" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-02</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:14</v>
+        <v>5:08</v>
       </c>
       <c r="H81" t="str">
-        <v>Luke Combs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-02</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:22</v>
+        <v>3:46</v>
       </c>
       <c r="H82" t="str">
-        <v>Allison Russell</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-02</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H83" t="str">
-        <v>We Three</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-02</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:54</v>
+        <v>2:31</v>
       </c>
       <c r="H84" t="str">
-        <v>paris jackson</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-02</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:46</v>
+        <v>3:14</v>
       </c>
       <c r="H85" t="str">
-        <v>Kane Brown</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-02</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:37</v>
+        <v>3:22</v>
       </c>
       <c r="H86" t="str">
-        <v>Lainey Wilson</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-02</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:57</v>
+        <v>3:43</v>
       </c>
       <c r="H87" t="str">
-        <v>Malcolm Todd</v>
+        <v>We Three</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-02</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:38</v>
+        <v>2:54</v>
       </c>
       <c r="H88" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>paris jackson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-02</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:29</v>
+        <v>2:46</v>
       </c>
       <c r="H89" t="str">
-        <v>Kungs</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-02</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:28</v>
+        <v>3:37</v>
       </c>
       <c r="H90" t="str">
-        <v>Sunday (1994)</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-02</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>2:57</v>
       </c>
       <c r="H91" t="str">
-        <v>aron!</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-02</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:51</v>
+        <v>3:38</v>
       </c>
       <c r="H92" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-02</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:49</v>
+        <v>4:29</v>
       </c>
       <c r="H93" t="str">
-        <v>Sunday (1994)</v>
+        <v>Kungs</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-02</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:16</v>
+        <v>4:28</v>
       </c>
       <c r="H94" t="str">
-        <v>Owen Riegling</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-02</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:16</v>
+        <v>3:26</v>
       </c>
       <c r="H95" t="str">
-        <v>LANY</v>
+        <v>aron!</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-02</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:25</v>
+        <v>3:51</v>
       </c>
       <c r="H96" t="str">
-        <v>Maverick Sabre</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-02</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:50</v>
+        <v>2:49</v>
       </c>
       <c r="H97" t="str">
-        <v>Amanda Jordan</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-02</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>4:16</v>
       </c>
       <c r="H98" t="str">
-        <v>Beabadoobee</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-02</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:58</v>
+        <v>4:16</v>
       </c>
       <c r="H99" t="str">
-        <v>Spacey Jane</v>
+        <v>LANY</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-02</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:25</v>
       </c>
       <c r="H100" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-02</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:09</v>
+        <v>2:50</v>
       </c>
       <c r="H101" t="str">
-        <v>Mei Semones</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>CHICA 305</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-02</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>CHICA 305 - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:08</v>
+        <v>3:57</v>
       </c>
       <c r="H102" t="str">
-        <v>John Summit</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>CHICA 305 - John Summit</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-02</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>2:32</v>
+        <v>3:58</v>
       </c>
       <c r="H103" t="str">
-        <v>In Color</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Days We Left Behind</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:18</v>
+        <v>3:25</v>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:47</v>
+        <v>4:09</v>
       </c>
       <c r="H105" t="str">
-        <v>Miley Cyrus</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>Buy Me A Car</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/buy-me-a-car/1887659688</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Buy Me A Car - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>6:17</v>
+        <v>3:29</v>
       </c>
       <c r="H106" t="str">
-        <v>RAYE</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/buy-me-a-car/1887659405</v>
       </c>
       <c r="L106" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>Buy Me A Car - Presley Regier</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>MARATHON</v>
+        <v>CHICA 305</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>MARATHON - Single</v>
+        <v>CHICA 305 - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:49</v>
+        <v>3:08</v>
       </c>
       <c r="H107" t="str">
-        <v>Becky G</v>
+        <v>John Summit</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
       </c>
       <c r="L107" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>CHICA 305 - John Summit</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ALL THE TIME</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>3:18</v>
       </c>
       <c r="H108" t="str">
-        <v>John Summit</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L108" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Sucker For Love</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sexistential</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:34</v>
+        <v>2:47</v>
       </c>
       <c r="H109" t="str">
-        <v>Robyn</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L109" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>FATHER</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>BULLY</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G110" t="str">
-        <v>2:49</v>
+        <v>6:17</v>
       </c>
       <c r="H110" t="str">
-        <v>Kanye West</v>
+        <v>RAYE</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L110" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Lose Control</v>
+        <v>MARATHON</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ADL</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>2:49</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>Becky G</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L111" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Zavier</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>3:00</v>
       </c>
       <c r="H112" t="str">
-        <v>Fetty Wap</v>
+        <v>John Summit</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WAGWAN</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>Sexistential</v>
       </c>
       <c r="G113" t="str">
-        <v>2:07</v>
+        <v>3:34</v>
       </c>
       <c r="H113" t="str">
-        <v>Central Cee</v>
+        <v>Robyn</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L113" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sideways</v>
+        <v>FATHER</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>KONNAKOL</v>
+        <v>BULLY</v>
       </c>
       <c r="G114" t="str">
-        <v>3:12</v>
+        <v>2:49</v>
       </c>
       <c r="H114" t="str">
-        <v>ZAYN</v>
+        <v>Kanye West</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L114" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Automatic</v>
+        <v>Lose Control</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Superbloom</v>
+        <v>ADL</v>
       </c>
       <c r="G115" t="str">
-        <v>2:57</v>
+        <v>2:39</v>
       </c>
       <c r="H115" t="str">
-        <v>Jessie Ware</v>
+        <v>Yeat</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L115" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tractor Beam</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ricochet</v>
+        <v>Zavier</v>
       </c>
       <c r="G116" t="str">
-        <v>3:34</v>
+        <v>3:44</v>
       </c>
       <c r="H116" t="str">
-        <v>Snail Mail</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L116" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Home on the Range</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G117" t="str">
-        <v>1:37</v>
+        <v>2:07</v>
       </c>
       <c r="H117" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Central Cee</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L117" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>prom queen</v>
+        <v>Sideways</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>prom queen - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G118" t="str">
-        <v>2:43</v>
+        <v>3:12</v>
       </c>
       <c r="H118" t="str">
-        <v>Amelia Moore</v>
+        <v>ZAYN</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L118" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Back Home</v>
+        <v>Automatic</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Superbloom</v>
       </c>
       <c r="G119" t="str">
-        <v>1:36</v>
+        <v>2:57</v>
       </c>
       <c r="H119" t="str">
-        <v>MIKE</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L119" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Pal Agua</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G120" t="str">
-        <v>3:26</v>
+        <v>3:34</v>
       </c>
       <c r="H120" t="str">
-        <v>J Balvin</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L120" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Phoenix</v>
+        <v>Jet Lag Mouth</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Phoenix - Single</v>
+        <v>Jet Lag Mouth - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:24</v>
+        <v>2:32</v>
       </c>
       <c r="H121" t="str">
-        <v>Marshmello</v>
+        <v>In Color</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
       </c>
       <c r="L121" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Jet Lag Mouth - In Color</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>prom queen</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:56</v>
+        <v>2:43</v>
       </c>
       <c r="H122" t="str">
-        <v>Ne-Yo</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L122" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Feel Your Rain</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G123" t="str">
-        <v>3:36</v>
+        <v>1:37</v>
       </c>
       <c r="H123" t="str">
-        <v>Eli</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L123" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Lonely</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ö</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H124" t="str">
-        <v>Fcukers</v>
+        <v>J Balvin</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L124" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Back in Love</v>
+        <v>Phoenix</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Back in Love - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:14</v>
+        <v>2:24</v>
       </c>
       <c r="H125" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Marshmello</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L125" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Sideways</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:55</v>
+        <v>2:56</v>
       </c>
       <c r="H126" t="str">
-        <v>Charlie Puth</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L126" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Honora</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:22</v>
+        <v>3:36</v>
       </c>
       <c r="H127" t="str">
-        <v>Flea</v>
+        <v>Eli</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L127" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Lonely</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G128" t="str">
         <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Fcukers</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Shame</v>
+        <v>Back in Love</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/shame/1887698916</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Shame - Single</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:02</v>
+        <v>3:14</v>
       </c>
       <c r="H129" t="str">
-        <v>BunnaB</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/bunnab/1695734940</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/shame/1887698914</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L129" t="str">
-        <v>Shame - BunnaB</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>One Thing At A Time</v>
+        <v>Sideways</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Creature of Habit</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G130" t="str">
-        <v>4:42</v>
+        <v>3:55</v>
       </c>
       <c r="H130" t="str">
-        <v>Courtney Barnett</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L130" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>wasteland</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>wasteland - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G131" t="str">
-        <v>3:05</v>
+        <v>4:22</v>
       </c>
       <c r="H131" t="str">
-        <v>Yuna</v>
+        <v>Flea</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L131" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>getting up to no good</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:31</v>
+        <v>2:58</v>
       </c>
       <c r="H132" t="str">
-        <v>Artemas</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L132" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Por LA</v>
+        <v>Shame</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/shame/1887698916</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>TODO Ø NADA</v>
+        <v>Shame - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:19</v>
+        <v>3:02</v>
       </c>
       <c r="H133" t="str">
-        <v>Linea Personal</v>
+        <v>BunnaB</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/bunnab/1695734940</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/shame/1887698914</v>
       </c>
       <c r="L133" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>Shame - BunnaB</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>You Lead Me</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G134" t="str">
-        <v>4:14</v>
+        <v>4:42</v>
       </c>
       <c r="H134" t="str">
-        <v>Lauren Daigle</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L134" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Just A Kid</v>
+        <v>wasteland</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Broken View</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>4:18</v>
+        <v>3:05</v>
       </c>
       <c r="H135" t="str">
-        <v>Sam Barber</v>
+        <v>Yuna</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L135" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Country And She Knows It</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G136" t="str">
-        <v>2:54</v>
+        <v>2:31</v>
       </c>
       <c r="H136" t="str">
-        <v>Luke Bryan</v>
+        <v>Artemas</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L136" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Georgia On My Mind</v>
+        <v>Por LA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G137" t="str">
-        <v>2:35</v>
+        <v>2:19</v>
       </c>
       <c r="H137" t="str">
-        <v>Thomas Rhett</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L137" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Deep Blue</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Deep Blue</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G138" t="str">
-        <v>3:17</v>
+        <v>4:14</v>
       </c>
       <c r="H138" t="str">
-        <v>ERNEST</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L138" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Special</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>sounds for someone</v>
+        <v>Broken View</v>
       </c>
       <c r="G139" t="str">
-        <v>2:49</v>
+        <v>4:18</v>
       </c>
       <c r="H139" t="str">
-        <v>Elmiene</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L139" t="str">
-        <v>Special - Elmiene</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Heart Attack</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>CANDY</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:52</v>
+        <v>2:54</v>
       </c>
       <c r="H140" t="str">
-        <v>Justine Skye</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L140" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>STAY</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>STAY - Single</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:06</v>
+        <v>2:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Stray Kids</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L141" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Unglued</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Work of Heart</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G142" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>ERNEST</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L142" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Ritual</v>
+        <v>Special</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Ritual - Single</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G143" t="str">
-        <v>3:01</v>
+        <v>2:49</v>
       </c>
       <c r="H143" t="str">
-        <v>Icona Pop</v>
+        <v>Elmiene</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L143" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>The Best</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>CANDY</v>
       </c>
       <c r="G144" t="str">
-        <v>3:48</v>
+        <v>2:52</v>
       </c>
       <c r="H144" t="str">
-        <v>Conan Gray</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L144" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Smile</v>
+        <v>STAY</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Smile - Single</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:50</v>
+        <v>3:06</v>
       </c>
       <c r="H145" t="str">
-        <v>Two Shell</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L145" t="str">
-        <v>Smile - Two Shell</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Duro</v>
+        <v>Unglued</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Duro - Single</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G146" t="str">
-        <v>3:05</v>
+        <v>3:54</v>
       </c>
       <c r="H146" t="str">
-        <v>Skrillex</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L146" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Ritual</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:58</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>Sublime</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L147" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Carousel</v>
+        <v>The Best</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Everything Glows</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G148" t="str">
-        <v>3:36</v>
+        <v>3:48</v>
       </c>
       <c r="H148" t="str">
-        <v>Cannons</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L148" t="str">
-        <v>Carousel - Cannons</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Mercy</v>
+        <v>Smile</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Mercy - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:49</v>
+        <v>3:50</v>
       </c>
       <c r="H149" t="str">
-        <v>PRESIDENT</v>
+        <v>Two Shell</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L149" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Palms</v>
+        <v>Duro</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Palms - Single</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:18</v>
+        <v>3:05</v>
       </c>
       <c r="H150" t="str">
-        <v>The Maine</v>
+        <v>Skrillex</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L150" t="str">
-        <v>Palms - The Maine</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ozzy's Song</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G151" t="str">
-        <v>5:28</v>
+        <v>2:58</v>
       </c>
       <c r="H151" t="str">
-        <v>Black Label Society</v>
+        <v>Sublime</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L151" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Danger</v>
+        <v>Carousel</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Danger - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G152" t="str">
-        <v>2:19</v>
+        <v>3:36</v>
       </c>
       <c r="H152" t="str">
-        <v>Nia Archives</v>
+        <v>Cannons</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L152" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Icarus</v>
+        <v>Mercy</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Icarus - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>4:25</v>
+        <v>3:49</v>
       </c>
       <c r="H153" t="str">
-        <v>Olivia O'Brien</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L153" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>idk idk</v>
+        <v>Palms</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>idk idk - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H154" t="str">
-        <v>Jim Legxacy</v>
+        <v>The Maine</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L154" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tonight</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Tonight - Single</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G155" t="str">
-        <v>2:25</v>
+        <v>5:28</v>
       </c>
       <c r="H155" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L155" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Danger</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Switcheroo</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H156" t="str">
-        <v>Gelli Haha</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L156" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>Icarus</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:45</v>
+        <v>4:25</v>
       </c>
       <c r="H157" t="str">
-        <v>BIA</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L157" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>this girl wants everything</v>
+        <v>idk idk</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:33</v>
+        <v>2:26</v>
       </c>
       <c r="H158" t="str">
-        <v>Isaia Huron</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L158" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>Tonight</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:44</v>
+        <v>2:25</v>
       </c>
       <c r="H159" t="str">
-        <v>Slayyyter</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L159" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Deep Water - EP</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G160" t="str">
-        <v>2:41</v>
+        <v>3:44</v>
       </c>
       <c r="H160" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L160" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>R3verse</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>takeaways</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G161" t="str">
-        <v>3:31</v>
+        <v>2:45</v>
       </c>
       <c r="H161" t="str">
-        <v>Medium Build</v>
+        <v>BIA</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L161" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G162" t="str">
-        <v>2:32</v>
+        <v>3:33</v>
       </c>
       <c r="H162" t="str">
-        <v>MIKE</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L162" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>heart of gold</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>heart of gold - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G163" t="str">
-        <v>2:51</v>
+        <v>3:44</v>
       </c>
       <c r="H163" t="str">
-        <v>kai devega</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L163" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Breaking Down</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Skeletor</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>4:21</v>
+        <v>2:41</v>
       </c>
       <c r="H164" t="str">
-        <v>Chief Keef</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L164" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Dream House</v>
+        <v>R3verse</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream House - Single</v>
+        <v>takeaways</v>
       </c>
       <c r="G165" t="str">
-        <v>2:54</v>
+        <v>3:31</v>
       </c>
       <c r="H165" t="str">
-        <v>Empress Of</v>
+        <v>Medium Build</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L165" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Baby Blue</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G166" t="str">
-        <v>2:51</v>
+        <v>2:32</v>
       </c>
       <c r="H166" t="str">
-        <v>Cody Simpson</v>
+        <v>MIKE</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L166" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>heart of gold</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:37</v>
+        <v>2:51</v>
       </c>
       <c r="H167" t="str">
-        <v>MEDUZA</v>
+        <v>kai devega</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Forever Now</v>
+        <v>Skeletor</v>
       </c>
       <c r="G168" t="str">
-        <v>4:05</v>
+        <v>4:21</v>
       </c>
       <c r="H168" t="str">
-        <v>Switchfoot</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L168" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Dream House</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:46</v>
+        <v>2:54</v>
       </c>
       <c r="H169" t="str">
-        <v>Benny G</v>
+        <v>Empress Of</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L169" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:03</v>
+        <v>2:51</v>
       </c>
       <c r="H170" t="str">
-        <v>Eric Bellinger</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L170" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>4:19</v>
+        <v>2:37</v>
       </c>
       <c r="H171" t="str">
-        <v>Anish Kumar</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L171" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>GASLIGHT</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G172" t="str">
-        <v>2:10</v>
+        <v>4:05</v>
       </c>
       <c r="H172" t="str">
-        <v>WesGhost</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L172" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Truth To Be Told</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:17</v>
+        <v>3:46</v>
       </c>
       <c r="H173" t="str">
-        <v>GERD</v>
+        <v>Benny G</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L173" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Free Your Mind</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:21</v>
+        <v>3:03</v>
       </c>
       <c r="H174" t="str">
-        <v>Prospa</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L174" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Down To The Bone</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>2:51</v>
+        <v>4:19</v>
       </c>
       <c r="H175" t="str">
-        <v>Josh Baker</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L175" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Breathe</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Breathe - Single</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:48</v>
+        <v>2:10</v>
       </c>
       <c r="H176" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>WesGhost</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L176" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>xs</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>xs - Single</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:19</v>
+        <v>3:17</v>
       </c>
       <c r="H177" t="str">
-        <v>Ashley Cooke</v>
+        <v>GERD</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L177" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Sail</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:54</v>
+        <v>3:21</v>
       </c>
       <c r="H178" t="str">
-        <v>Future Islands</v>
+        <v>Prospa</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L178" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Dreaming</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Dear Nashville</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:33</v>
+        <v>2:51</v>
       </c>
       <c r="H179" t="str">
-        <v>Ashley Monroe</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L179" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>NEW TINGZ</v>
+        <v>Breathe</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:39</v>
+        <v>2:48</v>
       </c>
       <c r="H180" t="str">
-        <v>Armanii</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L180" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>La Opinión</v>
+        <v>xs</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Mis Compas El Final</v>
+        <v>xs - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>3:19</v>
       </c>
       <c r="H181" t="str">
-        <v>Joss Favela</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L181" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>qué ves en mí?</v>
+        <v>Sail</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G182" t="str">
-        <v>3:24</v>
+        <v>4:54</v>
       </c>
       <c r="H182" t="str">
-        <v>Paloma Morphy</v>
+        <v>Future Islands</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L182" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>Dreaming</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G183" t="str">
-        <v>2:43</v>
+        <v>3:33</v>
       </c>
       <c r="H183" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L183" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>TUTUTU</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>TUTUTU - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G184" t="str">
-        <v>2:16</v>
+        <v>2:39</v>
       </c>
       <c r="H184" t="str">
-        <v>ELENA ROSE</v>
+        <v>Armanii</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L184" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>La Opinión</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G185" t="str">
-        <v>2:56</v>
+        <v>3:23</v>
       </c>
       <c r="H185" t="str">
-        <v>2'Live Bre</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Me Neither</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Heavy On The Soul</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:32</v>
+        <v>3:24</v>
       </c>
       <c r="H186" t="str">
-        <v>Ty Myers</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L186" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Cole Palmer</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Solid Ground</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:48</v>
+        <v>2:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Limoblaze</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L187" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Wonder</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Wonder - Single</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:48</v>
+        <v>2:16</v>
       </c>
       <c r="H188" t="str">
-        <v>Meeks Carter</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L188" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ICU</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>ICU - Single</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:53</v>
+        <v>2:56</v>
       </c>
       <c r="H189" t="str">
-        <v>Joseph O'Brien</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L189" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Me Neither</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G190" t="str">
-        <v>2:45</v>
+        <v>3:32</v>
       </c>
       <c r="H190" t="str">
-        <v>Jozzy</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L190" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Waiting Room (feat. Jordan Ward)</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Single</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G191" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H191" t="str">
-        <v>Jenevieve</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L191" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Wonder</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Rise</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:02</v>
+        <v>3:48</v>
       </c>
       <c r="H192" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L192" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Roll On Thru</v>
+        <v>ICU</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:51</v>
+        <v>2:53</v>
       </c>
       <c r="H193" t="str">
-        <v>Hayden Everett</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L193" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Delicately</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Delicately - Single</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>2:45</v>
       </c>
       <c r="H194" t="str">
-        <v>Andrea Bejar</v>
+        <v>Jozzy</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L194" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>One Of Those Things</v>
+        <v>Waiting Room (feat. Jordan Ward)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Waiting Room (feat. Jordan Ward) - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:27</v>
+        <v>3:21</v>
       </c>
       <c r="H195" t="str">
-        <v>Lucy Clearwater</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
       </c>
       <c r="L195" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>For Every Dusk</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Rise</v>
       </c>
       <c r="G196" t="str">
-        <v>6:04</v>
+        <v>4:02</v>
       </c>
       <c r="H196" t="str">
-        <v>José González</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L196" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I'll Wait</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:33</v>
+        <v>3:51</v>
       </c>
       <c r="H197" t="str">
-        <v>Buzzy Lee</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L197" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Daisy</v>
+        <v>Delicately</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-02</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Daisy - Single</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:02</v>
+        <v>3:20</v>
       </c>
       <c r="H198" t="str">
-        <v>Lola Blue</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L198" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-02</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Friend Remixes</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:57</v>
+        <v>3:27</v>
       </c>
       <c r="H199" t="str">
-        <v>james K</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L199" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-02</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Perdidos - Single</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G200" t="str">
-        <v>2:45</v>
+        <v>6:04</v>
       </c>
       <c r="H200" t="str">
-        <v>MAVICA</v>
+        <v>José González</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L200" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Fort</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-02</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Fort - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G201" t="str">
-        <v>2:27</v>
+        <v>3:33</v>
       </c>
       <c r="H201" t="str">
-        <v>Lamb</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L201" t="str">
-        <v>Fort - Lamb</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SAME LA</v>
+        <v>Daisy</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-02</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>SAME LA - Single</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:44</v>
+        <v>3:02</v>
       </c>
       <c r="H202" t="str">
-        <v>Tiffany Day</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L202" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Working On It</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-02</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Working On It - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H203" t="str">
-        <v>Arthur Hill</v>
+        <v>james K</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L203" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>spring cleaning</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-02</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>4:03</v>
+        <v>2:45</v>
       </c>
       <c r="H204" t="str">
-        <v>Ethan Regan</v>
+        <v>MAVICA</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L204" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Just Drivin'</v>
+        <v>Fort</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D205" t="str">
         <v>2026-04-02</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:26</v>
+        <v>2:27</v>
       </c>
       <c r="H205" t="str">
-        <v>Presley Haile</v>
+        <v>Lamb</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L205" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Simple Things</v>
+        <v>SAME LA</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D206" t="str">
         <v>2026-04-02</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Simple Things - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:46</v>
+        <v>3:44</v>
       </c>
       <c r="H206" t="str">
-        <v>Evening Elephants</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L206" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Want It Back</v>
+        <v>Working On It</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D207" t="str">
         <v>2026-04-02</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Want It Back - Single</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:27</v>
+        <v>3:06</v>
       </c>
       <c r="H207" t="str">
-        <v>Giant Rooks</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L207" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Bite Down</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D208" t="str">
         <v>2026-04-02</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Bite Down - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>3:36</v>
+        <v>4:03</v>
       </c>
       <c r="H208" t="str">
-        <v>Anna Sofia</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L208" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D209" t="str">
         <v>2026-04-02</v>
@@ -8317,36 +8317,36 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G209" t="str">
-        <v>5:42</v>
+        <v>3:26</v>
       </c>
       <c r="H209" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L209" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Demons</v>
+        <v>Simple Things</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D210" t="str">
         <v>2026-04-02</v>
@@ -8355,36 +8355,36 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G210" t="str">
-        <v>2:42</v>
+        <v>3:46</v>
       </c>
       <c r="H210" t="str">
-        <v>Anella</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L210" t="str">
-        <v>Demons - Anella</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Es brennt...</v>
+        <v>Want It Back</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D211" t="str">
         <v>2026-04-02</v>
@@ -8393,36 +8393,36 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G211" t="str">
-        <v>3:35</v>
+        <v>3:27</v>
       </c>
       <c r="H211" t="str">
-        <v>Till Lindemann</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L211" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Fire Marengo</v>
+        <v>Bite Down</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D212" t="str">
         <v>2026-04-02</v>
@@ -8431,68 +8431,258 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G212" t="str">
-        <v>3:49</v>
+        <v>3:36</v>
       </c>
       <c r="H212" t="str">
-        <v>Enslaved</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I212" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L212" t="str">
-        <v>Fire Marengo - Enslaved</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
+        <v>Ulvgjeld &amp; Blodsodel</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>Grand Serpent Rising</v>
+      </c>
+      <c r="G213" t="str">
+        <v>5:42</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Dimmu Borgir</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Demons</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>Ask Me How I’ve Been</v>
+      </c>
+      <c r="G214" t="str">
+        <v>2:42</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Anella</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Demons - Anella</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Es brennt...</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>Es brennt... - Single</v>
+      </c>
+      <c r="G215" t="str">
+        <v>3:35</v>
+      </c>
+      <c r="H215" t="str">
+        <v>Till Lindemann</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Es brennt... - Till Lindemann</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>Fire Marengo</v>
+      </c>
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+      </c>
+      <c r="D216" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+      </c>
+      <c r="G216" t="str">
+        <v>3:49</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Enslaved</v>
+      </c>
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+      </c>
+      <c r="K216" t="str">
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Fire Marengo - Enslaved</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
         <v>Close to the Bone</v>
       </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
+      <c r="B217" t="str">
+        <v/>
+      </c>
+      <c r="C217" t="str">
         <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
-      <c r="D213" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
+      <c r="D217" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
         <v>Emotion Factory Reset</v>
       </c>
-      <c r="G213" t="str">
+      <c r="G217" t="str">
         <v>4:09</v>
       </c>
-      <c r="H213" t="str">
+      <c r="H217" t="str">
         <v>Armored Saint</v>
       </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
+      <c r="I217" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J217" t="str">
         <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
-      <c r="K213" t="str">
+      <c r="K217" t="str">
         <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
-      <c r="L213" t="str">
+      <c r="L217" t="str">
         <v>Close to the Bone - Armored Saint</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Back Home</v>
+      </c>
+      <c r="B218" t="str">
+        <v/>
+      </c>
+      <c r="C218" t="str">
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+      </c>
+      <c r="D218" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v>POMPEII // UTILITY</v>
+      </c>
+      <c r="G218" t="str">
+        <v>1:36</v>
+      </c>
+      <c r="H218" t="str">
+        <v>MIKE</v>
+      </c>
+      <c r="I218" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J218" t="str">
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+      </c>
+      <c r="K218" t="str">
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Back Home - MIKE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L218"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L218"/>
+  <dimension ref="A1:L214"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410326&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-02</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:55</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ששון - היא יודעת קאבר</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410325&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-02</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2:45</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Ocean Alley</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ששון - היא יודעת קאבר</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נהוראי אברהם - מישל קאבר</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-02</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410324&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-02</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>6:29</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>RAYE</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נהוראי אברהם - מישל קאבר</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-02</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410323&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-02</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Take That</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-02</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:55</v>
+        <v>4:22</v>
       </c>
       <c r="H6" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Armik</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-02</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:45</v>
+        <v>4:10</v>
       </c>
       <c r="H7" t="str">
-        <v>Ocean Alley</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-02</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>6:29</v>
+        <v>3:19</v>
       </c>
       <c r="H8" t="str">
-        <v>RAYE</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-02</v>
@@ -720,10 +720,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:17</v>
+        <v>3:03</v>
       </c>
       <c r="H9" t="str">
-        <v>Take That</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B10" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-02</v>
@@ -758,10 +758,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:22</v>
+        <v>3:56</v>
       </c>
       <c r="H10" t="str">
-        <v>Armik</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-02</v>
@@ -796,10 +796,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:10</v>
+        <v>3:58</v>
       </c>
       <c r="H11" t="str">
-        <v>Switchfoot</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B12" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-02</v>
@@ -834,10 +834,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:19</v>
+        <v>3:56</v>
       </c>
       <c r="H12" t="str">
-        <v>Peter Gabriel</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B13" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-02</v>
@@ -872,10 +872,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:03</v>
+        <v>2:50</v>
       </c>
       <c r="H13" t="str">
-        <v>Sarah Julia</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-02</v>
@@ -910,10 +910,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:56</v>
+        <v>3:42</v>
       </c>
       <c r="H14" t="str">
-        <v>Chris Norman</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B15" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-02</v>
@@ -948,10 +948,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:58</v>
+        <v>2:16</v>
       </c>
       <c r="H15" t="str">
-        <v>Alan Walker</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-02</v>
@@ -986,10 +986,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:56</v>
+        <v>3:08</v>
       </c>
       <c r="H16" t="str">
-        <v>Charlie Puth</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-02</v>
@@ -1024,10 +1024,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:50</v>
+        <v>3:38</v>
       </c>
       <c r="H17" t="str">
-        <v>Miley Cyrus</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B18" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-02</v>
@@ -1062,10 +1062,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:42</v>
+        <v>3:01</v>
       </c>
       <c r="H18" t="str">
-        <v>Conan Gray</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-02</v>
@@ -1100,10 +1100,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:16</v>
+        <v>3:59</v>
       </c>
       <c r="H19" t="str">
-        <v>Charlie Puth</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-02</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:08</v>
+        <v>2:59</v>
       </c>
       <c r="H20" t="str">
-        <v>Kylie Morgan</v>
+        <v>Loreen</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-02</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H21" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-02</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:01</v>
+        <v>3:49</v>
       </c>
       <c r="H22" t="str">
-        <v>Angelina Mango</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-02</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:59</v>
+        <v>3:22</v>
       </c>
       <c r="H23" t="str">
-        <v>Julio Iglesias</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-02</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:59</v>
+        <v>3:50</v>
       </c>
       <c r="H24" t="str">
-        <v>Loreen</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-02</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:58</v>
+        <v>6:43</v>
       </c>
       <c r="H25" t="str">
-        <v>Jessie Ware</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-02</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:49</v>
+        <v>4:52</v>
       </c>
       <c r="H26" t="str">
-        <v>Holly Humberstone</v>
+        <v>Eagles</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-02</v>
@@ -1404,10 +1404,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:22</v>
+        <v>3:13</v>
       </c>
       <c r="H27" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-02</v>
@@ -1442,10 +1442,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:50</v>
+        <v>3:28</v>
       </c>
       <c r="H28" t="str">
-        <v>Ella Langley</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-02</v>
@@ -1480,10 +1480,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>6:43</v>
+        <v>3:01</v>
       </c>
       <c r="H29" t="str">
-        <v>David Gilmour</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B30" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-02</v>
@@ -1518,10 +1518,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:52</v>
+        <v>4:00</v>
       </c>
       <c r="H30" t="str">
-        <v>Eagles</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-02</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:13</v>
+        <v>5:35</v>
       </c>
       <c r="H31" t="str">
-        <v>Moody Joody</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-02</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H32" t="str">
-        <v>Jackson Dean</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-02</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:01</v>
+        <v>3:40</v>
       </c>
       <c r="H33" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-02</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:00</v>
+        <v>2:25</v>
       </c>
       <c r="H34" t="str">
-        <v>Madison Cunningham</v>
+        <v>twocolors</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-02</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:35</v>
+        <v>3:42</v>
       </c>
       <c r="H35" t="str">
-        <v>mary in the junkyard</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-02</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:01</v>
+        <v>3:56</v>
       </c>
       <c r="H36" t="str">
-        <v>Adam Sanders</v>
+        <v>Prince</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-02</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:40</v>
+        <v>5:12</v>
       </c>
       <c r="H37" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>RAYE</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-02</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:25</v>
+        <v>3:30</v>
       </c>
       <c r="H38" t="str">
-        <v>twocolors</v>
+        <v>The Warning</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-02</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:42</v>
+        <v>3:18</v>
       </c>
       <c r="H39" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-02</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:56</v>
+        <v>3:33</v>
       </c>
       <c r="H40" t="str">
-        <v>Prince</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B41" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-02</v>
@@ -1936,10 +1936,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:12</v>
+        <v>5:53</v>
       </c>
       <c r="H41" t="str">
-        <v>RAYE</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B42" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-02</v>
@@ -1974,10 +1974,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:30</v>
+        <v>2:37</v>
       </c>
       <c r="H42" t="str">
-        <v>The Warning</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B43" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-02</v>
@@ -2012,10 +2012,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:18</v>
+        <v>2:26</v>
       </c>
       <c r="H43" t="str">
-        <v>Pentatonix</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B44" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-02</v>
@@ -2050,10 +2050,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:33</v>
+        <v>2:40</v>
       </c>
       <c r="H44" t="str">
-        <v>Tenille Townes</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B45" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-02</v>
@@ -2088,10 +2088,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:53</v>
+        <v>3:30</v>
       </c>
       <c r="H45" t="str">
-        <v>Jessie Ware</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-02</v>
@@ -2126,10 +2126,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:37</v>
+        <v>4:02</v>
       </c>
       <c r="H46" t="str">
-        <v>Niall Horan</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-02</v>
@@ -2164,10 +2164,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:26</v>
+        <v>3:40</v>
       </c>
       <c r="H47" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-02</v>
@@ -2202,10 +2202,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:40</v>
+        <v>2:22</v>
       </c>
       <c r="H48" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-02</v>
@@ -2240,10 +2240,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:30</v>
+        <v>3:47</v>
       </c>
       <c r="H49" t="str">
-        <v>Jackson Dean</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-02</v>
@@ -2278,10 +2278,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:02</v>
+        <v>3:39</v>
       </c>
       <c r="H50" t="str">
-        <v>Foo Fighters</v>
+        <v>Cannons</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B51" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-02</v>
@@ -2316,10 +2316,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:40</v>
+        <v>4:10</v>
       </c>
       <c r="H51" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B52" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-02</v>
@@ -2354,10 +2354,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:22</v>
+        <v>4:47</v>
       </c>
       <c r="H52" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B53" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-02</v>
@@ -2392,10 +2392,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:47</v>
+        <v>2:14</v>
       </c>
       <c r="H53" t="str">
-        <v>Ella Langley</v>
+        <v>aron!</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B54" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-02</v>
@@ -2430,10 +2430,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:39</v>
+        <v>4:00</v>
       </c>
       <c r="H54" t="str">
-        <v>Cannons</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-02</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:10</v>
+        <v>3:56</v>
       </c>
       <c r="H55" t="str">
-        <v>Luke Combs</v>
+        <v>DMA'S</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-02</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:47</v>
+        <v>3:17</v>
       </c>
       <c r="H56" t="str">
-        <v>Nessa Barrett</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-02</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:14</v>
+        <v>3:17</v>
       </c>
       <c r="H57" t="str">
-        <v>aron!</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-02</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:00</v>
+        <v>3:31</v>
       </c>
       <c r="H58" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-02</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:56</v>
+        <v>3:38</v>
       </c>
       <c r="H59" t="str">
-        <v>DMA'S</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-02</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:17</v>
+        <v>4:11</v>
       </c>
       <c r="H60" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-02</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:17</v>
+        <v>2:57</v>
       </c>
       <c r="H61" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-02</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H62" t="str">
-        <v>Nick Carter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-02</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:38</v>
+        <v>7:10</v>
       </c>
       <c r="H63" t="str">
-        <v>Carly Pearce</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-02</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:11</v>
+        <v>3:06</v>
       </c>
       <c r="H64" t="str">
-        <v>OneRepublic</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-02</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:57</v>
+        <v>3:05</v>
       </c>
       <c r="H65" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-02</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:47</v>
+        <v>3:12</v>
       </c>
       <c r="H66" t="str">
-        <v>Armin van Buuren</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-02</v>
@@ -2924,7 +2924,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>7:10</v>
+        <v>9:11</v>
       </c>
       <c r="H67" t="str">
         <v>David Gilmour</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-02</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:06</v>
+        <v>3:49</v>
       </c>
       <c r="H68" t="str">
-        <v>Grace Enger</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-02</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:05</v>
+        <v>3:28</v>
       </c>
       <c r="H69" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-02</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:12</v>
+        <v>3:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Freya Ridings</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-02</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>9:11</v>
+        <v>3:11</v>
       </c>
       <c r="H71" t="str">
-        <v>David Gilmour</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-02</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:49</v>
+        <v>2:27</v>
       </c>
       <c r="H72" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>HAUSER</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-02</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:28</v>
+        <v>3:34</v>
       </c>
       <c r="H73" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-02</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:31</v>
+        <v>2:50</v>
       </c>
       <c r="H74" t="str">
-        <v>Martin Garrix</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-02</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H75" t="str">
-        <v>Baby Queen</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-02</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:27</v>
+        <v>2:39</v>
       </c>
       <c r="H76" t="str">
-        <v>HAUSER</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-02</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:34</v>
+        <v>5:08</v>
       </c>
       <c r="H77" t="str">
-        <v>Holly Humberstone</v>
+        <v>Jessie J</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-02</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:50</v>
+        <v>3:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-02</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:51</v>
+        <v>2:42</v>
       </c>
       <c r="H79" t="str">
-        <v>Rick Astley</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-02</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:39</v>
+        <v>2:31</v>
       </c>
       <c r="H80" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-02</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>5:08</v>
+        <v>3:14</v>
       </c>
       <c r="H81" t="str">
-        <v>Jessie J</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-02</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:46</v>
+        <v>3:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Bishop Briggs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-02</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:42</v>
+        <v>3:43</v>
       </c>
       <c r="H83" t="str">
-        <v>Dean Lewis</v>
+        <v>We Three</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-02</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:31</v>
+        <v>2:54</v>
       </c>
       <c r="H84" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>paris jackson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-02</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:14</v>
+        <v>2:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Luke Combs</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-02</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:22</v>
+        <v>3:37</v>
       </c>
       <c r="H86" t="str">
-        <v>Allison Russell</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-02</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:43</v>
+        <v>2:57</v>
       </c>
       <c r="H87" t="str">
-        <v>We Three</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-02</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:54</v>
+        <v>3:38</v>
       </c>
       <c r="H88" t="str">
-        <v>paris jackson</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-02</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:46</v>
+        <v>4:29</v>
       </c>
       <c r="H89" t="str">
-        <v>Kane Brown</v>
+        <v>Kungs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-02</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H90" t="str">
-        <v>Lainey Wilson</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-02</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Malcolm Todd</v>
+        <v>aron!</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-02</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:38</v>
+        <v>3:51</v>
       </c>
       <c r="H92" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-02</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:29</v>
+        <v>2:49</v>
       </c>
       <c r="H93" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-02</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:28</v>
+        <v>4:16</v>
       </c>
       <c r="H94" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-02</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:26</v>
+        <v>4:16</v>
       </c>
       <c r="H95" t="str">
-        <v>aron!</v>
+        <v>LANY</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-02</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:51</v>
+        <v>3:25</v>
       </c>
       <c r="H96" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-02</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:49</v>
+        <v>2:50</v>
       </c>
       <c r="H97" t="str">
-        <v>Sunday (1994)</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-02</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:16</v>
+        <v>3:57</v>
       </c>
       <c r="H98" t="str">
-        <v>Owen Riegling</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-02</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:16</v>
+        <v>3:58</v>
       </c>
       <c r="H99" t="str">
-        <v>LANY</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-02</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:25</v>
       </c>
       <c r="H100" t="str">
-        <v>Maverick Sabre</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-02</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:50</v>
+        <v>4:09</v>
       </c>
       <c r="H101" t="str">
-        <v>Amanda Jordan</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Buy Me A Car</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://music.apple.com/us/song/buy-me-a-car/1887659688</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-02</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>Buy Me A Car - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:57</v>
+        <v>3:29</v>
       </c>
       <c r="H102" t="str">
-        <v>Beabadoobee</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/buy-me-a-car/1887659405</v>
       </c>
       <c r="L102" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Buy Me A Car - Presley Regier</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>CHICA 305</v>
       </c>
       <c r="B103" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-02</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>3 weeks ago</v>
+        <v>CHICA 305 - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:58</v>
+        <v>3:08</v>
       </c>
       <c r="H103" t="str">
-        <v>Spacey Jane</v>
+        <v>John Summit</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
       </c>
       <c r="L103" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>CHICA 305 - John Summit</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Days We Left Behind</v>
       </c>
       <c r="B104" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>3 weeks ago</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G104" t="str">
-        <v>3:25</v>
+        <v>3:18</v>
       </c>
       <c r="H104" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
       </c>
       <c r="L104" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Days We Left Behind - Paul McCartney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B105" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>3 weeks ago</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>4:09</v>
+        <v>2:47</v>
       </c>
       <c r="H105" t="str">
-        <v>Mei Semones</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
       </c>
       <c r="L105" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Buy Me A Car</v>
+        <v>I Know You're Hurting.</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/buy-me-a-car/1887659688</v>
+        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Buy Me A Car - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G106" t="str">
-        <v>3:29</v>
+        <v>6:17</v>
       </c>
       <c r="H106" t="str">
-        <v>Presley Regier</v>
+        <v>RAYE</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/buy-me-a-car/1887659405</v>
+        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
       </c>
       <c r="L106" t="str">
-        <v>Buy Me A Car - Presley Regier</v>
+        <v>I Know You're Hurting. - RAYE</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>CHICA 305</v>
+        <v>MARATHON</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
+        <v>https://music.apple.com/us/song/marathon/1887320262</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>CHICA 305 - Single</v>
+        <v>MARATHON - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H107" t="str">
-        <v>John Summit</v>
+        <v>Becky G</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
+        <v>https://music.apple.com/us/album/marathon/1887320259</v>
       </c>
       <c r="L107" t="str">
-        <v>CHICA 305 - John Summit</v>
+        <v>MARATHON - Becky G</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Days We Left Behind</v>
+        <v>ALL THE TIME</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>ALL THE TIME - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:18</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Paul McCartney</v>
+        <v>John Summit</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
       </c>
       <c r="L108" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>ALL THE TIME - John Summit</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Sucker For Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>Sexistential</v>
       </c>
       <c r="G109" t="str">
-        <v>2:47</v>
+        <v>3:34</v>
       </c>
       <c r="H109" t="str">
-        <v>Miley Cyrus</v>
+        <v>Robyn</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
       </c>
       <c r="L109" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Sucker For Love - Robyn</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>FATHER</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://music.apple.com/us/song/father/1888707289</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>BULLY</v>
       </c>
       <c r="G110" t="str">
-        <v>6:17</v>
+        <v>2:49</v>
       </c>
       <c r="H110" t="str">
-        <v>RAYE</v>
+        <v>Kanye West</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v>https://music.apple.com/us/album/father/1888707282</v>
       </c>
       <c r="L110" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>FATHER - Kanye West</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>MARATHON</v>
+        <v>Lose Control</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>MARATHON - Single</v>
+        <v>ADL</v>
       </c>
       <c r="G111" t="str">
-        <v>2:49</v>
+        <v>2:39</v>
       </c>
       <c r="H111" t="str">
-        <v>Becky G</v>
+        <v>Yeat</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
       </c>
       <c r="L111" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>Lose Control - Yeat</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ALL THE TIME</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>Zavier</v>
       </c>
       <c r="G112" t="str">
-        <v>3:00</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>John Summit</v>
+        <v>Fetty Wap</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
       </c>
       <c r="L112" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Sucker For Love</v>
+        <v>WAGWAN</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Sexistential</v>
+        <v>ALL ROADS LEAD HOME</v>
       </c>
       <c r="G113" t="str">
-        <v>3:34</v>
+        <v>2:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Robyn</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
       </c>
       <c r="L113" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>WAGWAN - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>FATHER</v>
+        <v>Sideways</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://music.apple.com/us/song/sideways/1872664197</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>BULLY</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G114" t="str">
-        <v>2:49</v>
+        <v>3:12</v>
       </c>
       <c r="H114" t="str">
-        <v>Kanye West</v>
+        <v>ZAYN</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v>https://music.apple.com/us/album/sideways/1872663947</v>
       </c>
       <c r="L114" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Sideways - ZAYN</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Lose Control</v>
+        <v>Automatic</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://music.apple.com/us/song/automatic/1869414265</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ADL</v>
+        <v>Superbloom</v>
       </c>
       <c r="G115" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H115" t="str">
-        <v>Yeat</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v>https://music.apple.com/us/album/automatic/1869414259</v>
       </c>
       <c r="L115" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>Tractor Beam</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Zavier</v>
+        <v>Ricochet</v>
       </c>
       <c r="G116" t="str">
-        <v>3:44</v>
+        <v>3:34</v>
       </c>
       <c r="H116" t="str">
-        <v>Fetty Wap</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
       </c>
       <c r="L116" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>Tractor Beam - Snail Mail</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WAGWAN</v>
+        <v>Jet Lag Mouth</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>Jet Lag Mouth - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:07</v>
+        <v>2:32</v>
       </c>
       <c r="H117" t="str">
-        <v>Central Cee</v>
+        <v>In Color</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
       </c>
       <c r="L117" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Jet Lag Mouth - In Color</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sideways</v>
+        <v>prom queen</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>KONNAKOL</v>
+        <v>prom queen - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:12</v>
+        <v>2:43</v>
       </c>
       <c r="H118" t="str">
-        <v>ZAYN</v>
+        <v>Amelia Moore</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
       </c>
       <c r="L118" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>prom queen - Amelia Moore</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Automatic</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Superbloom</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G119" t="str">
-        <v>2:57</v>
+        <v>1:37</v>
       </c>
       <c r="H119" t="str">
-        <v>Jessie Ware</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L119" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Tractor Beam</v>
+        <v>Pal Agua</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Ricochet</v>
+        <v>Pal Agua - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:34</v>
+        <v>3:26</v>
       </c>
       <c r="H120" t="str">
-        <v>Snail Mail</v>
+        <v>J Balvin</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
       </c>
       <c r="L120" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Pal Agua - J Balvin</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>Phoenix</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>Phoenix - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:32</v>
+        <v>2:24</v>
       </c>
       <c r="H121" t="str">
-        <v>In Color</v>
+        <v>Marshmello</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
       </c>
       <c r="L121" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>Phoenix - Marshmello</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>prom queen</v>
+        <v>Up Out &amp; Gone</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>prom queen - Single</v>
+        <v>Up Out &amp; Gone - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:43</v>
+        <v>2:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Amelia Moore</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
       </c>
       <c r="L122" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>Up Out &amp; Gone - Ne-Yo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Home on the Range</v>
+        <v>Feel Your Rain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Feel Your Rain - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>1:37</v>
+        <v>3:36</v>
       </c>
       <c r="H123" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Eli</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
       </c>
       <c r="L123" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>Feel Your Rain - Eli</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Pal Agua</v>
+        <v>Lonely</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/lonely/1861895300</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G124" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H124" t="str">
-        <v>J Balvin</v>
+        <v>Fcukers</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/lonely/1861895134</v>
       </c>
       <c r="L124" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Lonely - Fcukers</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Phoenix</v>
+        <v>Back in Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Phoenix - Single</v>
+        <v>Back in Love - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:24</v>
+        <v>3:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Marshmello</v>
+        <v>Suki Waterhouse</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
       </c>
       <c r="L125" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Back in Love - Suki Waterhouse</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Sideways</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/sideways/1845190347</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G126" t="str">
-        <v>2:56</v>
+        <v>3:55</v>
       </c>
       <c r="H126" t="str">
-        <v>Ne-Yo</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/sideways/1845189970</v>
       </c>
       <c r="L126" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Sideways - Charlie Puth</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Feel Your Rain</v>
+        <v>Wichita Lineman (feat. Nick Cave)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G127" t="str">
-        <v>3:36</v>
+        <v>4:22</v>
       </c>
       <c r="H127" t="str">
-        <v>Eli</v>
+        <v>Flea</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
       </c>
       <c r="L127" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Lonely</v>
+        <v>SORRY I'M OBSESSED WITH YOU</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Ö</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
       </c>
       <c r="G128" t="str">
         <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Fcukers</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
       </c>
       <c r="L128" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Back in Love</v>
+        <v>Shame</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/shame/1887698916</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Back in Love - Single</v>
+        <v>Shame - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H129" t="str">
-        <v>Suki Waterhouse</v>
+        <v>BunnaB</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/bunnab/1695734940</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/shame/1887698914</v>
       </c>
       <c r="L129" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Shame - BunnaB</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Sideways</v>
+        <v>One Thing At A Time</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G130" t="str">
-        <v>3:55</v>
+        <v>4:42</v>
       </c>
       <c r="H130" t="str">
-        <v>Charlie Puth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
       </c>
       <c r="L130" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>One Thing At A Time - Courtney Barnett</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>wasteland</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Honora</v>
+        <v>wasteland - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:22</v>
+        <v>3:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Flea</v>
+        <v>Yuna</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
       </c>
       <c r="L131" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>wasteland - Yuna</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>i kinda like how u know just how beautiful u are</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G132" t="str">
-        <v>2:58</v>
+        <v>2:31</v>
       </c>
       <c r="H132" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Artemas</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
       </c>
       <c r="L132" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>i kinda like how u know just how beautiful u are - Artemas</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Shame</v>
+        <v>Por LA</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/shame/1887698916</v>
+        <v>https://music.apple.com/us/song/por-la/1883176748</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Shame - Single</v>
+        <v>TODO Ø NADA</v>
       </c>
       <c r="G133" t="str">
-        <v>3:02</v>
+        <v>2:19</v>
       </c>
       <c r="H133" t="str">
-        <v>BunnaB</v>
+        <v>Linea Personal</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/bunnab/1695734940</v>
+        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/shame/1887698914</v>
+        <v>https://music.apple.com/us/album/por-la/1883176465</v>
       </c>
       <c r="L133" t="str">
-        <v>Shame - BunnaB</v>
+        <v>Por LA - Linea Personal</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>One Thing At A Time</v>
+        <v>You Lead Me</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Creature of Habit</v>
+        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
       </c>
       <c r="G134" t="str">
-        <v>4:42</v>
+        <v>4:14</v>
       </c>
       <c r="H134" t="str">
-        <v>Courtney Barnett</v>
+        <v>Lauren Daigle</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
       </c>
       <c r="L134" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>You Lead Me - Lauren Daigle</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>wasteland</v>
+        <v>Just A Kid</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>wasteland - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G135" t="str">
-        <v>3:05</v>
+        <v>4:18</v>
       </c>
       <c r="H135" t="str">
-        <v>Yuna</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
       </c>
       <c r="L135" t="str">
-        <v>wasteland - Yuna</v>
+        <v>Just A Kid - Sam Barber</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Country And She Knows It</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>getting up to no good</v>
+        <v>Country And She Knows It - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:31</v>
+        <v>2:54</v>
       </c>
       <c r="H136" t="str">
-        <v>Artemas</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
       </c>
       <c r="L136" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Country And She Knows It - Luke Bryan</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Por LA</v>
+        <v>Georgia On My Mind</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>TODO Ø NADA</v>
+        <v>Georgia On My Mind - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:19</v>
+        <v>2:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Linea Personal</v>
+        <v>Thomas Rhett</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
       </c>
       <c r="L137" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>Georgia On My Mind - Thomas Rhett</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>You Lead Me</v>
+        <v>Deep Blue</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G138" t="str">
-        <v>4:14</v>
+        <v>3:17</v>
       </c>
       <c r="H138" t="str">
-        <v>Lauren Daigle</v>
+        <v>ERNEST</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
       </c>
       <c r="L138" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Deep Blue - ERNEST</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Just A Kid</v>
+        <v>Special</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/special/1860405766</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Broken View</v>
+        <v>sounds for someone</v>
       </c>
       <c r="G139" t="str">
-        <v>4:18</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>Sam Barber</v>
+        <v>Elmiene</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/special/1860405416</v>
       </c>
       <c r="L139" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Special - Elmiene</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Country And She Knows It</v>
+        <v>Heart Attack</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>CANDY</v>
       </c>
       <c r="G140" t="str">
-        <v>2:54</v>
+        <v>2:52</v>
       </c>
       <c r="H140" t="str">
-        <v>Luke Bryan</v>
+        <v>Justine Skye</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
       </c>
       <c r="L140" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>Heart Attack - Justine Skye</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Georgia On My Mind</v>
+        <v>STAY</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/stay/1882902388</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>STAY - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:35</v>
+        <v>3:06</v>
       </c>
       <c r="H141" t="str">
-        <v>Thomas Rhett</v>
+        <v>Stray Kids</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/stay/1882902387</v>
       </c>
       <c r="L141" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>STAY - Stray Kids</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Deep Blue</v>
+        <v>Unglued</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/unglued/1869618289</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Deep Blue</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G142" t="str">
-        <v>3:17</v>
+        <v>3:54</v>
       </c>
       <c r="H142" t="str">
-        <v>ERNEST</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/unglued/1869617637</v>
       </c>
       <c r="L142" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Unglued - Flatland Cavalry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Special</v>
+        <v>Ritual</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/ritual/1879895832</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>sounds for someone</v>
+        <v>Ritual - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:49</v>
+        <v>3:01</v>
       </c>
       <c r="H143" t="str">
-        <v>Elmiene</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/ritual/1879895655</v>
       </c>
       <c r="L143" t="str">
-        <v>Special - Elmiene</v>
+        <v>Ritual - Icona Pop</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Heart Attack</v>
+        <v>The Best</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/the-best/1886447721</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>CANDY</v>
+        <v>Wishbone (Deluxe)</v>
       </c>
       <c r="G144" t="str">
-        <v>2:52</v>
+        <v>3:48</v>
       </c>
       <c r="H144" t="str">
-        <v>Justine Skye</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/the-best/1886447307</v>
       </c>
       <c r="L144" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>The Best - Conan Gray</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>STAY</v>
+        <v>Smile</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/smile/1882074559</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>STAY - Single</v>
+        <v>Smile - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:06</v>
+        <v>3:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Stray Kids</v>
+        <v>Two Shell</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/smile/1882074557</v>
       </c>
       <c r="L145" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Smile - Two Shell</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Unglued</v>
+        <v>Duro</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/duro/1885875641</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Work of Heart</v>
+        <v>Duro - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:54</v>
+        <v>3:05</v>
       </c>
       <c r="H146" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Skrillex</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/duro/1885875640</v>
       </c>
       <c r="L146" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>Duro - Skrillex</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Ritual</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Ritual - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>2:58</v>
       </c>
       <c r="H147" t="str">
-        <v>Icona Pop</v>
+        <v>Sublime</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
       </c>
       <c r="L147" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Until The Sun Explodes - Sublime</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>The Best</v>
+        <v>Carousel</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/carousel/1870989676</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G148" t="str">
-        <v>3:48</v>
+        <v>3:36</v>
       </c>
       <c r="H148" t="str">
-        <v>Conan Gray</v>
+        <v>Cannons</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/carousel/1870989672</v>
       </c>
       <c r="L148" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Carousel - Cannons</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Smile</v>
+        <v>Mercy</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/mercy/1886265015</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Smile - Single</v>
+        <v>Mercy - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:50</v>
+        <v>3:49</v>
       </c>
       <c r="H149" t="str">
-        <v>Two Shell</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/mercy/1886265013</v>
       </c>
       <c r="L149" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Mercy - PRESIDENT</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Duro</v>
+        <v>Palms</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/palms/1881920935</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Duro - Single</v>
+        <v>Palms - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:05</v>
+        <v>3:18</v>
       </c>
       <c r="H150" t="str">
-        <v>Skrillex</v>
+        <v>The Maine</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/palms/1881920662</v>
       </c>
       <c r="L150" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Palms - The Maine</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Ozzy's Song</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:58</v>
+        <v>5:28</v>
       </c>
       <c r="H151" t="str">
-        <v>Sublime</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
       </c>
       <c r="L151" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Ozzy's Song - Black Label Society</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Carousel</v>
+        <v>Danger</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/danger/1885822963</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Everything Glows</v>
+        <v>Danger - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:36</v>
+        <v>2:19</v>
       </c>
       <c r="H152" t="str">
-        <v>Cannons</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/danger/1885822552</v>
       </c>
       <c r="L152" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Danger - Nia Archives</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Mercy</v>
+        <v>Icarus</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/icarus/1884315730</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Mercy - Single</v>
+        <v>Icarus - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:49</v>
+        <v>4:25</v>
       </c>
       <c r="H153" t="str">
-        <v>PRESIDENT</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/icarus/1884315726</v>
       </c>
       <c r="L153" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Icarus - Olivia O'Brien</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Palms</v>
+        <v>idk idk</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Palms - Single</v>
+        <v>idk idk - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:18</v>
+        <v>2:26</v>
       </c>
       <c r="H154" t="str">
-        <v>The Maine</v>
+        <v>Jim Legxacy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
       </c>
       <c r="L154" t="str">
-        <v>Palms - The Maine</v>
+        <v>idk idk - Jim Legxacy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ozzy's Song</v>
+        <v>Tonight</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/tonight/1885996687</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Tonight - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>5:28</v>
+        <v>2:25</v>
       </c>
       <c r="H155" t="str">
-        <v>Black Label Society</v>
+        <v>girlsweetvoiced</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/tonight/1885996684</v>
       </c>
       <c r="L155" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Tonight - girlsweetvoiced</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Danger</v>
+        <v>Klouds Will Carry Me To Sleep</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Danger - Single</v>
+        <v>Switcheroo</v>
       </c>
       <c r="G156" t="str">
-        <v>2:19</v>
+        <v>3:44</v>
       </c>
       <c r="H156" t="str">
-        <v>Nia Archives</v>
+        <v>Gelli Haha</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
       </c>
       <c r="L156" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Icarus</v>
+        <v>WE ON GO III (feat. TiaCorine)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Icarus - Single</v>
+        <v>WE ON GO PACK - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>4:25</v>
+        <v>2:45</v>
       </c>
       <c r="H157" t="str">
-        <v>Olivia O'Brien</v>
+        <v>BIA</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/bia/1112309486</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
       </c>
       <c r="L157" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>idk idk</v>
+        <v>this girl wants everything</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>idk idk - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G158" t="str">
-        <v>2:26</v>
+        <v>3:33</v>
       </c>
       <c r="H158" t="str">
-        <v>Jim Legxacy</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
       </c>
       <c r="L158" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>this girl wants everything - Isaia Huron</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Tonight</v>
+        <v>BRITTANY MURPHY.</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Tonight - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G159" t="str">
-        <v>2:25</v>
+        <v>3:44</v>
       </c>
       <c r="H159" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
       </c>
       <c r="L159" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>BRITTANY MURPHY. - Slayyyter</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Kingdom of Fear</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Switcheroo</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>3:44</v>
+        <v>2:41</v>
       </c>
       <c r="H160" t="str">
-        <v>Gelli Haha</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
       </c>
       <c r="L160" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Kingdom of Fear - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>R3verse</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>takeaways</v>
       </c>
       <c r="G161" t="str">
-        <v>2:45</v>
+        <v>3:31</v>
       </c>
       <c r="H161" t="str">
-        <v>BIA</v>
+        <v>Medium Build</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
       </c>
       <c r="L161" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>R3verse - Medium Build</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>this girl wants everything</v>
+        <v>Leadbelly (feat. MIKE)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G162" t="str">
-        <v>3:33</v>
+        <v>2:32</v>
       </c>
       <c r="H162" t="str">
-        <v>Isaia Huron</v>
+        <v>MIKE</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
       </c>
       <c r="L162" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>Leadbelly (feat. MIKE) - MIKE</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>heart of gold</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>heart of gold - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:44</v>
+        <v>2:51</v>
       </c>
       <c r="H163" t="str">
-        <v>Slayyyter</v>
+        <v>kai devega</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
       </c>
       <c r="L163" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>heart of gold - kai devega</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Breaking Down</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Deep Water - EP</v>
+        <v>Skeletor</v>
       </c>
       <c r="G164" t="str">
-        <v>2:41</v>
+        <v>4:21</v>
       </c>
       <c r="H164" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
       </c>
       <c r="L164" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Breaking Down - Chief Keef</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>R3verse</v>
+        <v>Dream House</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>takeaways</v>
+        <v>Dream House - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:31</v>
+        <v>2:54</v>
       </c>
       <c r="H165" t="str">
-        <v>Medium Build</v>
+        <v>Empress Of</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
       </c>
       <c r="L165" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>Dream House - Empress Of</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>Baby Blue</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Baby Blue / When It Comes To Loving You - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:32</v>
+        <v>2:51</v>
       </c>
       <c r="H166" t="str">
-        <v>MIKE</v>
+        <v>Cody Simpson</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
       </c>
       <c r="L166" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>Baby Blue - Cody Simpson</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>heart of gold</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>heart of gold - Single</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H167" t="str">
-        <v>kai devega</v>
+        <v>MEDUZA</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
       </c>
       <c r="L167" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Breaking Down</v>
+        <v>Wake Up, Mr. Crow</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Skeletor</v>
+        <v>Forever Now</v>
       </c>
       <c r="G168" t="str">
-        <v>4:21</v>
+        <v>4:05</v>
       </c>
       <c r="H168" t="str">
-        <v>Chief Keef</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
       </c>
       <c r="L168" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Wake Up, Mr. Crow - Switchfoot</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Dream House</v>
+        <v>She Was Just a Stranger</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dream House - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>2:54</v>
+        <v>3:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Empress Of</v>
+        <v>Benny G</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
       </c>
       <c r="L169" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>She Was Just a Stranger - Benny G</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Baby Blue</v>
+        <v>Cry In Front Of You</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Cry In Front Of You - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:51</v>
+        <v>3:03</v>
       </c>
       <c r="H170" t="str">
-        <v>Cody Simpson</v>
+        <v>Eric Bellinger</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
       </c>
       <c r="L170" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Cry In Front Of You - Eric Bellinger</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Come On, Let’s Get It</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>AK Cuts: Vol 3 - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>2:37</v>
+        <v>4:19</v>
       </c>
       <c r="H171" t="str">
-        <v>MEDUZA</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
       </c>
       <c r="L171" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Come On, Let’s Get It - Anish Kumar</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>GASLIGHT</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Forever Now</v>
+        <v>GASLIGHT - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:05</v>
+        <v>2:10</v>
       </c>
       <c r="H172" t="str">
-        <v>Switchfoot</v>
+        <v>WesGhost</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
       </c>
       <c r="L172" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>GASLIGHT - WesGhost</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Truth To Be Told</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Truth To Be Told - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:46</v>
+        <v>3:17</v>
       </c>
       <c r="H173" t="str">
-        <v>Benny G</v>
+        <v>GERD</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
       </c>
       <c r="L173" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Truth To Be Told - GERD</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>Free Your Mind - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H174" t="str">
-        <v>Eric Bellinger</v>
+        <v>Prospa</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
       </c>
       <c r="L174" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Free Your Mind - Prospa</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Down To The Bone</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Down To The Bone - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:19</v>
+        <v>2:51</v>
       </c>
       <c r="H175" t="str">
-        <v>Anish Kumar</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
       </c>
       <c r="L175" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Down To The Bone - Josh Baker</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>GASLIGHT</v>
+        <v>Breathe</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/breathe/1882913539</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:10</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>WesGhost</v>
+        <v>Marlon Hoffstadt</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/breathe/1882913535</v>
       </c>
       <c r="L176" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>Breathe - Marlon Hoffstadt</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Truth To Be Told</v>
+        <v>xs</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/xs/1886515563</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>xs - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:17</v>
+        <v>3:19</v>
       </c>
       <c r="H177" t="str">
-        <v>GERD</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/xs/1886515395</v>
       </c>
       <c r="L177" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>xs - Ashley Cooke</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Free Your Mind</v>
+        <v>Sail</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/sail/1883045745</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G178" t="str">
-        <v>3:21</v>
+        <v>4:54</v>
       </c>
       <c r="H178" t="str">
-        <v>Prospa</v>
+        <v>Future Islands</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/sail/1883045480</v>
       </c>
       <c r="L178" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Sail - Future Islands</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Down To The Bone</v>
+        <v>Dreaming</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>Dear Nashville</v>
       </c>
       <c r="G179" t="str">
-        <v>2:51</v>
+        <v>3:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Josh Baker</v>
+        <v>Ashley Monroe</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
       </c>
       <c r="L179" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>Dreaming - Ashley Monroe</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Breathe</v>
+        <v>NEW TINGZ</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Breathe - Single</v>
+        <v>THE IMPACT (Deluxe): PGLA Edition</v>
       </c>
       <c r="G180" t="str">
-        <v>2:48</v>
+        <v>2:39</v>
       </c>
       <c r="H180" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Armanii</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
       </c>
       <c r="L180" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>NEW TINGZ - Armanii</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>xs</v>
+        <v>La Opinión</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>xs - Single</v>
+        <v>Mis Compas El Final</v>
       </c>
       <c r="G181" t="str">
-        <v>3:19</v>
+        <v>3:23</v>
       </c>
       <c r="H181" t="str">
-        <v>Ashley Cooke</v>
+        <v>Joss Favela</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
       </c>
       <c r="L181" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>La Opinión - Joss Favela</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Sail</v>
+        <v>qué ves en mí?</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>qué ves en mí? / interesante - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:54</v>
+        <v>3:24</v>
       </c>
       <c r="H182" t="str">
-        <v>Future Islands</v>
+        <v>Paloma Morphy</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
       </c>
       <c r="L182" t="str">
-        <v>Sail - Future Islands</v>
+        <v>qué ves en mí? - Paloma Morphy</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Dreaming</v>
+        <v>Vengache Pa’ Aca</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Dear Nashville</v>
+        <v>Vengache Pa’ Aca - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:33</v>
+        <v>2:43</v>
       </c>
       <c r="H183" t="str">
-        <v>Ashley Monroe</v>
+        <v>Edgardo Nuñez</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
       </c>
       <c r="L183" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>NEW TINGZ</v>
+        <v>TUTUTU</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/tututu/1886801739</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>TUTUTU - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:39</v>
+        <v>2:16</v>
       </c>
       <c r="H184" t="str">
-        <v>Armanii</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/tututu/1886801737</v>
       </c>
       <c r="L184" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>TUTUTU - ELENA ROSE</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>La Opinión</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Mis Compas El Final</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:23</v>
+        <v>2:56</v>
       </c>
       <c r="H185" t="str">
-        <v>Joss Favela</v>
+        <v>2'Live Bre</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
       </c>
       <c r="L185" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>qué ves en mí?</v>
+        <v>Me Neither</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G186" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H186" t="str">
-        <v>Paloma Morphy</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
       </c>
       <c r="L186" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Me Neither - Ty Myers</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>Cole Palmer</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>Solid Ground</v>
       </c>
       <c r="G187" t="str">
-        <v>2:43</v>
+        <v>2:48</v>
       </c>
       <c r="H187" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>Limoblaze</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
       </c>
       <c r="L187" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>Cole Palmer - Limoblaze</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>TUTUTU</v>
+        <v>Wonder</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/wonder/1874405439</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Wonder - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:16</v>
+        <v>3:48</v>
       </c>
       <c r="H188" t="str">
-        <v>ELENA ROSE</v>
+        <v>Meeks Carter</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/wonder/1874405438</v>
       </c>
       <c r="L188" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>Wonder - Meeks Carter</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>ICU</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/icu/1879881618</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>ICU - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:56</v>
+        <v>2:53</v>
       </c>
       <c r="H189" t="str">
-        <v>2'Live Bre</v>
+        <v>Joseph O'Brien</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/icu/1879881617</v>
       </c>
       <c r="L189" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>ICU - Joseph O'Brien</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Me Neither</v>
+        <v>Supermans Weakness (feat. Chris Brown)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Soundtrack 2 Get Her Back</v>
       </c>
       <c r="G190" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H190" t="str">
-        <v>Ty Myers</v>
+        <v>Jozzy</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
       </c>
       <c r="L190" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Cole Palmer</v>
+        <v>Waiting Room (feat. Jordan Ward)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Solid Ground</v>
+        <v>Waiting Room (feat. Jordan Ward) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H191" t="str">
-        <v>Limoblaze</v>
+        <v>Jenevieve</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
       </c>
       <c r="L191" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Wonder</v>
+        <v>The Other Side Of Blue</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Wonder - Single</v>
+        <v>Rise</v>
       </c>
       <c r="G192" t="str">
-        <v>3:48</v>
+        <v>4:02</v>
       </c>
       <c r="H192" t="str">
-        <v>Meeks Carter</v>
+        <v>Melissa Etheridge</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
       </c>
       <c r="L192" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>The Other Side Of Blue - Melissa Etheridge</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>ICU</v>
+        <v>Roll On Thru</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>ICU - Single</v>
+        <v>Roll On Thru - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:53</v>
+        <v>3:51</v>
       </c>
       <c r="H193" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
       </c>
       <c r="L193" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>Roll On Thru - Hayden Everett</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Delicately</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/delicately/1880313498</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>Delicately - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:45</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>Jozzy</v>
+        <v>Andrea Bejar</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/delicately/1880313492</v>
       </c>
       <c r="L194" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Delicately - Andrea Bejar</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Waiting Room (feat. Jordan Ward)</v>
+        <v>One Of Those Things</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
+        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Single</v>
+        <v>One Of Those Things - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:21</v>
+        <v>3:27</v>
       </c>
       <c r="H195" t="str">
-        <v>Jenevieve</v>
+        <v>Lucy Clearwater</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
+        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
       </c>
       <c r="L195" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
+        <v>One Of Those Things - Lucy Clearwater</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>For Every Dusk</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Rise</v>
+        <v>Against The Dying Of The Light</v>
       </c>
       <c r="G196" t="str">
-        <v>4:02</v>
+        <v>6:04</v>
       </c>
       <c r="H196" t="str">
-        <v>Melissa Etheridge</v>
+        <v>José González</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
       </c>
       <c r="L196" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>For Every Dusk - José González</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Roll On Thru</v>
+        <v>I'll Wait</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Shoulder to Shoulder</v>
       </c>
       <c r="G197" t="str">
-        <v>3:51</v>
+        <v>3:33</v>
       </c>
       <c r="H197" t="str">
-        <v>Hayden Everett</v>
+        <v>Buzzy Lee</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
       </c>
       <c r="L197" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>I'll Wait - Buzzy Lee</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Delicately</v>
+        <v>Daisy</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/daisy/1879531184</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-02</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Delicately - Single</v>
+        <v>Daisy - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:20</v>
+        <v>3:02</v>
       </c>
       <c r="H198" t="str">
-        <v>Andrea Bejar</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/daisy/1879531182</v>
       </c>
       <c r="L198" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Daisy - Lola Blue</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>One Of Those Things</v>
+        <v>Play (Objekt Remix)</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-02</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>Friend Remixes</v>
       </c>
       <c r="G199" t="str">
-        <v>3:27</v>
+        <v>3:57</v>
       </c>
       <c r="H199" t="str">
-        <v>Lucy Clearwater</v>
+        <v>james K</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/james-k/955915784</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
       </c>
       <c r="L199" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>Play (Objekt Remix) - james K</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>For Every Dusk</v>
+        <v>Volverás (feat. Uma)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-02</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Perdidos - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>6:04</v>
+        <v>2:45</v>
       </c>
       <c r="H200" t="str">
-        <v>José González</v>
+        <v>MAVICA</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/mavica/566829940</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
       </c>
       <c r="L200" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>Volverás (feat. Uma) - MAVICA</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>I'll Wait</v>
+        <v>Fort</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/fort/1881952404</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-02</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Fort - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:33</v>
+        <v>2:27</v>
       </c>
       <c r="H201" t="str">
-        <v>Buzzy Lee</v>
+        <v>Lamb</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/fort/1881952403</v>
       </c>
       <c r="L201" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Fort - Lamb</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Daisy</v>
+        <v>SAME LA</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/same-la/1881772805</v>
       </c>
       <c r="D202" t="str">
         <v>2026-04-02</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Daisy - Single</v>
+        <v>SAME LA - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:02</v>
+        <v>3:44</v>
       </c>
       <c r="H202" t="str">
-        <v>Lola Blue</v>
+        <v>Tiffany Day</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/same-la/1881772354</v>
       </c>
       <c r="L202" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>SAME LA - Tiffany Day</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Working On It</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
       </c>
       <c r="D203" t="str">
         <v>2026-04-02</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Friend Remixes</v>
+        <v>Working On It - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:57</v>
+        <v>3:06</v>
       </c>
       <c r="H203" t="str">
-        <v>james K</v>
+        <v>Arthur Hill</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
       </c>
       <c r="L203" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Working On It - Arthur Hill</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>spring cleaning</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
       </c>
       <c r="D204" t="str">
         <v>2026-04-02</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Perdidos - Single</v>
+        <v>spring cleaning - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>2:45</v>
+        <v>4:03</v>
       </c>
       <c r="H204" t="str">
-        <v>MAVICA</v>
+        <v>Ethan Regan</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
       </c>
       <c r="L204" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>spring cleaning - Ethan Regan</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Fort</v>
+        <v>Just Drivin'</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
       </c>
       <c r="D205" t="str">
         <v>2026-04-02</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Fort - Single</v>
+        <v>Just Drivin' - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>2:27</v>
+        <v>3:26</v>
       </c>
       <c r="H205" t="str">
-        <v>Lamb</v>
+        <v>Presley Haile</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
       </c>
       <c r="L205" t="str">
-        <v>Fort - Lamb</v>
+        <v>Just Drivin' - Presley Haile</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SAME LA</v>
+        <v>Simple Things</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
       </c>
       <c r="D206" t="str">
         <v>2026-04-02</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>SAME LA - Single</v>
+        <v>Simple Things - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:44</v>
+        <v>3:46</v>
       </c>
       <c r="H206" t="str">
-        <v>Tiffany Day</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
       </c>
       <c r="L206" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Simple Things - Evening Elephants</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Working On It</v>
+        <v>Want It Back</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
       </c>
       <c r="D207" t="str">
         <v>2026-04-02</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Working On It - Single</v>
+        <v>Want It Back - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H207" t="str">
-        <v>Arthur Hill</v>
+        <v>Giant Rooks</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
       </c>
       <c r="L207" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Want It Back - Giant Rooks</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>spring cleaning</v>
+        <v>Bite Down</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
       </c>
       <c r="D208" t="str">
         <v>2026-04-02</v>
@@ -8279,36 +8279,36 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Bite Down - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>4:03</v>
+        <v>3:36</v>
       </c>
       <c r="H208" t="str">
-        <v>Ethan Regan</v>
+        <v>Anna Sofia</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
       </c>
       <c r="L208" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Bite Down - Anna Sofia</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Just Drivin'</v>
+        <v>Ulvgjeld &amp; Blodsodel</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
       </c>
       <c r="D209" t="str">
         <v>2026-04-02</v>
@@ -8317,36 +8317,36 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G209" t="str">
-        <v>3:26</v>
+        <v>5:42</v>
       </c>
       <c r="H209" t="str">
-        <v>Presley Haile</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
       </c>
       <c r="L209" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Simple Things</v>
+        <v>Demons</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/demons/1884707577</v>
       </c>
       <c r="D210" t="str">
         <v>2026-04-02</v>
@@ -8355,36 +8355,36 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Simple Things - Single</v>
+        <v>Ask Me How I’ve Been</v>
       </c>
       <c r="G210" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H210" t="str">
-        <v>Evening Elephants</v>
+        <v>Anella</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/anella/1789704259</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/demons/1884707575</v>
       </c>
       <c r="L210" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>Demons - Anella</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Want It Back</v>
+        <v>Es brennt...</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
       </c>
       <c r="D211" t="str">
         <v>2026-04-02</v>
@@ -8393,36 +8393,36 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Want It Back - Single</v>
+        <v>Es brennt... - Single</v>
       </c>
       <c r="G211" t="str">
-        <v>3:27</v>
+        <v>3:35</v>
       </c>
       <c r="H211" t="str">
-        <v>Giant Rooks</v>
+        <v>Till Lindemann</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
       </c>
       <c r="L211" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>Es brennt... - Till Lindemann</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Bite Down</v>
+        <v>Fire Marengo</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
       </c>
       <c r="D212" t="str">
         <v>2026-04-02</v>
@@ -8431,36 +8431,36 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>Bite Down - Single</v>
+        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
       </c>
       <c r="G212" t="str">
-        <v>3:36</v>
+        <v>3:49</v>
       </c>
       <c r="H212" t="str">
-        <v>Anna Sofia</v>
+        <v>Enslaved</v>
       </c>
       <c r="I212" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
       </c>
       <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
       </c>
       <c r="L212" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Fire Marengo - Enslaved</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Close to the Bone</v>
       </c>
       <c r="B213" t="str">
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
       </c>
       <c r="D213" t="str">
         <v>2026-04-02</v>
@@ -8469,36 +8469,36 @@
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G213" t="str">
-        <v>5:42</v>
+        <v>4:09</v>
       </c>
       <c r="H213" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I213" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
       </c>
       <c r="L213" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Close to the Bone - Armored Saint</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Demons</v>
+        <v>Back Home</v>
       </c>
       <c r="B214" t="str">
         <v/>
       </c>
       <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D214" t="str">
         <v>2026-04-02</v>
@@ -8507,182 +8507,30 @@
         <v/>
       </c>
       <c r="F214" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G214" t="str">
-        <v>2:42</v>
+        <v>1:36</v>
       </c>
       <c r="H214" t="str">
-        <v>Anella</v>
+        <v>MIKE</v>
       </c>
       <c r="I214" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L214" t="str">
-        <v>Demons - Anella</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Es brennt...</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Es brennt... - Single</v>
-      </c>
-      <c r="G215" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H215" t="str">
-        <v>Till Lindemann</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
-      </c>
-      <c r="L215" t="str">
-        <v>Es brennt... - Till Lindemann</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Fire Marengo</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
-      </c>
-      <c r="G216" t="str">
-        <v>3:49</v>
-      </c>
-      <c r="H216" t="str">
-        <v>Enslaved</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
-      </c>
-      <c r="L216" t="str">
-        <v>Fire Marengo - Enslaved</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Close to the Bone</v>
-      </c>
-      <c r="B217" t="str">
-        <v/>
-      </c>
-      <c r="C217" t="str">
-        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
-      </c>
-      <c r="D217" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G217" t="str">
-        <v>4:09</v>
-      </c>
-      <c r="H217" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I217" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J217" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K217" t="str">
-        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
-      </c>
-      <c r="L217" t="str">
-        <v>Close to the Bone - Armored Saint</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>Back Home</v>
-      </c>
-      <c r="B218" t="str">
-        <v/>
-      </c>
-      <c r="C218" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
-      </c>
-      <c r="D218" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="E218" t="str">
-        <v/>
-      </c>
-      <c r="F218" t="str">
-        <v>POMPEII // UTILITY</v>
-      </c>
-      <c r="G218" t="str">
-        <v>1:36</v>
-      </c>
-      <c r="H218" t="str">
-        <v>MIKE</v>
-      </c>
-      <c r="I218" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J218" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
-      </c>
-      <c r="K218" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
-      </c>
-      <c r="L218" t="str">
         <v>Back Home - MIKE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L218"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L214"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -1503,7 +1503,7 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>4:00</v>
@@ -1731,7 +1731,7 @@
         <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B36" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:56</v>
@@ -4049,7 +4049,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v>2:50</v>

--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -1047,7 +1047,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:01</v>
@@ -1085,7 +1085,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:59</v>

--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>שילה שטראל - תקופה שלמה</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410340&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>3:55</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Nothing But Thieves</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,36 +469,36 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>שילה שטראל - תקופה שלמה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>רון סויסה - האור בחשכה</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410339&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>2:45</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Ocean Alley</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>רון סויסה - האור בחשכה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>ישראל בניטה - מי אני</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410338&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>6:29</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>RAYE</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>ישראל בניטה - מי אני</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
       </c>
       <c r="B5" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410337&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Take That</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410336&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>4:22</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Armik</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>טלי רבקה סימן טוב - חיים חדשים</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410335&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>4:10</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Switchfoot</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>טלי רבקה סימן טוב - חיים חדשים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410334&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:19</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Peter Gabriel</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>גל סינואני - יום יפה</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410333&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:03</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Sarah Julia</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,36 +735,36 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>גל סינואני - יום יפה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>גל אדם - כבר לא שלך</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410332&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>3:56</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Chris Norman</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>גל אדם - כבר לא שלך</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410331&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>3:58</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Alan Walker</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,36 +811,36 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410330&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>3:56</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,36 +849,36 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410329&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>2:50</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>Miley Cyrus</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,36 +887,36 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410328&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>3:42</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>Conan Gray</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,36 +925,36 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>אביב לוי - דרום אמריקה</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410327&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>2:16</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>Charlie Puth</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,36 +963,36 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>אביב לוי - דרום אמריקה</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>BTS Arirang</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://yosmusic.com/bts-arirang/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>האלבום Arirang של BTS (שיצא במרץ 2026) הפך בתוך שבועות ספורים לאחד התקליטים המבוקשים בעולם גם פיזית (ויניל/מהדורות אספנים) וגם סטרימינג, וזה לא במקרה. מדובר בשילוב נדיר של אירוע תרבותי, מהלך מוזיקלי מחושב, ורגע רגשי של קאמבק. בעיני המעריצים, זה</v>
       </c>
       <c r="G16" t="str">
-        <v>3:08</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>Kylie Morgan</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,36 +1001,36 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>BTS Arirang</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23054&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>08:36</v>
       </c>
       <c r="G17" t="str">
-        <v>3:38</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:01</v>
+        <v>3:55</v>
       </c>
       <c r="H18" t="str">
-        <v>Angelina Mango</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:59</v>
+        <v>2:45</v>
       </c>
       <c r="H19" t="str">
-        <v>Julio Iglesias</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:59</v>
+        <v>6:29</v>
       </c>
       <c r="H20" t="str">
-        <v>Loreen</v>
+        <v>RAYE</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:58</v>
+        <v>3:17</v>
       </c>
       <c r="H21" t="str">
-        <v>Jessie Ware</v>
+        <v>Take That</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:49</v>
+        <v>4:22</v>
       </c>
       <c r="H22" t="str">
-        <v>Holly Humberstone</v>
+        <v>Armik</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:22</v>
+        <v>4:10</v>
       </c>
       <c r="H23" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:50</v>
+        <v>3:19</v>
       </c>
       <c r="H24" t="str">
-        <v>Ella Langley</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G25" t="str">
-        <v>6:43</v>
+        <v>3:03</v>
       </c>
       <c r="H25" t="str">
-        <v>David Gilmour</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:52</v>
+        <v>3:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Eagles</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:13</v>
+        <v>3:58</v>
       </c>
       <c r="H27" t="str">
-        <v>Moody Joody</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H28" t="str">
-        <v>Jackson Dean</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:01</v>
+        <v>2:50</v>
       </c>
       <c r="H29" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:00</v>
+        <v>3:42</v>
       </c>
       <c r="H30" t="str">
-        <v>Madison Cunningham</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:35</v>
+        <v>2:16</v>
       </c>
       <c r="H31" t="str">
-        <v>mary in the junkyard</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:01</v>
+        <v>3:08</v>
       </c>
       <c r="H32" t="str">
-        <v>Adam Sanders</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:40</v>
+        <v>3:38</v>
       </c>
       <c r="H33" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B34" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H34" t="str">
-        <v>twocolors</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B35" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>12 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:42</v>
+        <v>3:59</v>
       </c>
       <c r="H35" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>13 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>13 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:56</v>
+        <v>2:59</v>
       </c>
       <c r="H36" t="str">
-        <v>Prince</v>
+        <v>Loreen</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B37" t="str">
-        <v>13 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>13 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G37" t="str">
-        <v>5:12</v>
+        <v>2:58</v>
       </c>
       <c r="H37" t="str">
-        <v>RAYE</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B38" t="str">
-        <v>13 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>13 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:30</v>
+        <v>3:49</v>
       </c>
       <c r="H38" t="str">
-        <v>The Warning</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B39" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:18</v>
+        <v>3:22</v>
       </c>
       <c r="H39" t="str">
-        <v>Pentatonix</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B40" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H40" t="str">
-        <v>Tenille Townes</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B41" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:53</v>
+        <v>6:43</v>
       </c>
       <c r="H41" t="str">
-        <v>Jessie Ware</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B42" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:37</v>
+        <v>4:52</v>
       </c>
       <c r="H42" t="str">
-        <v>Niall Horan</v>
+        <v>Eagles</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:26</v>
+        <v>3:13</v>
       </c>
       <c r="H43" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:40</v>
+        <v>3:28</v>
       </c>
       <c r="H44" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H45" t="str">
-        <v>Jackson Dean</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B46" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:02</v>
+        <v>4:00</v>
       </c>
       <c r="H46" t="str">
-        <v>Foo Fighters</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B47" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>13 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:40</v>
+        <v>5:35</v>
       </c>
       <c r="H47" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:22</v>
+        <v>3:01</v>
       </c>
       <c r="H48" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H49" t="str">
-        <v>Ella Langley</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:39</v>
+        <v>2:25</v>
       </c>
       <c r="H50" t="str">
-        <v>Cannons</v>
+        <v>twocolors</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:10</v>
+        <v>3:42</v>
       </c>
       <c r="H51" t="str">
-        <v>Luke Combs</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:47</v>
+        <v>3:56</v>
       </c>
       <c r="H52" t="str">
-        <v>Nessa Barrett</v>
+        <v>Prince</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:14</v>
+        <v>5:12</v>
       </c>
       <c r="H53" t="str">
-        <v>aron!</v>
+        <v>RAYE</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:00</v>
+        <v>3:30</v>
       </c>
       <c r="H54" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>The Warning</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:56</v>
+        <v>3:18</v>
       </c>
       <c r="H55" t="str">
-        <v>DMA'S</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H56" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:17</v>
+        <v>5:53</v>
       </c>
       <c r="H57" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:31</v>
+        <v>2:37</v>
       </c>
       <c r="H58" t="str">
-        <v>Nick Carter</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:38</v>
+        <v>2:26</v>
       </c>
       <c r="H59" t="str">
-        <v>Carly Pearce</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:11</v>
+        <v>2:40</v>
       </c>
       <c r="H60" t="str">
-        <v>OneRepublic</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:57</v>
+        <v>3:30</v>
       </c>
       <c r="H61" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:47</v>
+        <v>4:02</v>
       </c>
       <c r="H62" t="str">
-        <v>Armin van Buuren</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
-        <v>7:10</v>
+        <v>3:40</v>
       </c>
       <c r="H63" t="str">
-        <v>David Gilmour</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:06</v>
+        <v>2:22</v>
       </c>
       <c r="H64" t="str">
-        <v>Grace Enger</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:05</v>
+        <v>3:47</v>
       </c>
       <c r="H65" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:12</v>
+        <v>3:39</v>
       </c>
       <c r="H66" t="str">
-        <v>Freya Ridings</v>
+        <v>Cannons</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
-        <v>9:11</v>
+        <v>4:10</v>
       </c>
       <c r="H67" t="str">
-        <v>David Gilmour</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:49</v>
+        <v>4:47</v>
       </c>
       <c r="H68" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:28</v>
+        <v>2:14</v>
       </c>
       <c r="H69" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>aron!</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:31</v>
+        <v>4:00</v>
       </c>
       <c r="H70" t="str">
-        <v>Martin Garrix</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:11</v>
+        <v>3:56</v>
       </c>
       <c r="H71" t="str">
-        <v>Baby Queen</v>
+        <v>DMA'S</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:27</v>
+        <v>3:17</v>
       </c>
       <c r="H72" t="str">
-        <v>HAUSER</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:34</v>
+        <v>3:17</v>
       </c>
       <c r="H73" t="str">
-        <v>Holly Humberstone</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:50</v>
+        <v>3:31</v>
       </c>
       <c r="H74" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:51</v>
+        <v>3:38</v>
       </c>
       <c r="H75" t="str">
-        <v>Rick Astley</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:39</v>
+        <v>4:11</v>
       </c>
       <c r="H76" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
-        <v>5:08</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie J</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:46</v>
+        <v>3:47</v>
       </c>
       <c r="H78" t="str">
-        <v>Bishop Briggs</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:42</v>
+        <v>7:10</v>
       </c>
       <c r="H79" t="str">
-        <v>Dean Lewis</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:31</v>
+        <v>3:06</v>
       </c>
       <c r="H80" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:14</v>
+        <v>3:05</v>
       </c>
       <c r="H81" t="str">
-        <v>Luke Combs</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:22</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>Allison Russell</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:43</v>
+        <v>9:11</v>
       </c>
       <c r="H83" t="str">
-        <v>We Three</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:54</v>
+        <v>3:49</v>
       </c>
       <c r="H84" t="str">
-        <v>paris jackson</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H85" t="str">
-        <v>Kane Brown</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:37</v>
+        <v>3:31</v>
       </c>
       <c r="H86" t="str">
-        <v>Lainey Wilson</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:57</v>
+        <v>3:11</v>
       </c>
       <c r="H87" t="str">
-        <v>Malcolm Todd</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:38</v>
+        <v>2:27</v>
       </c>
       <c r="H88" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>HAUSER</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:29</v>
+        <v>3:34</v>
       </c>
       <c r="H89" t="str">
-        <v>Kungs</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:28</v>
+        <v>2:50</v>
       </c>
       <c r="H90" t="str">
-        <v>Sunday (1994)</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H91" t="str">
-        <v>aron!</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:51</v>
+        <v>2:39</v>
       </c>
       <c r="H92" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:49</v>
+        <v>5:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Sunday (1994)</v>
+        <v>Jessie J</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:16</v>
+        <v>3:46</v>
       </c>
       <c r="H94" t="str">
-        <v>Owen Riegling</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:16</v>
+        <v>2:42</v>
       </c>
       <c r="H95" t="str">
-        <v>LANY</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:25</v>
+        <v>2:31</v>
       </c>
       <c r="H96" t="str">
-        <v>Maverick Sabre</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:50</v>
+        <v>3:14</v>
       </c>
       <c r="H97" t="str">
-        <v>Amanda Jordan</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H98" t="str">
-        <v>Beabadoobee</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:58</v>
+        <v>3:43</v>
       </c>
       <c r="H99" t="str">
-        <v>Spacey Jane</v>
+        <v>We Three</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H100" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>paris jackson</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:09</v>
+        <v>2:46</v>
       </c>
       <c r="H101" t="str">
-        <v>Mei Semones</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,4301 +4231,4301 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Buy Me A Car</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/buy-me-a-car/1887659688</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Buy Me A Car - Single</v>
+        <v>3w ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:29</v>
+        <v>3:37</v>
       </c>
       <c r="H102" t="str">
-        <v>Presley Regier</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/buy-me-a-car/1887659405</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Buy Me A Car - Presley Regier</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>CHICA 305</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>CHICA 305 - Single</v>
+        <v>3w ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:08</v>
+        <v>2:57</v>
       </c>
       <c r="H103" t="str">
-        <v>John Summit</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>CHICA 305 - John Summit</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Days We Left Behind</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/days-we-left-behind/1887403088</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>3w ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:18</v>
+        <v>3:38</v>
       </c>
       <c r="H104" t="str">
-        <v>Paul McCartney</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/days-we-left-behind/1887402919</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Days We Left Behind - Paul McCartney</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/1887385342</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>3w ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:47</v>
+        <v>4:29</v>
       </c>
       <c r="H105" t="str">
-        <v>Miley Cyrus</v>
+        <v>Kungs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1887385339</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Know You're Hurting.</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-know-youre-hurting/1871085698</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>3w ago</v>
       </c>
       <c r="G106" t="str">
-        <v>6:17</v>
+        <v>4:28</v>
       </c>
       <c r="H106" t="str">
-        <v>RAYE</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-know-youre-hurting/1871085677</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>I Know You're Hurting. - RAYE</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>MARATHON</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/marathon/1887320262</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>MARATHON - Single</v>
+        <v>3w ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:49</v>
+        <v>3:26</v>
       </c>
       <c r="H107" t="str">
-        <v>Becky G</v>
+        <v>aron!</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/marathon/1887320259</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>MARATHON - Becky G</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ALL THE TIME</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1886684036</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>ALL THE TIME - Single</v>
+        <v>3w ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>3:51</v>
       </c>
       <c r="H108" t="str">
-        <v>John Summit</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1886683822</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>ALL THE TIME - John Summit</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Sucker For Love</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sucker-for-love/1852752617</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sexistential</v>
+        <v>3w ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:34</v>
+        <v>2:49</v>
       </c>
       <c r="H109" t="str">
-        <v>Robyn</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sucker-for-love/1852752613</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Sucker For Love - Robyn</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>FATHER</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/father/1888707289</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>BULLY</v>
+        <v>3w ago</v>
       </c>
       <c r="G110" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H110" t="str">
-        <v>Kanye West</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/kanye-west/2715720</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/father/1888707282</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>FATHER - Kanye West</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Lose Control</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/lose-control/1888322969</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ADL</v>
+        <v>3w ago</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>4:16</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>LANY</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/lose-control/1888322963</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Lose Control - Yeat</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/white-roses-feat-divinity-ymanie/1885054151</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Zavier</v>
+        <v>3w ago</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>3:25</v>
       </c>
       <c r="H112" t="str">
-        <v>Fetty Wap</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/fetty-wap/872900424</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/white-roses-feat-divinity-ymanie/1885054146</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>White Roses (feat. Divinity &amp; Ymanie) - Fetty Wap</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WAGWAN</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/wagwan/1876931507</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ALL ROADS LEAD HOME</v>
+        <v>3w ago</v>
       </c>
       <c r="G113" t="str">
-        <v>2:07</v>
+        <v>2:50</v>
       </c>
       <c r="H113" t="str">
-        <v>Central Cee</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/wagwan/1876931503</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>WAGWAN - Central Cee</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sideways</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sideways/1872664197</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>KONNAKOL</v>
+        <v>3w ago</v>
       </c>
       <c r="G114" t="str">
-        <v>3:12</v>
+        <v>3:57</v>
       </c>
       <c r="H114" t="str">
-        <v>ZAYN</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sideways/1872663947</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>Sideways - ZAYN</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Automatic</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/automatic/1869414265</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Superbloom</v>
+        <v>3w ago</v>
       </c>
       <c r="G115" t="str">
-        <v>2:57</v>
+        <v>3:58</v>
       </c>
       <c r="H115" t="str">
-        <v>Jessie Ware</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/automatic/1869414259</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Automatic - Jessie Ware</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tractor Beam</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tractor-beam/1862845744</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ricochet</v>
+        <v>3w ago</v>
       </c>
       <c r="G116" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="H116" t="str">
-        <v>Snail Mail</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tractor-beam/1862845733</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>Tractor Beam - Snail Mail</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>3w ago</v>
       </c>
       <c r="G117" t="str">
-        <v>2:32</v>
+        <v>4:09</v>
       </c>
       <c r="H117" t="str">
-        <v>In Color</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v/>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v/>
       </c>
       <c r="L117" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>prom queen</v>
+        <v>The More I Hope</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/prom-queen/1886597439</v>
+        <v>https://music.apple.com/us/song/the-more-i-hope/1882826389</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>prom queen - Single</v>
+        <v>Broken View</v>
       </c>
       <c r="G118" t="str">
-        <v>2:43</v>
+        <v>4:06</v>
       </c>
       <c r="H118" t="str">
-        <v>Amelia Moore</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/amelia-moore/1348611202</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/prom-queen/1886597438</v>
+        <v>https://music.apple.com/us/album/the-more-i-hope/1882826154</v>
       </c>
       <c r="L118" t="str">
-        <v>prom queen - Amelia Moore</v>
+        <v>The More I Hope - Sam Barber</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Home on the Range</v>
+        <v>the van</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/the-van/1872842315</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G119" t="str">
-        <v>1:37</v>
+        <v>2:58</v>
       </c>
       <c r="H119" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>Bleachers</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/the-van/1872842313</v>
       </c>
       <c r="L119" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>the van - Bleachers</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Pal Agua</v>
+        <v>Reply To This</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/pal-agua/1887740894</v>
+        <v>https://music.apple.com/us/song/reply-to-this/1888625007</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Pal Agua - Single</v>
+        <v>Whatever's Clever! (Expanded)</v>
       </c>
       <c r="G120" t="str">
-        <v>3:26</v>
+        <v>2:57</v>
       </c>
       <c r="H120" t="str">
-        <v>J Balvin</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/pal-agua/1887740893</v>
+        <v>https://music.apple.com/us/album/reply-to-this/1888624679</v>
       </c>
       <c r="L120" t="str">
-        <v>Pal Agua - J Balvin</v>
+        <v>Reply To This - Charlie Puth</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Phoenix</v>
+        <v>Funny Friends</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/phoenix/1886403159</v>
+        <v>https://music.apple.com/us/song/funny-friends/1861531673</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Phoenix - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G121" t="str">
-        <v>2:24</v>
+        <v>2:35</v>
       </c>
       <c r="H121" t="str">
-        <v>Marshmello</v>
+        <v>Thundercat</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/phoenix/1886403156</v>
+        <v>https://music.apple.com/us/album/funny-friends/1861531667</v>
       </c>
       <c r="L121" t="str">
-        <v>Phoenix - Marshmello</v>
+        <v>Funny Friends - Thundercat</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Up Out &amp; Gone</v>
+        <v>Turtleneck</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/up-out-gone/1885968511</v>
+        <v>https://music.apple.com/us/song/turtleneck/1890056028</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Up Out &amp; Gone - Single</v>
+        <v>Turtleneck - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:56</v>
+        <v>1:35</v>
       </c>
       <c r="H122" t="str">
-        <v>Ne-Yo</v>
+        <v>Tank</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/tank/3293014</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/up-out-gone/1885968268</v>
+        <v>https://music.apple.com/us/album/turtleneck/1890056027</v>
       </c>
       <c r="L122" t="str">
-        <v>Up Out &amp; Gone - Ne-Yo</v>
+        <v>Turtleneck - Tank</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Feel Your Rain</v>
+        <v>G.O.D. And The Broken Ribs</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/feel-your-rain/1886776415</v>
+        <v>https://music.apple.com/us/song/g-o-d-and-the-broken-ribs/1883199709</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Feel Your Rain - Single</v>
+        <v>G.O.D. And The Broken Ribs / Derecho Demonico - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:36</v>
+        <v>3:43</v>
       </c>
       <c r="H123" t="str">
-        <v>Eli</v>
+        <v>Jack White</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/jack-white/826980</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/feel-your-rain/1886776413</v>
+        <v>https://music.apple.com/us/album/g-o-d-and-the-broken-ribs/1883199707</v>
       </c>
       <c r="L123" t="str">
-        <v>Feel Your Rain - Eli</v>
+        <v>G.O.D. And The Broken Ribs - Jack White</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Lonely</v>
+        <v>In A Life</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/lonely/1861895300</v>
+        <v>https://music.apple.com/us/song/in-a-life/1888147404</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ö</v>
+        <v>Easter Lily EP</v>
       </c>
       <c r="G124" t="str">
-        <v>2:58</v>
+        <v>4:33</v>
       </c>
       <c r="H124" t="str">
-        <v>Fcukers</v>
+        <v>U2</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/lonely/1861895134</v>
+        <v>https://music.apple.com/us/album/in-a-life/1888147400</v>
       </c>
       <c r="L124" t="str">
-        <v>Lonely - Fcukers</v>
+        <v>In A Life - U2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Back in Love</v>
+        <v>Buy Me A Car</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/back-in-love/1886199084</v>
+        <v>https://music.apple.com/us/song/buy-me-a-car/1887659688</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Back in Love - Single</v>
+        <v>Buy Me A Car - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H125" t="str">
-        <v>Suki Waterhouse</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/suki-waterhouse/926014669</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/back-in-love/1886199079</v>
+        <v>https://music.apple.com/us/album/buy-me-a-car/1887659405</v>
       </c>
       <c r="L125" t="str">
-        <v>Back in Love - Suki Waterhouse</v>
+        <v>Buy Me A Car - Presley Regier</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Sideways</v>
+        <v>CHICA 305</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sideways/1845190347</v>
+        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Whatever's Clever!</v>
+        <v>CHICA 305 - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:55</v>
+        <v>3:08</v>
       </c>
       <c r="H126" t="str">
-        <v>Charlie Puth</v>
+        <v>John Summit</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sideways/1845189970</v>
+        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
       </c>
       <c r="L126" t="str">
-        <v>Sideways - Charlie Puth</v>
+        <v>CHICA 305 - John Summit</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Wichita Lineman (feat. Nick Cave)</v>
+        <v>Jet Lag Mouth</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/wichita-lineman-feat-nick-cave/1861644319</v>
+        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Honora</v>
+        <v>Jet Lag Mouth - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:22</v>
+        <v>2:32</v>
       </c>
       <c r="H127" t="str">
-        <v>Flea</v>
+        <v>In Color</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/wichita-lineman-feat-nick-cave/1861644307</v>
+        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
       </c>
       <c r="L127" t="str">
-        <v>Wichita Lineman (feat. Nick Cave) - Flea</v>
+        <v>Jet Lag Mouth - In Color</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/sorry-im-obsessed-with-you/1884701942</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>1:37</v>
       </c>
       <c r="H128" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/sorry-im-obsessed-with-you/1884701940</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L128" t="str">
-        <v>SORRY I'M OBSESSED WITH YOU - Chelsea Cutler</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Shame</v>
+        <v>Back Home</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/shame/1887698916</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Shame - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G129" t="str">
-        <v>3:02</v>
+        <v>1:36</v>
       </c>
       <c r="H129" t="str">
-        <v>BunnaB</v>
+        <v>MIKE</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/bunnab/1695734940</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/shame/1887698914</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L129" t="str">
-        <v>Shame - BunnaB</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>One Thing At A Time</v>
+        <v>Reputation</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/one-thing-at-a-time/1868686718</v>
+        <v>https://music.apple.com/us/song/reputation/1888615203</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Creature of Habit</v>
+        <v>Reputation / Bobby - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:42</v>
+        <v>3:55</v>
       </c>
       <c r="H130" t="str">
-        <v>Courtney Barnett</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/one-thing-at-a-time/1868686713</v>
+        <v>https://music.apple.com/us/album/reputation/1888615202</v>
       </c>
       <c r="L130" t="str">
-        <v>One Thing At A Time - Courtney Barnett</v>
+        <v>Reputation - Ravyn Lenae</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>wasteland</v>
+        <v>MURAL</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/wasteland/1876917820</v>
+        <v>https://music.apple.com/us/song/mural/1885914724</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>wasteland - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G131" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H131" t="str">
-        <v>Yuna</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/wasteland/1876917816</v>
+        <v>https://music.apple.com/us/album/mural/1885914714</v>
       </c>
       <c r="L131" t="str">
-        <v>wasteland - Yuna</v>
+        <v>MURAL - Swae Lee</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>i kinda like how u know just how beautiful u are</v>
+        <v>Business &amp; Personal (second half)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764652</v>
+        <v>https://music.apple.com/us/song/business-personal-second-half/1889934787</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>getting up to no good</v>
+        <v>Business &amp; Personal - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:31</v>
+        <v>2:19</v>
       </c>
       <c r="H132" t="str">
-        <v>Artemas</v>
+        <v>Latto</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/i-kinda-like-how-u-know-just-how-beautiful-u-are/1878764647</v>
+        <v>https://music.apple.com/us/album/business-personal-second-half/1889934634</v>
       </c>
       <c r="L132" t="str">
-        <v>i kinda like how u know just how beautiful u are - Artemas</v>
+        <v>Business &amp; Personal (second half) - Latto</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Por LA</v>
+        <v>Beams</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/por-la/1883176748</v>
+        <v>https://music.apple.com/us/song/beams/1862570896</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>TODO Ø NADA</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G133" t="str">
-        <v>2:19</v>
+        <v>3:39</v>
       </c>
       <c r="H133" t="str">
-        <v>Linea Personal</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/linea-personal/1621429938</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/por-la/1883176465</v>
+        <v>https://music.apple.com/us/album/beams/1862570378</v>
       </c>
       <c r="L133" t="str">
-        <v>Por LA - Linea Personal</v>
+        <v>Beams - Arlo Parks</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>You Lead Me</v>
+        <v>Hysteria</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/you-lead-me/1883714972</v>
+        <v>https://music.apple.com/us/song/hysteria/1887407036</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>House Of David (Music Inspired By The Prime Video Original Series) [Season Two]</v>
+        <v>Hysteria - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>4:14</v>
+        <v>2:23</v>
       </c>
       <c r="H134" t="str">
-        <v>Lauren Daigle</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lauren-daigle/722177758</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/you-lead-me/1883714965</v>
+        <v>https://music.apple.com/us/album/hysteria/1887407035</v>
       </c>
       <c r="L134" t="str">
-        <v>You Lead Me - Lauren Daigle</v>
+        <v>Hysteria - Bebe Rexha</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Just A Kid</v>
+        <v>Need Your Love</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/just-a-kid/1882826380</v>
+        <v>https://music.apple.com/us/song/need-your-love/1884740423</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Broken View</v>
+        <v>Need Your Love - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>4:18</v>
+        <v>3:58</v>
       </c>
       <c r="H135" t="str">
-        <v>Sam Barber</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/just-a-kid/1882826154</v>
+        <v>https://music.apple.com/us/album/need-your-love/1884740422</v>
       </c>
       <c r="L135" t="str">
-        <v>Just A Kid - Sam Barber</v>
+        <v>Need Your Love - OneRepublic</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Country And She Knows It</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/country-and-she-knows-it/1882890988</v>
+        <v>https://music.apple.com/us/song/my-mouth-is-lonely-for-you-from-mother-mary/1886744205</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Country And She Knows It - Single</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:54</v>
+        <v>4:04</v>
       </c>
       <c r="H136" t="str">
-        <v>Luke Bryan</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/country-and-she-knows-it/1882890986</v>
+        <v>https://music.apple.com/us/album/my-mouth-is-lonely-for-you-from-mother-mary/1886744203</v>
       </c>
       <c r="L136" t="str">
-        <v>Country And She Knows It - Luke Bryan</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Georgia On My Mind</v>
+        <v>SORRY! CRASH!</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/georgia-on-my-mind/1882128424</v>
+        <v>https://music.apple.com/us/song/sorry-crash/1886485698</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Georgia On My Mind - Single</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G137" t="str">
-        <v>2:35</v>
+        <v>3:09</v>
       </c>
       <c r="H137" t="str">
-        <v>Thomas Rhett</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/thomas-rhett/502541718</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/georgia-on-my-mind/1882128423</v>
+        <v>https://music.apple.com/us/album/sorry-crash/1886485694</v>
       </c>
       <c r="L137" t="str">
-        <v>Georgia On My Mind - Thomas Rhett</v>
+        <v>SORRY! CRASH! - Ecca Vandal</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Deep Blue</v>
+        <v>Shine Again</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/deep-blue/1885061185</v>
+        <v>https://music.apple.com/us/song/shine-again/1887991690</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Deep Blue</v>
+        <v>Shine Again - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:17</v>
+        <v>4:05</v>
       </c>
       <c r="H138" t="str">
-        <v>ERNEST</v>
+        <v>Weezer</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/deep-blue/1885061168</v>
+        <v>https://music.apple.com/us/album/shine-again/1887991688</v>
       </c>
       <c r="L138" t="str">
-        <v>Deep Blue - ERNEST</v>
+        <v>Shine Again - Weezer</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Special</v>
+        <v>Choose Love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/special/1860405766</v>
+        <v>https://music.apple.com/us/song/choose-love/1877910665</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>sounds for someone</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G139" t="str">
-        <v>2:49</v>
+        <v>3:54</v>
       </c>
       <c r="H139" t="str">
-        <v>Elmiene</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/special/1860405416</v>
+        <v>https://music.apple.com/us/album/choose-love/1877910655</v>
       </c>
       <c r="L139" t="str">
-        <v>Special - Elmiene</v>
+        <v>Choose Love - Ringo Starr</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Heart Attack</v>
+        <v>BABYRECORDS.</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/heart-attack/1874761578</v>
+        <v>https://music.apple.com/us/song/babyrecords/1888590545</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>CANDY</v>
+        <v>BABYRECORDS. - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:52</v>
+        <v>2:29</v>
       </c>
       <c r="H140" t="str">
-        <v>Justine Skye</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/justine-skye/685830864</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/heart-attack/1874761574</v>
+        <v>https://music.apple.com/us/album/babyrecords/1888590544</v>
       </c>
       <c r="L140" t="str">
-        <v>Heart Attack - Justine Skye</v>
+        <v>BABYRECORDS. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>STAY</v>
+        <v>Paperbag Boy</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/stay/1882902388</v>
+        <v>https://music.apple.com/us/song/paperbag-boy/1889345415</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>STAY - Single</v>
+        <v>Paperbag Boy - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:06</v>
+        <v>3:11</v>
       </c>
       <c r="H141" t="str">
-        <v>Stray Kids</v>
+        <v>Trippie Redd</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/stray-kids/1304823362</v>
+        <v>https://music.apple.com/us/artist/trippie-redd/1203172438</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/stay/1882902387</v>
+        <v>https://music.apple.com/us/album/paperbag-boy/1889345414</v>
       </c>
       <c r="L141" t="str">
-        <v>STAY - Stray Kids</v>
+        <v>Paperbag Boy - Trippie Redd</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Unglued</v>
+        <v>I AM</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/unglued/1869618289</v>
+        <v>https://music.apple.com/us/song/i-am/1880890454</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Work of Heart</v>
+        <v>CLARITY OF MIND</v>
       </c>
       <c r="G142" t="str">
-        <v>3:54</v>
+        <v>3:12</v>
       </c>
       <c r="H142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>OMAH LAY</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/unglued/1869617637</v>
+        <v>https://music.apple.com/us/album/i-am/1880890112</v>
       </c>
       <c r="L142" t="str">
-        <v>Unglued - Flatland Cavalry</v>
+        <v>I AM - OMAH LAY</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Ritual</v>
+        <v>Want Love</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ritual/1879895832</v>
+        <v>https://music.apple.com/us/song/want-love/1886384365</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Ritual - Single</v>
+        <v>Want Love - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:01</v>
+        <v>3:20</v>
       </c>
       <c r="H143" t="str">
-        <v>Icona Pop</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ritual/1879895655</v>
+        <v>https://music.apple.com/us/album/want-love/1886384355</v>
       </c>
       <c r="L143" t="str">
-        <v>Ritual - Icona Pop</v>
+        <v>Want Love - Mary J. Blige</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>The Best</v>
+        <v>Live, Love, Learn</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-best/1886447721</v>
+        <v>https://music.apple.com/us/song/live-love-learn/1884749128</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Wishbone (Deluxe)</v>
+        <v>Live, Love, Learn - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:48</v>
+        <v>4:19</v>
       </c>
       <c r="H144" t="str">
-        <v>Conan Gray</v>
+        <v>Estelle</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/conan-gray/1168567308</v>
+        <v>https://music.apple.com/us/artist/estelle/27060010</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-best/1886447307</v>
+        <v>https://music.apple.com/us/album/live-love-learn/1884749126</v>
       </c>
       <c r="L144" t="str">
-        <v>The Best - Conan Gray</v>
+        <v>Live, Love, Learn - Estelle</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Smile</v>
+        <v>Remember to Forget</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/smile/1882074559</v>
+        <v>https://music.apple.com/us/song/remember-to-forget/1887886676</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Smile - Single</v>
+        <v>Remember to Forget - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:50</v>
+        <v>3:39</v>
       </c>
       <c r="H145" t="str">
-        <v>Two Shell</v>
+        <v>Hailey Whitters</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/two-shell/1480032608</v>
+        <v>https://music.apple.com/us/artist/hailey-whitters/553410914</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/smile/1882074557</v>
+        <v>https://music.apple.com/us/album/remember-to-forget/1887886674</v>
       </c>
       <c r="L145" t="str">
-        <v>Smile - Two Shell</v>
+        <v>Remember to Forget - Hailey Whitters</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Duro</v>
+        <v>Sun Comes Up Tremendous</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/duro/1885875641</v>
+        <v>https://music.apple.com/us/song/sun-comes-up-tremendous/1883229766</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Duro - Single</v>
+        <v>Sun Comes Up Tremendous - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:05</v>
+        <v>3:33</v>
       </c>
       <c r="H146" t="str">
-        <v>Skrillex</v>
+        <v>Disclosure</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/disclosure/520848228</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/duro/1885875640</v>
+        <v>https://music.apple.com/us/album/sun-comes-up-tremendous/1883229765</v>
       </c>
       <c r="L146" t="str">
-        <v>Duro - Skrillex</v>
+        <v>Sun Comes Up Tremendous - Disclosure</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Say So</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/until-the-sun-explodes/1886811453</v>
+        <v>https://music.apple.com/us/song/say-so/1888326036</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Say So - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:58</v>
+        <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>Sublime</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/until-the-sun-explodes/1886810990</v>
+        <v>https://music.apple.com/us/album/say-so/1888325785</v>
       </c>
       <c r="L147" t="str">
-        <v>Until The Sun Explodes - Sublime</v>
+        <v>Say So - Dan + Shay</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Carousel</v>
+        <v>Fantasy</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/carousel/1870989676</v>
+        <v>https://music.apple.com/us/song/fantasy/1880361475</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Everything Glows</v>
+        <v>Lost, Found &amp; Forgotten...</v>
       </c>
       <c r="G148" t="str">
-        <v>3:36</v>
+        <v>4:07</v>
       </c>
       <c r="H148" t="str">
-        <v>Cannons</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/carousel/1870989672</v>
+        <v>https://music.apple.com/us/album/fantasy/1880361449</v>
       </c>
       <c r="L148" t="str">
-        <v>Carousel - Cannons</v>
+        <v>Fantasy - Chris Stussy</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Mercy</v>
+        <v>Favour</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/mercy/1886265015</v>
+        <v>https://music.apple.com/us/song/favour/1885941038</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Mercy - Single</v>
+        <v>Favour - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:49</v>
+        <v>3:14</v>
       </c>
       <c r="H149" t="str">
-        <v>PRESIDENT</v>
+        <v>FISHER</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/mercy/1886265013</v>
+        <v>https://music.apple.com/us/album/favour/1885941037</v>
       </c>
       <c r="L149" t="str">
-        <v>Mercy - PRESIDENT</v>
+        <v>Favour - FISHER</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Palms</v>
+        <v>Dangerous Lover</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/palms/1881920935</v>
+        <v>https://music.apple.com/us/song/dangerous-lover/1884781285</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Palms - Single</v>
+        <v>Dangerous Lover - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:18</v>
+        <v>3:24</v>
       </c>
       <c r="H150" t="str">
-        <v>The Maine</v>
+        <v>Sekou</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/sekou/1685844750</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/palms/1881920662</v>
+        <v>https://music.apple.com/us/album/dangerous-lover/1884781284</v>
       </c>
       <c r="L150" t="str">
-        <v>Palms - The Maine</v>
+        <v>Dangerous Lover - Sekou</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ozzy's Song</v>
+        <v>Foolsong</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ozzys-song/1887370019</v>
+        <v>https://music.apple.com/us/song/foolsong/1886215975</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Engines of Demolition (Apple Music Deluxe Edition)</v>
+        <v>Foolsong - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:28</v>
+        <v>3:18</v>
       </c>
       <c r="H151" t="str">
-        <v>Black Label Society</v>
+        <v>aron!</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ozzys-song/1887369752</v>
+        <v>https://music.apple.com/us/album/foolsong/1886215974</v>
       </c>
       <c r="L151" t="str">
-        <v>Ozzy's Song - Black Label Society</v>
+        <v>Foolsong - aron!</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Danger</v>
+        <v>I Don't Wanna Be</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/danger/1885822963</v>
+        <v>https://music.apple.com/us/song/i-dont-wanna-be/1888501665</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Danger - Single</v>
+        <v>I Don't Wanna Be - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:19</v>
+        <v>3:16</v>
       </c>
       <c r="H152" t="str">
-        <v>Nia Archives</v>
+        <v>Blake Rose</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/blake-rose/1167991720</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/danger/1885822552</v>
+        <v>https://music.apple.com/us/album/i-dont-wanna-be/1888501664</v>
       </c>
       <c r="L152" t="str">
-        <v>Danger - Nia Archives</v>
+        <v>I Don't Wanna Be - Blake Rose</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Icarus</v>
+        <v>Lonesome Dove</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/icarus/1884315730</v>
+        <v>https://music.apple.com/us/song/lonesome-dove/1874700246</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Icarus - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G153" t="str">
-        <v>4:25</v>
+        <v>3:04</v>
       </c>
       <c r="H153" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/olivia-obrien/1023538468</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/icarus/1884315726</v>
+        <v>https://music.apple.com/us/album/lonesome-dove/1874700242</v>
       </c>
       <c r="L153" t="str">
-        <v>Icarus - Olivia O'Brien</v>
+        <v>Lonesome Dove - Charley Crockett</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>idk idk</v>
+        <v>Cowgirl's Prayer</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/idk-idk/1886524286</v>
+        <v>https://music.apple.com/us/song/cowgirls-prayer/1884167296</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>idk idk - Single</v>
+        <v>Cowgirl's Prayer - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:26</v>
+        <v>3:49</v>
       </c>
       <c r="H154" t="str">
-        <v>Jim Legxacy</v>
+        <v>Danielle Bradbery</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jim-legxacy/1460066773</v>
+        <v>https://music.apple.com/us/artist/danielle-bradbery/624068729</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/idk-idk/1886524284</v>
+        <v>https://music.apple.com/us/album/cowgirls-prayer/1884167295</v>
       </c>
       <c r="L154" t="str">
-        <v>idk idk - Jim Legxacy</v>
+        <v>Cowgirl's Prayer - Danielle Bradbery</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tonight</v>
+        <v>Hall of Fame</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/tonight/1885996687</v>
+        <v>https://music.apple.com/us/song/hall-of-fame/1886576289</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Tonight - Single</v>
+        <v>Hall of Fame - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:25</v>
+        <v>3:11</v>
       </c>
       <c r="H155" t="str">
-        <v>girlsweetvoiced</v>
+        <v>Chxrry</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/girlsweetvoiced/1791358712</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/tonight/1885996684</v>
+        <v>https://music.apple.com/us/album/hall-of-fame/1886576288</v>
       </c>
       <c r="L155" t="str">
-        <v>Tonight - girlsweetvoiced</v>
+        <v>Hall of Fame - Chxrry</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Klouds Will Carry Me To Sleep</v>
+        <v>Fashion</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/klouds-will-carry-me-to-sleep/1882818391</v>
+        <v>https://music.apple.com/us/song/fashion/1887487303</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Switcheroo</v>
+        <v>Fashion - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:44</v>
+        <v>2:08</v>
       </c>
       <c r="H156" t="str">
-        <v>Gelli Haha</v>
+        <v>IVE</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/gelli-haha/1797160694</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/klouds-will-carry-me-to-sleep/1882818124</v>
+        <v>https://music.apple.com/us/album/fashion/1887487297</v>
       </c>
       <c r="L156" t="str">
-        <v>Klouds Will Carry Me To Sleep - Gelli Haha</v>
+        <v>Fashion - IVE</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>WE ON GO III (feat. TiaCorine)</v>
+        <v>heal</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/we-on-go-iii-feat-tiacorine/1887372444</v>
+        <v>https://music.apple.com/us/song/heal/1880216061</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WE ON GO PACK - EP</v>
+        <v>Unfold</v>
       </c>
       <c r="G157" t="str">
-        <v>2:45</v>
+        <v>3:59</v>
       </c>
       <c r="H157" t="str">
-        <v>BIA</v>
+        <v>MONSTA X</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bia/1112309486</v>
+        <v>https://music.apple.com/us/artist/monsta-x/992315362</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/we-on-go-iii-feat-tiacorine/1887372441</v>
+        <v>https://music.apple.com/us/album/heal/1880216060</v>
       </c>
       <c r="L157" t="str">
-        <v>WE ON GO III (feat. TiaCorine) - BIA</v>
+        <v>heal - MONSTA X</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>this girl wants everything</v>
+        <v>Beautiful</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/this-girl-wants-everything/1884983628</v>
+        <v>https://music.apple.com/us/song/beautiful/1887979307</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Beautiful - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:33</v>
+        <v>3:35</v>
       </c>
       <c r="H158" t="str">
-        <v>Isaia Huron</v>
+        <v>Anyma</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/this-girl-wants-everything/1884983213</v>
+        <v>https://music.apple.com/us/album/beautiful/1887979305</v>
       </c>
       <c r="L158" t="str">
-        <v>this girl wants everything - Isaia Huron</v>
+        <v>Beautiful - Anyma</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>BRITTANY MURPHY.</v>
+        <v>Wildfire</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/brittany-murphy/1867531545</v>
+        <v>https://music.apple.com/us/song/wildfire/1887444526</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>For All The Right Reasons Vol. 1</v>
       </c>
       <c r="G159" t="str">
-        <v>3:44</v>
+        <v>3:11</v>
       </c>
       <c r="H159" t="str">
-        <v>Slayyyter</v>
+        <v>Lekan</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/brittany-murphy/1867530577</v>
+        <v>https://music.apple.com/us/album/wildfire/1887444297</v>
       </c>
       <c r="L159" t="str">
-        <v>BRITTANY MURPHY. - Slayyyter</v>
+        <v>Wildfire - Lekan</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Kingdom of Fear</v>
+        <v>Sliced by a Fingernail</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/kingdom-of-fear/1887606227</v>
+        <v>https://music.apple.com/us/song/sliced-by-a-fingernail/1879769225</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Deep Water - EP</v>
+        <v>Sliced by a Fingernail - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:41</v>
+        <v>4:08</v>
       </c>
       <c r="H160" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Dry Cleaning</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/dry-cleaning/1469164908</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/kingdom-of-fear/1887606218</v>
+        <v>https://music.apple.com/us/album/sliced-by-a-fingernail/1879769223</v>
       </c>
       <c r="L160" t="str">
-        <v>Kingdom of Fear - Cameron Whitcomb</v>
+        <v>Sliced by a Fingernail - Dry Cleaning</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>R3verse</v>
+        <v>FENIAN (feat. Casiokids)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/r3verse/1884444862</v>
+        <v>https://music.apple.com/us/song/fenian-feat-casiokids/1881565596</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>takeaways</v>
+        <v>FENIAN - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:31</v>
+        <v>3:14</v>
       </c>
       <c r="H161" t="str">
-        <v>Medium Build</v>
+        <v>Kneecap</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/medium-build/1034696339</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/r3verse/1884444861</v>
+        <v>https://music.apple.com/us/album/fenian-feat-casiokids/1881565579</v>
       </c>
       <c r="L161" t="str">
-        <v>R3verse - Medium Build</v>
+        <v>FENIAN (feat. Casiokids) - Kneecap</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Leadbelly (feat. MIKE)</v>
+        <v>Sólo Tú</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/leadbelly-feat-mike/1870867495</v>
+        <v>https://music.apple.com/us/song/s%C3%B3lo-t%C3%BA/1887417656</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Sólo Tú - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:32</v>
+        <v>2:37</v>
       </c>
       <c r="H162" t="str">
-        <v>MIKE</v>
+        <v>Los Primos Del Este</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/los-primos-del-este/1462043487</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/leadbelly-feat-mike/1870867411</v>
+        <v>https://music.apple.com/us/album/s%C3%B3lo-t%C3%BA/1887417649</v>
       </c>
       <c r="L162" t="str">
-        <v>Leadbelly (feat. MIKE) - MIKE</v>
+        <v>Sólo Tú - Los Primos Del Este</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>heart of gold</v>
+        <v>The Jesus I Know Now</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/heart-of-gold/1885691150</v>
+        <v>https://music.apple.com/us/song/the-jesus-i-know-now/1887978274</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>heart of gold - Single</v>
+        <v>The Jesus I Know Now - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:51</v>
+        <v>3:33</v>
       </c>
       <c r="H163" t="str">
-        <v>kai devega</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kai-devega/1760413396</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/heart-of-gold/1885691148</v>
+        <v>https://music.apple.com/us/album/the-jesus-i-know-now/1887978263</v>
       </c>
       <c r="L163" t="str">
-        <v>heart of gold - kai devega</v>
+        <v>The Jesus I Know Now - Brandon Lake</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Breaking Down</v>
+        <v>Turnstile</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/breaking-down/1882892615</v>
+        <v>https://music.apple.com/us/song/turnstile/1867616937</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Skeletor</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G164" t="str">
-        <v>4:21</v>
+        <v>3:50</v>
       </c>
       <c r="H164" t="str">
-        <v>Chief Keef</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/breaking-down/1882892614</v>
+        <v>https://music.apple.com/us/album/turnstile/1867616617</v>
       </c>
       <c r="L164" t="str">
-        <v>Breaking Down - Chief Keef</v>
+        <v>Turnstile - Dermot Kennedy</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Dream House</v>
+        <v>Surrender (From Your Friends &amp; Neighbors)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/dream-house/1871195178</v>
+        <v>https://music.apple.com/us/song/surrender-from-your-friends-neighbors/1887371368</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Dream House - Single</v>
+        <v>Surrender (From Your Friends &amp; Neighbors) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:54</v>
+        <v>3:04</v>
       </c>
       <c r="H165" t="str">
-        <v>Empress Of</v>
+        <v>Lindsey Stirling</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/empress-of/568038037</v>
+        <v>https://music.apple.com/us/artist/lindsey-stirling/403025113</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/dream-house/1871195176</v>
+        <v>https://music.apple.com/us/album/surrender-from-your-friends-neighbors/1887371353</v>
       </c>
       <c r="L165" t="str">
-        <v>Dream House - Empress Of</v>
+        <v>Surrender (From Your Friends &amp; Neighbors) - Lindsey Stirling</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Baby Blue</v>
+        <v>Before This Even Starts</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/baby-blue/1886255177</v>
+        <v>https://music.apple.com/us/song/before-this-even-starts/1883698214</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Baby Blue / When It Comes To Loving You - Single</v>
+        <v>Therapy &amp; Yoga - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>2:51</v>
+        <v>2:44</v>
       </c>
       <c r="H166" t="str">
-        <v>Cody Simpson</v>
+        <v>JESSIA</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/cody-simpson/343196171</v>
+        <v>https://music.apple.com/us/artist/jessia/1399415802</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/baby-blue/1886255174</v>
+        <v>https://music.apple.com/us/album/before-this-even-starts/1883698028</v>
       </c>
       <c r="L166" t="str">
-        <v>Baby Blue - Cody Simpson</v>
+        <v>Before This Even Starts - JESSIA</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile)</v>
+        <v>Roses</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/dont-wanna-go-home-feat-henry-camamile/1883806528</v>
+        <v>https://music.apple.com/us/song/roses/1883777517</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - Single</v>
+        <v>Middle School Dropout - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>2:37</v>
+        <v>3:10</v>
       </c>
       <c r="H167" t="str">
-        <v>MEDUZA</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/meduza/1449138676</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/dont-wanna-go-home-feat-henry-camamile/1883806456</v>
+        <v>https://music.apple.com/us/album/roses/1883777352</v>
       </c>
       <c r="L167" t="str">
-        <v>Don’t Wanna Go Home (feat. Henry Camamile) - MEDUZA</v>
+        <v>Roses - Iris Copperman</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Wake Up, Mr. Crow</v>
+        <v>Does Your Father Know You Dance Like That?</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/wake-up-mr-crow/1884987644</v>
+        <v>https://music.apple.com/us/song/does-your-father-know-you-dance-like-that/1886621446</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Forever Now</v>
+        <v>Does Your Father Know You Dance Like That? - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:05</v>
+        <v>2:28</v>
       </c>
       <c r="H168" t="str">
-        <v>Switchfoot</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/wake-up-mr-crow/1884987638</v>
+        <v>https://music.apple.com/us/album/does-your-father-know-you-dance-like-that/1886621445</v>
       </c>
       <c r="L168" t="str">
-        <v>Wake Up, Mr. Crow - Switchfoot</v>
+        <v>Does Your Father Know You Dance Like That? - Steve Aoki</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>She Was Just a Stranger</v>
+        <v>Loco</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/she-was-just-a-stranger/1885677049</v>
+        <v>https://music.apple.com/us/song/loco/1888397210</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>Loco - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:46</v>
+        <v>2:34</v>
       </c>
       <c r="H169" t="str">
-        <v>Benny G</v>
+        <v>Key Glock</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/she-was-just-a-stranger/1885677041</v>
+        <v>https://music.apple.com/us/album/loco/1888397209</v>
       </c>
       <c r="L169" t="str">
-        <v>She Was Just a Stranger - Benny G</v>
+        <v>Loco - Key Glock</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Cry In Front Of You</v>
+        <v>Hold It For Her</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/cry-in-front-of-you/1884163636</v>
+        <v>https://music.apple.com/us/song/hold-it-for-her/1861380253</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Cry In Front Of You - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G170" t="str">
-        <v>3:03</v>
+        <v>3:48</v>
       </c>
       <c r="H170" t="str">
-        <v>Eric Bellinger</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/eric-bellinger/395826107</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/cry-in-front-of-you/1884163349</v>
+        <v>https://music.apple.com/us/album/hold-it-for-her/1861380240</v>
       </c>
       <c r="L170" t="str">
-        <v>Cry In Front Of You - Eric Bellinger</v>
+        <v>Hold It For Her - Peach PRC</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Come On, Let’s Get It</v>
+        <v>Ghost town...</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/come-on-lets-get-it/1880699568</v>
+        <v>https://music.apple.com/us/song/ghost-town/1870971561</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>AK Cuts: Vol 3 - EP</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G171" t="str">
-        <v>4:19</v>
+        <v>2:44</v>
       </c>
       <c r="H171" t="str">
-        <v>Anish Kumar</v>
+        <v>R3HAB</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/come-on-lets-get-it/1880699566</v>
+        <v>https://music.apple.com/us/album/ghost-town/1870971550</v>
       </c>
       <c r="L171" t="str">
-        <v>Come On, Let’s Get It - Anish Kumar</v>
+        <v>Ghost town... - R3HAB</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>GASLIGHT</v>
+        <v>WASTE SOME TIME</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/gaslight/1887369247</v>
+        <v>https://music.apple.com/us/song/waste-some-time/1887768620</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>GASLIGHT - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G172" t="str">
-        <v>2:10</v>
+        <v>3:26</v>
       </c>
       <c r="H172" t="str">
-        <v>WesGhost</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/gaslight/1887369246</v>
+        <v>https://music.apple.com/us/album/waste-some-time/1887768606</v>
       </c>
       <c r="L172" t="str">
-        <v>GASLIGHT - WesGhost</v>
+        <v>WASTE SOME TIME - Forrest Frank</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Truth To Be Told</v>
+        <v>control.</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/truth-to-be-told/1882891423</v>
+        <v>https://music.apple.com/us/song/control/1887392580</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Truth To Be Told - Single</v>
+        <v>control. - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:17</v>
+        <v>2:50</v>
       </c>
       <c r="H173" t="str">
-        <v>GERD</v>
+        <v>Paco</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/gerd/1586399854</v>
+        <v>https://music.apple.com/us/artist/paco/1513830139</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/truth-to-be-told/1882891422</v>
+        <v>https://music.apple.com/us/album/control/1887392578</v>
       </c>
       <c r="L173" t="str">
-        <v>Truth To Be Told - GERD</v>
+        <v>control. - Paco</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Free Your Mind</v>
+        <v>Wouldn't Try Again</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/free-your-mind/1884097804</v>
+        <v>https://music.apple.com/us/song/wouldnt-try-again/1889328836</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Free Your Mind - Single</v>
+        <v>Wouldn't Try Again - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:21</v>
+        <v>2:45</v>
       </c>
       <c r="H174" t="str">
-        <v>Prospa</v>
+        <v>Quail P</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/quail-p/1447409001</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/free-your-mind/1884097801</v>
+        <v>https://music.apple.com/us/album/wouldnt-try-again/1889328830</v>
       </c>
       <c r="L174" t="str">
-        <v>Free Your Mind - Prospa</v>
+        <v>Wouldn't Try Again - Quail P</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Down To The Bone</v>
+        <v>i need u</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/down-to-the-bone/1884402177</v>
+        <v>https://music.apple.com/us/song/i-need-u/1889349101</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Down To The Bone - Single</v>
+        <v>i need u - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:51</v>
+        <v>3:45</v>
       </c>
       <c r="H175" t="str">
-        <v>Josh Baker</v>
+        <v>BUNT.</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/down-to-the-bone/1884402173</v>
+        <v>https://music.apple.com/us/album/i-need-u/1889349100</v>
       </c>
       <c r="L175" t="str">
-        <v>Down To The Bone - Josh Baker</v>
+        <v>i need u - BUNT.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Breathe</v>
+        <v>Outlaw</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882913539</v>
+        <v>https://music.apple.com/us/song/outlaw/1877229747</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Breathe - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G176" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H176" t="str">
-        <v>Marlon Hoffstadt</v>
+        <v>Shinedown</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/marlon-hoffstadt/457222498</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882913535</v>
+        <v>https://music.apple.com/us/album/outlaw/1877229738</v>
       </c>
       <c r="L176" t="str">
-        <v>Breathe - Marlon Hoffstadt</v>
+        <v>Outlaw - Shinedown</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>xs</v>
+        <v>A.L.O.N.E.</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/xs/1886515563</v>
+        <v>https://music.apple.com/us/song/a-l-o-n-e/1886537119</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>xs - Single</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G177" t="str">
-        <v>3:19</v>
+        <v>3:24</v>
       </c>
       <c r="H177" t="str">
-        <v>Ashley Cooke</v>
+        <v>HEALTH</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/xs/1886515395</v>
+        <v>https://music.apple.com/us/album/a-l-o-n-e/1886536873</v>
       </c>
       <c r="L177" t="str">
-        <v>xs - Ashley Cooke</v>
+        <v>A.L.O.N.E. - HEALTH</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Sail</v>
+        <v>Him</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/sail/1883045745</v>
+        <v>https://music.apple.com/us/song/him/1887319676</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Him - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>4:54</v>
+        <v>2:07</v>
       </c>
       <c r="H178" t="str">
-        <v>Future Islands</v>
+        <v>Sheff G</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/sail/1883045480</v>
+        <v>https://music.apple.com/us/album/him/1887319675</v>
       </c>
       <c r="L178" t="str">
-        <v>Sail - Future Islands</v>
+        <v>Him - Sheff G</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Dreaming</v>
+        <v>MVP (feat. Key Glock)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/dreaming/1886158585</v>
+        <v>https://music.apple.com/us/song/mvp-feat-key-glock/1888298376</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Dear Nashville</v>
+        <v>AREA 41</v>
       </c>
       <c r="G179" t="str">
-        <v>3:33</v>
+        <v>3:08</v>
       </c>
       <c r="H179" t="str">
-        <v>Ashley Monroe</v>
+        <v>41</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/ashley-monroe/55466160</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/dreaming/1886158441</v>
+        <v>https://music.apple.com/us/album/mvp-feat-key-glock/1888298368</v>
       </c>
       <c r="L179" t="str">
-        <v>Dreaming - Ashley Monroe</v>
+        <v>MVP (feat. Key Glock) - 41</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>NEW TINGZ</v>
+        <v>S.I.M.P.L.E</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/new-tingz/1884461925</v>
+        <v>https://music.apple.com/us/song/s-i-m-p-l-e/1885386665</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>THE IMPACT (Deluxe): PGLA Edition</v>
+        <v>DND</v>
       </c>
       <c r="G180" t="str">
-        <v>2:39</v>
+        <v>2:33</v>
       </c>
       <c r="H180" t="str">
-        <v>Armanii</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/armanii/1519476498</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/new-tingz/1884461924</v>
+        <v>https://music.apple.com/us/album/s-i-m-p-l-e/1885386569</v>
       </c>
       <c r="L180" t="str">
-        <v>NEW TINGZ - Armanii</v>
+        <v>S.I.M.P.L.E - TheARTI$t</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>La Opinión</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/la-opini%C3%B3n/1885934233</v>
+        <v>https://music.apple.com/us/song/at-least-shes-beautiful/1884405874</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Mis Compas El Final</v>
+        <v>At Least She's Beautiful - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:23</v>
+        <v>2:36</v>
       </c>
       <c r="H181" t="str">
-        <v>Joss Favela</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/joss-favela/547475643</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/la-opini%C3%B3n/1885934223</v>
+        <v>https://music.apple.com/us/album/at-least-shes-beautiful/1884405873</v>
       </c>
       <c r="L181" t="str">
-        <v>La Opinión - Joss Favela</v>
+        <v>At Least She's Beautiful - rjtheweirdo</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>qué ves en mí?</v>
+        <v>Hella Good (feat. Bonnie McKee)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/qu%C3%A9-ves-en-m%C3%AD/1887326301</v>
+        <v>https://music.apple.com/us/song/hella-good-feat-bonnie-mckee/1886001675</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>qué ves en mí? / interesante - Single</v>
+        <v>Hella Good (feat. Bonnie McKee) - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:24</v>
+        <v>3:45</v>
       </c>
       <c r="H182" t="str">
-        <v>Paloma Morphy</v>
+        <v>Trixie Mattel</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/paloma-morphy/1654342484</v>
+        <v>https://music.apple.com/us/artist/trixie-mattel/960467089</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/qu%C3%A9-ves-en-m%C3%AD/1887326298</v>
+        <v>https://music.apple.com/us/album/hella-good-feat-bonnie-mckee/1886001667</v>
       </c>
       <c r="L182" t="str">
-        <v>qué ves en mí? - Paloma Morphy</v>
+        <v>Hella Good (feat. Bonnie McKee) - Trixie Mattel</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Vengache Pa’ Aca</v>
+        <v>The Show</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/vengache-pa-aca/1886811016</v>
+        <v>https://music.apple.com/us/song/the-show/1889121528</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Vengache Pa’ Aca - Single</v>
+        <v>The Show - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:43</v>
+        <v>2:47</v>
       </c>
       <c r="H183" t="str">
-        <v>Edgardo Nuñez</v>
+        <v>DPR IAN</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/edgardo-nu%C3%B1ez/1546012648</v>
+        <v>https://music.apple.com/us/artist/dpr-ian/1500739803</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/vengache-pa-aca/1886811014</v>
+        <v>https://music.apple.com/us/album/the-show/1889121369</v>
       </c>
       <c r="L183" t="str">
-        <v>Vengache Pa’ Aca - Edgardo Nuñez</v>
+        <v>The Show - DPR IAN</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>TUTUTU</v>
+        <v>His Eye Is On the Sparrow</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tututu/1886801739</v>
+        <v>https://music.apple.com/us/song/his-eye-is-on-the-sparrow/1880392628</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>TUTUTU - Single</v>
+        <v>Grandma's Gospel Favorites</v>
       </c>
       <c r="G184" t="str">
-        <v>2:16</v>
+        <v>3:20</v>
       </c>
       <c r="H184" t="str">
-        <v>ELENA ROSE</v>
+        <v>Jason Mraz</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/jason-mraz/156987</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tututu/1886801737</v>
+        <v>https://music.apple.com/us/album/his-eye-is-on-the-sparrow/1880392609</v>
       </c>
       <c r="L184" t="str">
-        <v>TUTUTU - ELENA ROSE</v>
+        <v>His Eye Is On the Sparrow - Jason Mraz</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2</v>
+        <v>Slowly</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/southern-country-girl-part-2/1886499792</v>
+        <v>https://music.apple.com/us/song/slowly/1869140941</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - Single</v>
+        <v>Change Of Plans</v>
       </c>
       <c r="G185" t="str">
-        <v>2:56</v>
+        <v>3:11</v>
       </c>
       <c r="H185" t="str">
-        <v>2'Live Bre</v>
+        <v>49 Winchester</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/2live-bre/1447692492</v>
+        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/southern-country-girl-part-2/1886499790</v>
+        <v>https://music.apple.com/us/album/slowly/1869140544</v>
       </c>
       <c r="L185" t="str">
-        <v>SOUTHERN COUNTRY GIRL PART 2 - 2'Live Bre</v>
+        <v>Slowly - 49 Winchester</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Me Neither</v>
+        <v>On Our Way Along</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/me-neither/1867275482</v>
+        <v>https://music.apple.com/us/song/on-our-way-along/1863814124</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Heavy On The Soul</v>
+        <v>On Our Way Along - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:32</v>
+        <v>4:21</v>
       </c>
       <c r="H186" t="str">
-        <v>Ty Myers</v>
+        <v>Billy Ray Cyrus</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/billy-ray-cyrus/1793659079</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/me-neither/1867275110</v>
+        <v>https://music.apple.com/us/album/on-our-way-along/1863813853</v>
       </c>
       <c r="L186" t="str">
-        <v>Me Neither - Ty Myers</v>
+        <v>On Our Way Along - Billy Ray Cyrus</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Cole Palmer</v>
+        <v>COMING OF AGE</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/cole-palmer/1871565351</v>
+        <v>https://music.apple.com/us/song/coming-of-age/1882886175</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Solid Ground</v>
+        <v>COMING OF AGE - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:48</v>
+        <v>4:08</v>
       </c>
       <c r="H187" t="str">
-        <v>Limoblaze</v>
+        <v>METTE</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/limoblaze/993035016</v>
+        <v>https://music.apple.com/us/artist/mette/1553768125</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/cole-palmer/1871565347</v>
+        <v>https://music.apple.com/us/album/coming-of-age/1882886174</v>
       </c>
       <c r="L187" t="str">
-        <v>Cole Palmer - Limoblaze</v>
+        <v>COMING OF AGE - METTE</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Wonder</v>
+        <v>the man with money in his hands</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/wonder/1874405439</v>
+        <v>https://music.apple.com/us/song/the-man-with-money-in-his-hands/1887707057</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Wonder - Single</v>
+        <v>the man with money in his hands - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:48</v>
+        <v>2:57</v>
       </c>
       <c r="H188" t="str">
-        <v>Meeks Carter</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/meeks-carter/1451413595</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/wonder/1874405438</v>
+        <v>https://music.apple.com/us/album/the-man-with-money-in-his-hands/1887707053</v>
       </c>
       <c r="L188" t="str">
-        <v>Wonder - Meeks Carter</v>
+        <v>the man with money in his hands - Jessie Mazin</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ICU</v>
+        <v>WRANGLER</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/icu/1879881618</v>
+        <v>https://music.apple.com/us/song/wrangler/1876267962</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>ICU - Single</v>
+        <v>WHAT CAN I TELL U</v>
       </c>
       <c r="G189" t="str">
-        <v>2:53</v>
+        <v>2:05</v>
       </c>
       <c r="H189" t="str">
-        <v>Joseph O'Brien</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/joseph-obrien/272290619</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/icu/1879881617</v>
+        <v>https://music.apple.com/us/album/wrangler/1876267654</v>
       </c>
       <c r="L189" t="str">
-        <v>ICU - Joseph O'Brien</v>
+        <v>WRANGLER - Claudia Valentina</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Supermans Weakness (feat. Chris Brown)</v>
+        <v>Rydly</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/supermans-weakness-feat-chris-brown/1886020725</v>
+        <v>https://music.apple.com/us/song/rydly/1878477155</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Soundtrack 2 Get Her Back</v>
+        <v>We Are Friends, Vol. 12 (Disk 2)</v>
       </c>
       <c r="G190" t="str">
-        <v>2:45</v>
+        <v>6:52</v>
       </c>
       <c r="H190" t="str">
-        <v>Jozzy</v>
+        <v>deadmau5</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jozzy/1399337702</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/supermans-weakness-feat-chris-brown/1886020713</v>
+        <v>https://music.apple.com/us/album/rydly/1878476797</v>
       </c>
       <c r="L190" t="str">
-        <v>Supermans Weakness (feat. Chris Brown) - Jozzy</v>
+        <v>Rydly - deadmau5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Waiting Room (feat. Jordan Ward)</v>
+        <v>all the time</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/waiting-room-feat-jordan-ward/1884548258</v>
+        <v>https://music.apple.com/us/song/all-the-time/1874100418</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Single</v>
+        <v>ARCADE</v>
       </c>
       <c r="G191" t="str">
-        <v>3:21</v>
+        <v>3:01</v>
       </c>
       <c r="H191" t="str">
-        <v>Jenevieve</v>
+        <v>Deb Never</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jenevieve/1494362598</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/waiting-room-feat-jordan-ward/1884548243</v>
+        <v>https://music.apple.com/us/album/all-the-time/1874100412</v>
       </c>
       <c r="L191" t="str">
-        <v>Waiting Room (feat. Jordan Ward) - Jenevieve</v>
+        <v>all the time - Deb Never</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Other Side Of Blue</v>
+        <v>Misery</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-other-side-of-blue/1851110319</v>
+        <v>https://music.apple.com/us/song/misery/1888294484</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Rise</v>
+        <v>Misery - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:02</v>
+        <v>2:55</v>
       </c>
       <c r="H192" t="str">
-        <v>Melissa Etheridge</v>
+        <v>Alex Sampson</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/melissa-etheridge/117519</v>
+        <v>https://music.apple.com/us/artist/alex-sampson/1486112083</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-other-side-of-blue/1851110125</v>
+        <v>https://music.apple.com/us/album/misery/1888294483</v>
       </c>
       <c r="L192" t="str">
-        <v>The Other Side Of Blue - Melissa Etheridge</v>
+        <v>Misery - Alex Sampson</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Roll On Thru</v>
+        <v>Don't Fall</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/roll-on-thru/1872125100</v>
+        <v>https://music.apple.com/us/song/dont-fall/1884794995</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Roll On Thru - Single</v>
+        <v>Games - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>3:51</v>
+        <v>4:20</v>
       </c>
       <c r="H193" t="str">
-        <v>Hayden Everett</v>
+        <v>Common People</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/roll-on-thru/1872125099</v>
+        <v>https://music.apple.com/us/album/dont-fall/1884794990</v>
       </c>
       <c r="L193" t="str">
-        <v>Roll On Thru - Hayden Everett</v>
+        <v>Don't Fall - Common People</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Delicately</v>
+        <v>Alternate Ending</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/delicately/1880313498</v>
+        <v>https://music.apple.com/us/song/alternate-ending/1886010374</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Delicately - Single</v>
+        <v>Alternate Ending - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>3:10</v>
       </c>
       <c r="H194" t="str">
-        <v>Andrea Bejar</v>
+        <v>Thelma &amp; James</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/andrea-bejar/1644036486</v>
+        <v>https://music.apple.com/us/artist/thelma-james/1787091600</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/delicately/1880313492</v>
+        <v>https://music.apple.com/us/album/alternate-ending/1886010053</v>
       </c>
       <c r="L194" t="str">
-        <v>Delicately - Andrea Bejar</v>
+        <v>Alternate Ending - Thelma &amp; James</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>One Of Those Things</v>
+        <v>LuCkY</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/one-of-those-things/1880139237</v>
+        <v>https://music.apple.com/us/song/lucky/1888001208</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>One Of Those Things - Single</v>
+        <v>MOEWYA</v>
       </c>
       <c r="G195" t="str">
-        <v>3:27</v>
+        <v>2:17</v>
       </c>
       <c r="H195" t="str">
-        <v>Lucy Clearwater</v>
+        <v>MoeIsBetter</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lucy-clearwater/1109747461</v>
+        <v>https://music.apple.com/us/artist/moeisbetter/1762833637</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/one-of-those-things/1880139236</v>
+        <v>https://music.apple.com/us/album/lucky/1888001204</v>
       </c>
       <c r="L195" t="str">
-        <v>One Of Those Things - Lucy Clearwater</v>
+        <v>LuCkY - MoeIsBetter</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>For Every Dusk</v>
+        <v>Mutual</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/for-every-dusk/1860962166</v>
+        <v>https://music.apple.com/us/song/mutual/1882922798</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Against The Dying Of The Light</v>
+        <v>Mutual - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>6:04</v>
+        <v>3:49</v>
       </c>
       <c r="H196" t="str">
-        <v>José González</v>
+        <v>PJ Morton</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/pj-morton/44719201</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/for-every-dusk/1860962162</v>
+        <v>https://music.apple.com/us/album/mutual/1882922794</v>
       </c>
       <c r="L196" t="str">
-        <v>For Every Dusk - José González</v>
+        <v>Mutual - PJ Morton</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I'll Wait</v>
+        <v>Waiting On</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/ill-wait/1872032417</v>
+        <v>https://music.apple.com/us/song/waiting-on/1883846539</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Shoulder to Shoulder</v>
+        <v>Waiting On - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:33</v>
+        <v>3:11</v>
       </c>
       <c r="H197" t="str">
-        <v>Buzzy Lee</v>
+        <v>Tniyah</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/buzzy-lee/1341609373</v>
+        <v>https://music.apple.com/us/artist/tniyah/513967453</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/ill-wait/1872032415</v>
+        <v>https://music.apple.com/us/album/waiting-on/1883846538</v>
       </c>
       <c r="L197" t="str">
-        <v>I'll Wait - Buzzy Lee</v>
+        <v>Waiting On - Tniyah</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Daisy</v>
+        <v>En La Montaña</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/daisy/1879531184</v>
+        <v>https://music.apple.com/us/song/en-la-monta%C3%B1a/1884092212</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Daisy - Single</v>
+        <v>En La Montaña - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H198" t="str">
-        <v>Lola Blue</v>
+        <v>Nueva H</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/daisy/1879531182</v>
+        <v>https://music.apple.com/us/album/en-la-monta%C3%B1a/1884092207</v>
       </c>
       <c r="L198" t="str">
-        <v>Daisy - Lola Blue</v>
+        <v>En La Montaña - Nueva H</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Play (Objekt Remix)</v>
+        <v>Falling Short</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/play-objekt-remix/1884612004</v>
+        <v>https://music.apple.com/us/song/falling-short/1884803703</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Friend Remixes</v>
+        <v>Falling Short - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:57</v>
+        <v>3:05</v>
       </c>
       <c r="H199" t="str">
-        <v>james K</v>
+        <v>Hudson Macready</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/james-k/955915784</v>
+        <v>https://music.apple.com/us/artist/hudson-macready/1534530042</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/play-objekt-remix/1884611745</v>
+        <v>https://music.apple.com/us/album/falling-short/1884803515</v>
       </c>
       <c r="L199" t="str">
-        <v>Play (Objekt Remix) - james K</v>
+        <v>Falling Short - Hudson Macready</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Volverás (feat. Uma)</v>
+        <v>When You Give It Up</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/volver%C3%A1s-feat-uma/1880032399</v>
+        <v>https://music.apple.com/us/song/when-you-give-it-up/1879883866</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Perdidos - Single</v>
+        <v>When You Give It Up - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:45</v>
+        <v>2:42</v>
       </c>
       <c r="H200" t="str">
-        <v>MAVICA</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/mavica/566829940</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/volver%C3%A1s-feat-uma/1880032398</v>
+        <v>https://music.apple.com/us/album/when-you-give-it-up/1879883863</v>
       </c>
       <c r="L200" t="str">
-        <v>Volverás (feat. Uma) - MAVICA</v>
+        <v>When You Give It Up - Chelsea Plank</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Fort</v>
+        <v>Wasted</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/fort/1881952404</v>
+        <v>https://music.apple.com/us/song/wasted/1885578001</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Fort - Single</v>
+        <v>Wasted - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:27</v>
+        <v>3:18</v>
       </c>
       <c r="H201" t="str">
-        <v>Lamb</v>
+        <v>Highly Suspect</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lamb/1698218862</v>
+        <v>https://music.apple.com/us/artist/highly-suspect/419913603</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/fort/1881952403</v>
+        <v>https://music.apple.com/us/album/wasted/1885578000</v>
       </c>
       <c r="L201" t="str">
-        <v>Fort - Lamb</v>
+        <v>Wasted - Highly Suspect</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SAME LA</v>
+        <v>Burn</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/same-la/1881772805</v>
+        <v>https://music.apple.com/us/song/burn/1883195616</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>SAME LA - Single</v>
+        <v>Burn - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:44</v>
+        <v>2:56</v>
       </c>
       <c r="H202" t="str">
-        <v>Tiffany Day</v>
+        <v>Cold Court</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-day/1125468067</v>
+        <v>https://music.apple.com/us/artist/cold-court/1809708831</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/same-la/1881772354</v>
+        <v>https://music.apple.com/us/album/burn/1883195615</v>
       </c>
       <c r="L202" t="str">
-        <v>SAME LA - Tiffany Day</v>
+        <v>Burn - Cold Court</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Working On It</v>
+        <v>Smash</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/working-on-it/1885603912</v>
+        <v>https://music.apple.com/us/song/smash/1884655608</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Working On It - Single</v>
+        <v>Eternal BAM Nation</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>2:27</v>
       </c>
       <c r="H203" t="str">
-        <v>Arthur Hill</v>
+        <v>Born At Midnite</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/arthur-hill/1207962876</v>
+        <v>https://music.apple.com/us/artist/born-at-midnite/1497209280</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/working-on-it/1885603911</v>
+        <v>https://music.apple.com/us/album/smash/1884655462</v>
       </c>
       <c r="L203" t="str">
-        <v>Working On It - Arthur Hill</v>
+        <v>Smash - Born At Midnite</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>spring cleaning</v>
+        <v>Smile</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/spring-cleaning/1887331397</v>
+        <v>https://music.apple.com/us/song/smile/1859619683</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E204" t="str">
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>spring cleaning - Single</v>
+        <v>Birding</v>
       </c>
       <c r="G204" t="str">
-        <v>4:03</v>
+        <v>5:09</v>
       </c>
       <c r="H204" t="str">
-        <v>Ethan Regan</v>
+        <v>deary</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/ethan-regan/1329542870</v>
+        <v>https://music.apple.com/us/artist/deary/1641536096</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/spring-cleaning/1887331396</v>
+        <v>https://music.apple.com/us/album/smile/1859619407</v>
       </c>
       <c r="L204" t="str">
-        <v>spring cleaning - Ethan Regan</v>
+        <v>Smile - deary</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Just Drivin'</v>
+        <v>Eshi</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/just-drivin/1886177060</v>
+        <v>https://music.apple.com/us/song/eshi/1880700566</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E205" t="str">
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Just Drivin' - Single</v>
+        <v>Zero</v>
       </c>
       <c r="G205" t="str">
-        <v>3:26</v>
+        <v>3:12</v>
       </c>
       <c r="H205" t="str">
-        <v>Presley Haile</v>
+        <v>Alewya</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/presley-haile/1577106672</v>
+        <v>https://music.apple.com/us/artist/alewya/1450971317</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/just-drivin/1886177048</v>
+        <v>https://music.apple.com/us/album/eshi/1880699673</v>
       </c>
       <c r="L205" t="str">
-        <v>Just Drivin' - Presley Haile</v>
+        <v>Eshi - Alewya</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Simple Things</v>
+        <v>NO HOMEGIRLS</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/simple-things/1884763128</v>
+        <v>https://music.apple.com/us/song/no-homegirls/1886801763</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E206" t="str">
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Simple Things - Single</v>
+        <v>NO HOMEGIRLS - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:46</v>
+        <v>2:05</v>
       </c>
       <c r="H206" t="str">
-        <v>Evening Elephants</v>
+        <v>BBYKOBE</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/bbykobe/1693491560</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/simple-things/1884763127</v>
+        <v>https://music.apple.com/us/album/no-homegirls/1886801762</v>
       </c>
       <c r="L206" t="str">
-        <v>Simple Things - Evening Elephants</v>
+        <v>NO HOMEGIRLS - BBYKOBE</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Want It Back</v>
+        <v>I Want You Back</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/want-it-back/1885904818</v>
+        <v>https://music.apple.com/us/song/i-want-you-back/1889281139</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E207" t="str">
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Want It Back - Single</v>
+        <v>I Want You Back - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>3:27</v>
+        <v>3:18</v>
       </c>
       <c r="H207" t="str">
-        <v>Giant Rooks</v>
+        <v>Johnny Venus</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/giant-rooks/1181446985</v>
+        <v>https://music.apple.com/us/artist/johnny-venus/1777129720</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/want-it-back/1885904812</v>
+        <v>https://music.apple.com/us/album/i-want-you-back/1889281136</v>
       </c>
       <c r="L207" t="str">
-        <v>Want It Back - Giant Rooks</v>
+        <v>I Want You Back - Johnny Venus</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Bite Down</v>
+        <v>Needed You</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/bite-down/1877982010</v>
+        <v>https://music.apple.com/us/song/needed-you/1887702402</v>
       </c>
       <c r="D208" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E208" t="str">
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Bite Down - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G208" t="str">
-        <v>3:36</v>
+        <v>3:17</v>
       </c>
       <c r="H208" t="str">
-        <v>Anna Sofia</v>
+        <v>Active Child</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/anna-sofia/1457876137</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/bite-down/1877982009</v>
+        <v>https://music.apple.com/us/album/needed-you/1887701924</v>
       </c>
       <c r="L208" t="str">
-        <v>Bite Down - Anna Sofia</v>
+        <v>Needed You - Active Child</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Ulvgjeld &amp; Blodsodel</v>
+        <v>Finish Line</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/ulvgjeld-blodsodel/1883121672</v>
+        <v>https://music.apple.com/us/song/finish-line/1887371855</v>
       </c>
       <c r="D209" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E209" t="str">
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Finish Line - Single</v>
       </c>
       <c r="G209" t="str">
-        <v>5:42</v>
+        <v>3:18</v>
       </c>
       <c r="H209" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/ulvgjeld-blodsodel/1883121436</v>
+        <v>https://music.apple.com/us/album/finish-line/1887371854</v>
       </c>
       <c r="L209" t="str">
-        <v>Ulvgjeld &amp; Blodsodel - Dimmu Borgir</v>
+        <v>Finish Line - Ally Salort</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Demons</v>
+        <v>Daredevil</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/demons/1884707577</v>
+        <v>https://music.apple.com/us/song/daredevil/1883231048</v>
       </c>
       <c r="D210" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E210" t="str">
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Ask Me How I’ve Been</v>
+        <v>Daredevil - Single</v>
       </c>
       <c r="G210" t="str">
-        <v>2:42</v>
+        <v>4:16</v>
       </c>
       <c r="H210" t="str">
-        <v>Anella</v>
+        <v>Zach Hood</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/anella/1789704259</v>
+        <v>https://music.apple.com/us/artist/zach-hood/1518857330</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/demons/1884707575</v>
+        <v>https://music.apple.com/us/album/daredevil/1883231047</v>
       </c>
       <c r="L210" t="str">
-        <v>Demons - Anella</v>
+        <v>Daredevil - Zach Hood</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Es brennt...</v>
+        <v>Asleep On The Killing Floor</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/es-brennt/1887318990</v>
+        <v>https://music.apple.com/us/song/asleep-on-the-killing-floor/1869086163</v>
       </c>
       <c r="D211" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E211" t="str">
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Es brennt... - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G211" t="str">
-        <v>3:35</v>
+        <v>4:08</v>
       </c>
       <c r="H211" t="str">
-        <v>Till Lindemann</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/till-lindemann/20851094</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/es-brennt/1887318989</v>
+        <v>https://music.apple.com/us/album/asleep-on-the-killing-floor/1869085524</v>
       </c>
       <c r="L211" t="str">
-        <v>Es brennt... - Till Lindemann</v>
+        <v>Asleep On The Killing Floor - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Fire Marengo</v>
+        <v>You Bastard</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/fire-marengo/1880687773</v>
+        <v>https://music.apple.com/us/song/you-bastard/1871211807</v>
       </c>
       <c r="D212" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E212" t="str">
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>Enslaved &amp; Storm Weather Shanty Choir - Single</v>
+        <v>Neverending</v>
       </c>
       <c r="G212" t="str">
-        <v>3:49</v>
+        <v>4:19</v>
       </c>
       <c r="H212" t="str">
-        <v>Enslaved</v>
+        <v>Monolord</v>
       </c>
       <c r="I212" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/enslaved/251500660</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/fire-marengo/1880687771</v>
+        <v>https://music.apple.com/us/album/you-bastard/1871211801</v>
       </c>
       <c r="L212" t="str">
-        <v>Fire Marengo - Enslaved</v>
+        <v>You Bastard - Monolord</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Close to the Bone</v>
+        <v>Vanilla Latte</v>
       </c>
       <c r="B213" t="str">
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/close-to-the-bone/1872193861</v>
+        <v>https://music.apple.com/us/song/vanilla-latte/1884524943</v>
       </c>
       <c r="D213" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E213" t="str">
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>Vanilla Latte - EP</v>
       </c>
       <c r="G213" t="str">
-        <v>4:09</v>
+        <v>2:24</v>
       </c>
       <c r="H213" t="str">
-        <v>Armored Saint</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I213" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/close-to-the-bone/1872193859</v>
+        <v>https://music.apple.com/us/album/vanilla-latte/1884524941</v>
       </c>
       <c r="L213" t="str">
-        <v>Close to the Bone - Armored Saint</v>
+        <v>Vanilla Latte - The Barbarians of California</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Back Home</v>
+        <v>Nostalgia Kills</v>
       </c>
       <c r="B214" t="str">
         <v/>
       </c>
       <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/nostalgia-kills/1887961043</v>
       </c>
       <c r="D214" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E214" t="str">
         <v/>
       </c>
       <c r="F214" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Nostalgia Kills - Single</v>
       </c>
       <c r="G214" t="str">
-        <v>1:36</v>
+        <v>3:03</v>
       </c>
       <c r="H214" t="str">
-        <v>MIKE</v>
+        <v>Static Dress</v>
       </c>
       <c r="I214" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/static-dress/1476714067</v>
       </c>
       <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/nostalgia-kills/1887961038</v>
       </c>
       <c r="L214" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Nostalgia Kills - Static Dress</v>
       </c>
     </row>
   </sheetData>

--- a/data/global/2026-04-week01/titles.xlsx
+++ b/data/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L214"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שילה שטראל - תקופה שלמה</v>
+        <v>שושנה קנו - סיגריות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410340&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410351&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-03</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שילה שטראל - תקופה שלמה</v>
+        <v>שושנה קנו - סיגריות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רון סויסה - האור בחשכה</v>
+        <v>רפאל אלוש - שערי שמיים פתח</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410339&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410350&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-03</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רון סויסה - האור בחשכה</v>
+        <v>רפאל אלוש - שערי שמיים פתח</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ישראל בניטה - מי אני</v>
+        <v>יואש - להינשא הלילה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410338&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410349&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-03</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ישראל בניטה - מי אני</v>
+        <v>יואש - להינשא הלילה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
+        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410337&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410348&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-03</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
+        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+        <v>אוראל &amp; ויק - צ׳לה בלה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410336&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410347&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-03</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+        <v>אוראל &amp; ויק - צ׳לה בלה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+        <v>שי פורטוגלי - עד מתי</v>
       </c>
       <c r="B7" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410335&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410346&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-03</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+        <v>שי פורטוגלי - עד מתי</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+        <v>פרחי ירושלים - ביבי מיקונה</v>
       </c>
       <c r="B8" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410334&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410345&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-03</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+        <v>פרחי ירושלים - ביבי מיקונה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>גל סינואני - יום יפה</v>
+        <v>נעם בוסקילה - והיא שעמדה</v>
       </c>
       <c r="B9" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410333&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410344&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-03</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>גל סינואני - יום יפה</v>
+        <v>נעם בוסקילה - והיא שעמדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>גל אדם - כבר לא שלך</v>
+        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
       </c>
       <c r="B10" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410332&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410343&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-03</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>גל אדם - כבר לא שלך</v>
+        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+        <v>דולב הרץ - אהבה</v>
       </c>
       <c r="B11" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410331&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410342&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-03</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+        <v>דולב הרץ - אהבה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
+        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
       </c>
       <c r="B12" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410330&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410341&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-03</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
+        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-04-03</v>
+        <v>4d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410329&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-03</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>3:55</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-04-03</v>
+        <v>4d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410328&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-03</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>2:45</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Ocean Alley</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>אביב לוי - דרום אמריקה</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-04-03</v>
+        <v>4d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410327&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-03</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>4d ago</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>6:29</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>RAYE</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>אביב לוי - דרום אמריקה</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>BTS Arirang</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-04-03</v>
+        <v>6d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://yosmusic.com/bts-arirang/</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-03</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>האלבום Arirang של BTS (שיצא במרץ 2026) הפך בתוך שבועות ספורים לאחד התקליטים המבוקשים בעולם גם פיזית (ויניל/מהדורות אספנים) וגם סטרימינג, וזה לא במקרה. מדובר בשילוב נדיר של אירוע תרבותי, מהלך מוזיקלי מחושב, ורגע רגשי של קאמבק. בעיני המעריצים, זה</v>
+        <v>6d ago</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Take That</v>
       </c>
       <c r="I16" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>BTS Arirang</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-04-03</v>
+        <v>6d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=23054&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-03</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>08:36</v>
+        <v>6d ago</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>4:22</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>Armik</v>
       </c>
       <c r="I17" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>אֶריק ברמן - אהבה ואלוהים אחרים 2017</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-03</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:55</v>
+        <v>4:10</v>
       </c>
       <c r="H18" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B19" t="str">
-        <v>4d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-03</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:45</v>
+        <v>3:19</v>
       </c>
       <c r="H19" t="str">
-        <v>Ocean Alley</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-03</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G20" t="str">
-        <v>6:29</v>
+        <v>3:03</v>
       </c>
       <c r="H20" t="str">
-        <v>RAYE</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-03</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:17</v>
+        <v>3:56</v>
       </c>
       <c r="H21" t="str">
-        <v>Take That</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-03</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:22</v>
+        <v>3:58</v>
       </c>
       <c r="H22" t="str">
-        <v>Armik</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B23" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-03</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:10</v>
+        <v>3:56</v>
       </c>
       <c r="H23" t="str">
-        <v>Switchfoot</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B24" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-03</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H24" t="str">
-        <v>Peter Gabriel</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-03</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:03</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>Sarah Julia</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B26" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-03</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:56</v>
+        <v>2:16</v>
       </c>
       <c r="H26" t="str">
-        <v>Chris Norman</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>7d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-03</v>
@@ -1404,10 +1404,10 @@
         <v>7d ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:58</v>
+        <v>3:08</v>
       </c>
       <c r="H27" t="str">
-        <v>Alan Walker</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>7d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-03</v>
@@ -1442,10 +1442,10 @@
         <v>7d ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:56</v>
+        <v>3:38</v>
       </c>
       <c r="H28" t="str">
-        <v>Charlie Puth</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B29" t="str">
         <v>7d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-03</v>
@@ -1480,10 +1480,10 @@
         <v>7d ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:50</v>
+        <v>3:01</v>
       </c>
       <c r="H29" t="str">
-        <v>Miley Cyrus</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B30" t="str">
         <v>7d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-03</v>
@@ -1518,10 +1518,10 @@
         <v>7d ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:42</v>
+        <v>3:59</v>
       </c>
       <c r="H30" t="str">
-        <v>Conan Gray</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>7d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-03</v>
@@ -1556,10 +1556,10 @@
         <v>7d ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:16</v>
+        <v>2:59</v>
       </c>
       <c r="H31" t="str">
-        <v>Charlie Puth</v>
+        <v>Loreen</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B32" t="str">
         <v>7d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-03</v>
@@ -1594,10 +1594,10 @@
         <v>7d ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:08</v>
+        <v>2:58</v>
       </c>
       <c r="H32" t="str">
-        <v>Kylie Morgan</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B33" t="str">
         <v>7d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-03</v>
@@ -1632,10 +1632,10 @@
         <v>7d ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:38</v>
+        <v>3:49</v>
       </c>
       <c r="H33" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B34" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-03</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:01</v>
+        <v>3:22</v>
       </c>
       <c r="H34" t="str">
-        <v>Angelina Mango</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B35" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-03</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:59</v>
+        <v>3:50</v>
       </c>
       <c r="H35" t="str">
-        <v>Julio Iglesias</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
       </c>
       <c r="B36" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-03</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:59</v>
+        <v>6:43</v>
       </c>
       <c r="H36" t="str">
-        <v>Loreen</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>7d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-03</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:58</v>
+        <v>4:52</v>
       </c>
       <c r="H37" t="str">
-        <v>Jessie Ware</v>
+        <v>Eagles</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-03</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:49</v>
+        <v>3:13</v>
       </c>
       <c r="H38" t="str">
-        <v>Holly Humberstone</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-03</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:22</v>
+        <v>3:28</v>
       </c>
       <c r="H39" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-03</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:50</v>
+        <v>3:01</v>
       </c>
       <c r="H40" t="str">
-        <v>Ella Langley</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B41" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=aNRzuDqoT3Q</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-03</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G41" t="str">
-        <v>6:43</v>
+        <v>4:00</v>
       </c>
       <c r="H41" t="str">
-        <v>David Gilmour</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>David Gilmour - Time / Breathe (In The Air) (reprise) (Live at Allianz Parque, São Paulo, 2015) - David Gilmour</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B42" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-03</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:52</v>
+        <v>5:35</v>
       </c>
       <c r="H42" t="str">
-        <v>Eagles</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8d ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-03</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8d ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:13</v>
+        <v>3:01</v>
       </c>
       <c r="H43" t="str">
-        <v>Moody Joody</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B44" t="str">
-        <v>9d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-03</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:28</v>
+        <v>3:40</v>
       </c>
       <c r="H44" t="str">
-        <v>Jackson Dean</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-03</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:01</v>
+        <v>2:25</v>
       </c>
       <c r="H45" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>twocolors</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B46" t="str">
-        <v>9d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-03</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:00</v>
+        <v>3:42</v>
       </c>
       <c r="H46" t="str">
-        <v>Madison Cunningham</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B47" t="str">
-        <v>9d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-03</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G47" t="str">
-        <v>5:35</v>
+        <v>3:56</v>
       </c>
       <c r="H47" t="str">
-        <v>mary in the junkyard</v>
+        <v>Prince</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-03</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:01</v>
+        <v>5:12</v>
       </c>
       <c r="H48" t="str">
-        <v>Adam Sanders</v>
+        <v>RAYE</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-03</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12d ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:40</v>
+        <v>3:30</v>
       </c>
       <c r="H49" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>The Warning</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>12d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-03</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:25</v>
+        <v>3:18</v>
       </c>
       <c r="H50" t="str">
-        <v>twocolors</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-03</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:42</v>
+        <v>3:33</v>
       </c>
       <c r="H51" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B52" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-03</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:56</v>
+        <v>5:53</v>
       </c>
       <c r="H52" t="str">
-        <v>Prince</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B53" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-03</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G53" t="str">
-        <v>5:12</v>
+        <v>2:37</v>
       </c>
       <c r="H53" t="str">
-        <v>RAYE</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B54" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-03</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:30</v>
+        <v>2:26</v>
       </c>
       <c r="H54" t="str">
-        <v>The Warning</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-03</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:18</v>
+        <v>2:40</v>
       </c>
       <c r="H55" t="str">
-        <v>Pentatonix</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B56" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-03</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:33</v>
+        <v>3:30</v>
       </c>
       <c r="H56" t="str">
-        <v>Tenille Townes</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-03</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:53</v>
+        <v>4:02</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B58" t="str">
         <v>2w ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-03</v>
@@ -2582,10 +2582,10 @@
         <v>2w ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:37</v>
+        <v>3:40</v>
       </c>
       <c r="H58" t="str">
-        <v>Niall Horan</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>2w ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-03</v>
@@ -2620,10 +2620,10 @@
         <v>2w ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:26</v>
+        <v>2:22</v>
       </c>
       <c r="H59" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2w ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-03</v>
@@ -2658,10 +2658,10 @@
         <v>2w ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:40</v>
+        <v>3:47</v>
       </c>
       <c r="H60" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>2w ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-03</v>
@@ -2696,10 +2696,10 @@
         <v>2w ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:30</v>
+        <v>3:39</v>
       </c>
       <c r="H61" t="str">
-        <v>Jackson Dean</v>
+        <v>Cannons</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2w ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-03</v>
@@ -2734,10 +2734,10 @@
         <v>2w ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:02</v>
+        <v>4:10</v>
       </c>
       <c r="H62" t="str">
-        <v>Foo Fighters</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B63" t="str">
         <v>2w ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-03</v>
@@ -2772,10 +2772,10 @@
         <v>2w ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:40</v>
+        <v>4:47</v>
       </c>
       <c r="H63" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B64" t="str">
         <v>2w ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-03</v>
@@ -2810,10 +2810,10 @@
         <v>2w ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:22</v>
+        <v>2:14</v>
       </c>
       <c r="H64" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>aron!</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B65" t="str">
         <v>2w ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-03</v>
@@ -2848,10 +2848,10 @@
         <v>2w ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:47</v>
+        <v>4:00</v>
       </c>
       <c r="H65" t="str">
-        <v>Ella Langley</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2w ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-03</v>
@@ -2886,10 +2886,10 @@
         <v>2w ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:39</v>
+        <v>3:56</v>
       </c>
       <c r="H66" t="str">
-        <v>Cannons</v>
+        <v>DMA'S</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2w ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-03</v>
@@ -2924,10 +2924,10 @@
         <v>2w ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:10</v>
+        <v>3:17</v>
       </c>
       <c r="H67" t="str">
-        <v>Luke Combs</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2w ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-03</v>
@@ -2962,10 +2962,10 @@
         <v>2w ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:47</v>
+        <v>3:17</v>
       </c>
       <c r="H68" t="str">
-        <v>Nessa Barrett</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B69" t="str">
         <v>2w ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-03</v>
@@ -3000,10 +3000,10 @@
         <v>2w ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:14</v>
+        <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>aron!</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2w ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-03</v>
@@ -3038,10 +3038,10 @@
         <v>2w ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:00</v>
+        <v>3:38</v>
       </c>
       <c r="H70" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B71" t="str">
         <v>2w ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-03</v>
@@ -3076,10 +3076,10 @@
         <v>2w ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:56</v>
+        <v>4:11</v>
       </c>
       <c r="H71" t="str">
-        <v>DMA'S</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>2w ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-03</v>
@@ -3114,10 +3114,10 @@
         <v>2w ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:17</v>
+        <v>2:57</v>
       </c>
       <c r="H72" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B73" t="str">
         <v>2w ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-03</v>
@@ -3152,10 +3152,10 @@
         <v>2w ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:17</v>
+        <v>3:47</v>
       </c>
       <c r="H73" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B74" t="str">
         <v>2w ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-03</v>
@@ -3190,10 +3190,10 @@
         <v>2w ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:31</v>
+        <v>7:10</v>
       </c>
       <c r="H74" t="str">
-        <v>Nick Carter</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B75" t="str">
         <v>2w ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-03</v>
@@ -3228,10 +3228,10 @@
         <v>2w ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:38</v>
+        <v>3:06</v>
       </c>
       <c r="H75" t="str">
-        <v>Carly Pearce</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>2w ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-03</v>
@@ -3266,10 +3266,10 @@
         <v>2w ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:11</v>
+        <v>3:05</v>
       </c>
       <c r="H76" t="str">
-        <v>OneRepublic</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2w ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-03</v>
@@ -3304,10 +3304,10 @@
         <v>2w ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:57</v>
+        <v>3:12</v>
       </c>
       <c r="H77" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B78" t="str">
         <v>2w ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-03</v>
@@ -3342,10 +3342,10 @@
         <v>2w ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:47</v>
+        <v>9:11</v>
       </c>
       <c r="H78" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B79" t="str">
         <v>2w ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-03</v>
@@ -3380,10 +3380,10 @@
         <v>2w ago</v>
       </c>
       <c r="G79" t="str">
-        <v>7:10</v>
+        <v>3:49</v>
       </c>
       <c r="H79" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B80" t="str">
         <v>2w ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-03</v>
@@ -3418,10 +3418,10 @@
         <v>2w ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:06</v>
+        <v>3:28</v>
       </c>
       <c r="H80" t="str">
-        <v>Grace Enger</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2w ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-03</v>
@@ -3456,10 +3456,10 @@
         <v>2w ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:05</v>
+        <v>3:31</v>
       </c>
       <c r="H81" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B82" t="str">
         <v>2w ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-03</v>
@@ -3494,10 +3494,10 @@
         <v>2w ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:12</v>
+        <v>3:11</v>
       </c>
       <c r="H82" t="str">
-        <v>Freya Ridings</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-03</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G83" t="str">
-        <v>9:11</v>
+        <v>2:27</v>
       </c>
       <c r="H83" t="str">
-        <v>David Gilmour</v>
+        <v>HAUSER</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-03</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:49</v>
+        <v>3:34</v>
       </c>
       <c r="H84" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-03</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:28</v>
+        <v>2:50</v>
       </c>
       <c r="H85" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-03</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:31</v>
+        <v>3:51</v>
       </c>
       <c r="H86" t="str">
-        <v>Martin Garrix</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-03</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:11</v>
+        <v>2:39</v>
       </c>
       <c r="H87" t="str">
-        <v>Baby Queen</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-03</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:27</v>
+        <v>5:08</v>
       </c>
       <c r="H88" t="str">
-        <v>HAUSER</v>
+        <v>Jessie J</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-03</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:34</v>
+        <v>3:46</v>
       </c>
       <c r="H89" t="str">
-        <v>Holly Humberstone</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-03</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:50</v>
+        <v>2:42</v>
       </c>
       <c r="H90" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-03</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:51</v>
+        <v>2:31</v>
       </c>
       <c r="H91" t="str">
-        <v>Rick Astley</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B92" t="str">
         <v>3w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-03</v>
@@ -3874,10 +3874,10 @@
         <v>3w ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:39</v>
+        <v>3:14</v>
       </c>
       <c r="H92" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>3w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-03</v>
@@ -3912,10 +3912,10 @@
         <v>3w ago</v>
       </c>
       <c r="G93" t="str">
-        <v>5:08</v>
+        <v>3:22</v>
       </c>
       <c r="H93" t="str">
-        <v>Jessie J</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>3w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-03</v>
@@ -3950,10 +3950,10 @@
         <v>3w ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:46</v>
+        <v>3:43</v>
       </c>
       <c r="H94" t="str">
-        <v>Bishop Briggs</v>
+        <v>We Three</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
     